--- a/data_input/monthly/2026-02.xlsx
+++ b/data_input/monthly/2026-02.xlsx
@@ -16,19 +16,20 @@
     <sheet name="fact_promo_day" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="fact_lto_line" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="fact_partner" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="booking" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="ads_month" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="ads_brand" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="ads_objective" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="ads_campaign_detail" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="store_month" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="daily" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="coverage" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="dim_target" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="oa" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="cogs_cov" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="voucher_month" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="voucher_join" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="daily_party" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="booking" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="ads_month" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="ads_brand" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="ads_objective" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="ads_campaign_detail" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="store_month" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="daily" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="coverage" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="dim_target" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="oa" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="cogs_cov" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="voucher_month" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="voucher_join" sheetId="23" state="visible" r:id="rId23"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -472,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A78"/>
+  <dimension ref="A1:A80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="118" customWidth="1" min="1" max="1"/>
@@ -778,215 +779,229 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   booking                    8 dòng   bắt buộc: month, status</t>
+          <t xml:space="preserve">   daily_party               38 dòng   bắt buộc: date, store, net, tc</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Booking tiệc &amp; sự kiện — gộp theo tháng NHẬN LEAD (month) × tháng DIỄN RA (ev_month) × cửa hàng × phân khúc × loại × nguồn × trạng thái. month = Inquiry Date → Input Date → (thiếu cả hai) ngày sự kiện, khi đó inq_est đếm số lead bị ước. seg ∈ event|table, stage ∈ won|open|lost — luật ở $booking. exp chỉ cộng ô có số (exp_n lead); ô trống/TBA KHÔNG tính là 0. closed_n = số lead Confirmed đã nhập Closed Revenue.</t>
+          <t xml:space="preserve">                                  Phần KHÁCH TIỆC của `daily`: chỉ các hoá đơn có Số khách ≥ $guest_segment.party_min_guests, gộp theo NGÀY × cửa hàng. ETL tự sinh từ bảng kê hoá đơn (S02). Khách lẻ = daily − daily_party.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ads_month                  1 dòng   bắt buộc: month</t>
+          <t xml:space="preserve">   booking                    8 dòng   bắt buộc: month, status</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Meta Ads tổng theo tháng. CHỈ cộng dòng cấp campaign — cộng cả adset là nhân đôi.</t>
+          <t xml:space="preserve">                                  Booking tiệc &amp; sự kiện — gộp theo tháng NHẬN LEAD (month) × tháng DIỄN RA (ev_month) × cửa hàng × phân khúc × loại × nguồn × trạng thái. month = Inquiry Date → Input Date → (thiếu cả hai) ngày sự kiện, khi đó inq_est đếm số lead bị ước. seg ∈ event|table, stage ∈ won|open|lost — luật ở $booking. exp chỉ cộng ô có số (exp_n lead); ô trống/TBA KHÔNG tính là 0. closed_n = số lead Confirmed đã nhập Closed Revenue.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ads_brand                  4 dòng   bắt buộc: month, brand</t>
+          <t xml:space="preserve">   ads_month                  1 dòng   bắt buộc: month</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Meta Ads theo brand. Nhãn `Tuyển dụng` không phải marketing thương hiệu.</t>
+          <t xml:space="preserve">                                  Meta Ads tổng theo tháng. CHỈ cộng dòng cấp campaign — cộng cả adset là nhân đôi.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ads_objective              4 dòng   bắt buộc: month, objective</t>
+          <t xml:space="preserve">   ads_brand                  4 dòng   bắt buộc: month, brand</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Meta Ads theo mục tiêu chiến dịch.</t>
+          <t xml:space="preserve">                                  Meta Ads theo brand. Nhãn `Tuyển dụng` không phải marketing thương hiệu.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ads_campaign_detail       13 dòng   bắt buộc: month, brand, objective, campaign</t>
+          <t xml:space="preserve">   ads_objective              4 dòng   bắt buộc: month, objective</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Chi tiết từng chiến dịch Meta trong tháng. page = mã fanpage đầu tên chiến dịch · rkind = loại kết quả chuẩn hoá · funnel = 'booking' nếu thuộc phễu booking tiệc (luật $booking.ads).</t>
+          <t xml:space="preserve">                                  Meta Ads theo mục tiêu chiến dịch.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  loader tự tính: cpr</t>
+          <t xml:space="preserve">   ads_campaign_detail       13 dòng   bắt buộc: month, brand, objective, campaign</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   store_month                9 dòng   bắt buộc: month, store, net, guest, tc</t>
+          <t xml:space="preserve">                                  Chi tiết từng chiến dịch Meta trong tháng. page = mã fanpage đầu tên chiến dịch · rkind = loại kết quả chuẩn hoá · funnel = 'booking' nếu thuộc phễu booking tiệc (luật $booking.ads).</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  XƯƠNG SỐNG của hệ thống. net = doanh thu thuần · guest = số khách · tc = số hoá đơn.</t>
+          <t xml:space="preserve">                                  loader tự tính: cpr</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  loader tự tính: ta, aov, brand, tier</t>
+          <t xml:space="preserve">   store_month                9 dòng   bắt buộc: month, store, net, guest, tc</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   daily                    167 dòng   bắt buộc: date, store, net</t>
+          <t xml:space="preserve">                                  XƯƠNG SỐNG của hệ thống. net = doanh thu thuần · guest = số khách · tc = số hoá đơn.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Doanh thu theo NGÀY × cửa hàng. Ngày phải nằm trong tháng của file.</t>
+          <t xml:space="preserve">                                  loader tự tính: ta, aov, brand, tier</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   coverage                   1 dòng   bắt buộc: month</t>
+          <t xml:space="preserve">   daily                    167 dòng   bắt buộc: date, store, net</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Số ngày THỰC CÓ dữ liệu — nhận diện tháng chưa trọn kỳ. Không khai thì loader suy từ daily.</t>
+          <t xml:space="preserve">                                  Doanh thu theo NGÀY × cửa hàng. Ngày phải nằm trong tháng của file.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  loader tự tính: partial</t>
+          <t xml:space="preserve">   coverage                   1 dòng   bắt buộc: month</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   dim_target                 4 dòng   bắt buộc: month, store, target</t>
+          <t xml:space="preserve">                                  Số ngày THỰC CÓ dữ liệu — nhận diện tháng chưa trọn kỳ. Không khai thì loader suy từ daily.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Target doanh thu theo cửa hàng × tháng. Được phép khai cả tháng tương lai.</t>
+          <t xml:space="preserve">                                  loader tự tính: partial</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   oa                         1 dòng   bắt buộc: month</t>
+          <t xml:space="preserve">   dim_target                 4 dòng   bắt buộc: month, store, target</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Zalo OA. follows = Quan tâm · views = Xem trang thông tin OA · menu = Tương tác thanh menu · content = Xem nội dung.</t>
+          <t xml:space="preserve">                                  Target doanh thu theo cửa hàng × tháng. Được phép khai cả tháng tương lai.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   cogs_cov                   1 dòng   bắt buộc: month</t>
+          <t xml:space="preserve">   oa                         1 dòng   bắt buộc: month</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Độ phủ giá vốn theo tháng.</t>
+          <t xml:space="preserve">                                  Zalo OA. follows = Quan tâm · views = Xem trang thông tin OA · menu = Tương tác thanh menu · content = Xem nội dung.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  loader tự tính: pct</t>
+          <t xml:space="preserve">   cogs_cov                   1 dòng   bắt buộc: month</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   voucher_month              4 dòng   bắt buộc: m, brand</t>
+          <t xml:space="preserve">                                  Độ phủ giá vốn theo tháng.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Voucher đã dùng theo tháng × brand.</t>
+          <t xml:space="preserve">                                  loader tự tính: pct</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   voucher_join               1 dòng   bắt buộc: m</t>
+          <t xml:space="preserve">   voucher_month              4 dòng   bắt buộc: m, brand</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Tỷ lệ voucher khớp được với hoá đơn trong cùng tháng.</t>
+          <t xml:space="preserve">                                  Voucher đã dùng theo tháng × brand.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   voucher_join               1 dòng   bắt buộc: m</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                  Tỷ lệ voucher khớp được với hoá đơn trong cùng tháng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">                                  loader tự tính: rate</t>
         </is>
@@ -998,6 +1013,852 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E39"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>net</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>28161410</v>
+      </c>
+      <c r="D2" t="n">
+        <v>58</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>784728</v>
+      </c>
+      <c r="D3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>6528035</v>
+      </c>
+      <c r="D4" t="n">
+        <v>12</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>4263700</v>
+      </c>
+      <c r="D5" t="n">
+        <v>20</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>NCB_9ST</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>517500</v>
+      </c>
+      <c r="D6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>24861597</v>
+      </c>
+      <c r="D7" t="n">
+        <v>27</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>138799000</v>
+      </c>
+      <c r="D8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>56244919</v>
+      </c>
+      <c r="D9" t="n">
+        <v>21</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>15811732</v>
+      </c>
+      <c r="D10" t="n">
+        <v>28</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>10444833</v>
+      </c>
+      <c r="D11" t="n">
+        <v>25</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1189600</v>
+      </c>
+      <c r="D12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>36268953</v>
+      </c>
+      <c r="D13" t="n">
+        <v>37</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>6531700</v>
+      </c>
+      <c r="D14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>4085913</v>
+      </c>
+      <c r="D15" t="n">
+        <v>12</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>5208925</v>
+      </c>
+      <c r="D16" t="n">
+        <v>29</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>86762844</v>
+      </c>
+      <c r="D17" t="n">
+        <v>45</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1748628</v>
+      </c>
+      <c r="D18" t="n">
+        <v>11</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>78246</v>
+      </c>
+      <c r="D19" t="n">
+        <v>11</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>22022700</v>
+      </c>
+      <c r="D20" t="n">
+        <v>13</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>20298600</v>
+      </c>
+      <c r="D21" t="n">
+        <v>28</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>9107208</v>
+      </c>
+      <c r="D22" t="n">
+        <v>66</v>
+      </c>
+      <c r="E22" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>2528064</v>
+      </c>
+      <c r="D23" t="n">
+        <v>23</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>18111832</v>
+      </c>
+      <c r="D24" t="n">
+        <v>41</v>
+      </c>
+      <c r="E24" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>5342546</v>
+      </c>
+      <c r="D25" t="n">
+        <v>25</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>3929310</v>
+      </c>
+      <c r="D26" t="n">
+        <v>41</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>6440202</v>
+      </c>
+      <c r="D27" t="n">
+        <v>20</v>
+      </c>
+      <c r="E27" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>148000</v>
+      </c>
+      <c r="D28" t="n">
+        <v>21</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>874314</v>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>796450</v>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>5643635</v>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1216000</v>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>2148000</v>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>IFC_SIG</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>106200</v>
+      </c>
+      <c r="D34" t="n">
+        <v>12</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>1971900</v>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>8108250</v>
+      </c>
+      <c r="D36" t="n">
+        <v>22</v>
+      </c>
+      <c r="E36" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>NCB_9ST</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>812250</v>
+      </c>
+      <c r="D37" t="n">
+        <v>17</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>NCB_NDC</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>1993600</v>
+      </c>
+      <c r="D38" t="n">
+        <v>28</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1679454</v>
+      </c>
+      <c r="D39" t="n">
+        <v>15</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1717,7 +2578,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1784,7 +2645,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1898,7 +2759,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2012,7 +2873,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2653,7 +3514,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2956,7 +3817,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6511,7 +7372,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6582,7 +7443,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6671,91 +7532,6 @@
       </c>
       <c r="C5" t="n">
         <v>340000000</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>month</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>follows</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>msgs</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>views</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>menu</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>content</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>days</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>7</v>
-      </c>
-      <c r="C2" t="n">
-        <v>9</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>21</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -6922,38 +7698,52 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>month</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>rev</t>
-        </is>
-      </c>
-      <c r="C1" s="5" t="inlineStr">
-        <is>
-          <t>rev_cov</t>
-        </is>
-      </c>
-      <c r="D1" s="5" t="inlineStr">
-        <is>
-          <t>sku</t>
-        </is>
-      </c>
-      <c r="E1" s="5" t="inlineStr">
-        <is>
-          <t>sku_cov</t>
-        </is>
-      </c>
-      <c r="F1" s="5" t="inlineStr">
-        <is>
-          <t>pct</t>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>follows</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>msgs</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>views</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>menu</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>content</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>days</t>
         </is>
       </c>
     </row>
@@ -6964,19 +7754,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4074479228</v>
+        <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>2032367000</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>601</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4988</v>
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -6990,33 +7783,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>month</t>
         </is>
       </c>
       <c r="B1" s="5" t="inlineStr">
         <is>
-          <t>brand</t>
+          <t>rev</t>
         </is>
       </c>
       <c r="C1" s="5" t="inlineStr">
         <is>
-          <t>used</t>
+          <t>rev_cov</t>
         </is>
       </c>
       <c r="D1" s="5" t="inlineStr">
         <is>
-          <t>rev</t>
+          <t>sku</t>
         </is>
       </c>
       <c r="E1" s="5" t="inlineStr">
         <is>
-          <t>disc</t>
+          <t>sku_cov</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>pct</t>
         </is>
       </c>
     </row>
@@ -7026,82 +7824,20 @@
           <t>2026-02</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>NCB</t>
-        </is>
+      <c r="B2" t="n">
+        <v>4074479228</v>
       </c>
       <c r="C2" t="n">
-        <v>112</v>
+        <v>2032367000</v>
       </c>
       <c r="D2" t="n">
-        <v>39730000</v>
+        <v>601</v>
       </c>
       <c r="E2" t="n">
-        <v>8253200</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>NDC</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>15</v>
-      </c>
-      <c r="D3" t="n">
-        <v>26612100</v>
-      </c>
-      <c r="E3" t="n">
-        <v>5171000</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>NJFB</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>7</v>
-      </c>
-      <c r="D4" t="n">
-        <v>4498000</v>
-      </c>
-      <c r="E4" t="n">
-        <v>899600</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Không rõ</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>8</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1184000</v>
-      </c>
-      <c r="E5" t="n">
-        <v>236800</v>
+        <v>156</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.4988</v>
       </c>
     </row>
   </sheetData>
@@ -7110,6 +7846,131 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>used</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>rev</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>disc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>NCB</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>112</v>
+      </c>
+      <c r="D2" t="n">
+        <v>39730000</v>
+      </c>
+      <c r="E2" t="n">
+        <v>8253200</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>15</v>
+      </c>
+      <c r="D3" t="n">
+        <v>26612100</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5171000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NJFB</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4498000</v>
+      </c>
+      <c r="E4" t="n">
+        <v>899600</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Không rõ</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>8</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1184000</v>
+      </c>
+      <c r="E5" t="n">
+        <v>236800</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/data_input/monthly/2026-02.xlsx
+++ b/data_input/monthly/2026-02.xlsx
@@ -8,22 +8,22 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_HƯỚNG DẪN" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="crm_month" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="crm_store" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="member" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daypart" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="channel" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="identify" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="nature" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="recon" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="fact_promo_day" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="fact_lto_line" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="fact_partner" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_party" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="heat" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="payment" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="product_month" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="booking" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="booking" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="crm_month" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="crm_store" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="member" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daypart" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="channel" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="identify" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="nature" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="recon" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="fact_promo_day" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="fact_lto_line" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="fact_partner" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_party" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="heat" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="payment" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="product_month" sheetId="17" state="visible" r:id="rId17"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="store_month" sheetId="18" state="visible" r:id="rId18"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily" sheetId="19" state="visible" r:id="rId19"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="coverage" sheetId="20" state="visible" r:id="rId20"/>
@@ -46,7 +46,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -62,12 +62,8 @@
     <font>
       <b val="1"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00F3F2EE"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -84,11 +80,6 @@
         <fgColor rgb="FFF2EFE6"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F1F26"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -102,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -114,7 +105,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -660,238 +650,238 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   crm_month                  1 dòng   bắt buộc: month</t>
+          <t xml:space="preserve">   booking                    8 dòng   bắt buộc: month, status</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  CRM theo THÁNG toàn chuỗi (S27 file CRM tháng · S28 lịch sử T1–T8 · S29 CSV). spend_* = lượt chi tiêu của member theo lần (lần đầu / lần 2 / từ 3 lần); mem_rev = doanh thu thành viên SAU giảm; mem_inv = hoá đơn thành viên. Ô trống = nguồn không có (vd. T8 thiếu cơ cấu lượt) — KHÔNG phải 0. v_* = báo cáo voucher của CRM iPOS (khác nhật ký S11: bao mọi loại voucher).</t>
+          <t xml:space="preserve">                                  Booking tiệc &amp; sự kiện — gộp theo tháng NHẬN LEAD (month) × tháng DIỄN RA (ev_month) × cửa hàng × phân khúc × loại × nguồn × trạng thái. month = Inquiry Date → Input Date → (thiếu cả hai) ngày sự kiện, khi đó inq_est đếm số lead bị ước. seg ∈ event|table, stage ∈ won|open|lost — luật ở $booking. exp chỉ cộng ô có số (exp_n lead); ô trống/TBA KHÔNG tính là 0. closed_n = số lead Confirmed đã nhập Closed Revenue.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   crm_store                  7 dòng   bắt buộc: month, store</t>
+          <t xml:space="preserve">   crm_month                  1 dòng   bắt buộc: month</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  CRM theo THÁNG × CỬA HÀNG (mã dim_store). mem_* từ CSV doanh thu thành viên / sheet 2·4 file CRM; spend_* chỉ có tháng có file CRM tháng; v_* chỉ T8 (lịch sử) và tháng có sheet voucher hợp lệ.</t>
+          <t xml:space="preserve">                                  CRM theo THÁNG toàn chuỗi (S27 file CRM tháng · S28 lịch sử T1–T8 · S29 CSV). spend_* = lượt chi tiêu của member theo lần (lần đầu / lần 2 / từ 3 lần); mem_rev = doanh thu thành viên SAU giảm; mem_inv = hoá đơn thành viên. Ô trống = nguồn không có (vd. T8 thiếu cơ cấu lượt) — KHÔNG phải 0. v_* = báo cáo voucher của CRM iPOS (khác nhật ký S11: bao mọi loại voucher).</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   member                     1 dòng   bắt buộc: month</t>
+          <t xml:space="preserve">   crm_store                  7 dòng   bắt buộc: month, store</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Member đăng ký mới &amp; OA follow mới theo tháng (số toàn chuỗi).</t>
+          <t xml:space="preserve">                                  CRM theo THÁNG × CỬA HÀNG (mã dim_store). mem_* từ CSV doanh thu thành viên / sheet 2·4 file CRM; spend_* chỉ có tháng có file CRM tháng; v_* chỉ T8 (lịch sử) và tháng có sheet voucher hợp lệ.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   daypart                   36 dòng   bắt buộc: month, store, daypart</t>
+          <t xml:space="preserve">   member                     1 dòng   bắt buộc: month</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Doanh thu theo khung giờ trong ngày × cửa hàng (bộ lọc brand / phạm vi ở M3 cần cột store).</t>
+          <t xml:space="preserve">                                  Member đăng ký mới &amp; OA follow mới theo tháng (số toàn chuỗi).</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   channel                   16 dòng   bắt buộc: month, store, channel</t>
+          <t xml:space="preserve">   daypart                   36 dòng   bắt buộc: month, store, daypart</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Doanh thu theo kênh bán (tại chỗ, mang về, giao hàng…) × cửa hàng.</t>
+          <t xml:space="preserve">                                  Doanh thu theo khung giờ trong ngày × cửa hàng (bộ lọc brand / phạm vi ở M3 cần cột store).</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   identify                   1 dòng   bắt buộc: month, bills, id_bills</t>
+          <t xml:space="preserve">   channel                   16 dòng   bắt buộc: month, store, channel</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Tỷ lệ hoá đơn nhận diện được khách — trần trên của mọi phép quy doanh thu về khách. `items` = số dòng món đã xử lý trong tháng, nuôi thẻ đếm ở tab D1.</t>
+          <t xml:space="preserve">                                  Doanh thu theo kênh bán (tại chỗ, mang về, giao hàng…) × cửa hàng.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  loader tự tính: rate</t>
+          <t xml:space="preserve">   identify                   1 dòng   bắt buộc: month, bills, id_bills</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   nature                    14 dòng   bắt buộc: month, nature, brand, rev</t>
+          <t xml:space="preserve">                                  Tỷ lệ hoá đơn nhận diện được khách — trần trên của mọi phép quy doanh thu về khách. `items` = số dòng món đã xử lý trong tháng, nuôi thẻ đếm ở tab D1.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Bản chất chương trình khuyến mãi. nature ∈ COMMERCIAL|INTERNAL|PARTNER|LOYALTY. `rev` = doanh thu chạm (cấp dòng món, THÀNH TIỀN) · `disc` = chiết khấu thật (cấp HOÁ ĐƠN) — hai base khác nhau, xem fact_promo_day.</t>
+          <t xml:space="preserve">                                  loader tự tính: rate</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   recon                      9 dòng   bắt buộc: month, store, net</t>
+          <t xml:space="preserve">   nature                    14 dòng   bắt buộc: month, nature, brand, rev</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Đối soát ba tầng: bảng tháng ↔ bảng món ↔ bảng hoá đơn.</t>
+          <t xml:space="preserve">                                  Bản chất chương trình khuyến mãi. nature ∈ COMMERCIAL|INTERNAL|PARTNER|LOYALTY. `rev` = doanh thu chạm (cấp dòng món, THÀNH TIỀN) · `disc` = chiết khấu thật (cấp HOÁ ĐƠN) — hai base khác nhau, xem fact_promo_day.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  loader tự tính: d_bill</t>
+          <t xml:space="preserve">   recon                      9 dòng   bắt buộc: month, store, net</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   fact_promo_day           559 dòng   bắt buộc: date, store, name_pos</t>
+          <t xml:space="preserve">                                  Đối soát ba tầng: bảng tháng ↔ bảng món ↔ bảng hoá đơn.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  CTKM theo NGÀY × cửa hàng — nền của M7.2. `disc` = Giảm giá + Chiết khấu ở cấp HOÁ ĐƠN · `voucher` = Phiếu GG, để riêng vì voucher là phương thức thanh toán chứ không phải giảm giá. `net` = Tổng tiền (cùng base với daily/store_month — kỳ nền của M7.2 lấy từ đó). `rev`/`items` từ lane dòng món theo THÀNH TIỀN — base khác `net`, đừng cộng chung. `name_pos` giữ nguyên văn, chuẩn hoá ở dim_campaign.</t>
+          <t xml:space="preserve">                                  loader tự tính: d_bill</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   fact_lto_line            120 dòng   bắt buộc: date, store, bill, item_code</t>
+          <t xml:space="preserve">   fact_promo_day           559 dòng   bắt buộc: date, store, name_pos</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Dòng món thuộc nhóm LTO (Nhóm món chứa $campaign.lto_group_rx) gắn TỔNG hoá đơn chứa nó — nền doanh thu CTKM của chương trình LTO chạy theo món. `bill_net` = Tổng tiền cả hoá đơn (gồm món khác) · `line_rev` = Thành tiền riêng dòng LTO. Một hoá đơn có nhiều dòng LTO → cộng bill_net theo hoá đơn DUY NHẤT.</t>
+          <t xml:space="preserve">                                  CTKM theo NGÀY × cửa hàng — nền của M7.2. `disc` = Giảm giá + Chiết khấu ở cấp HOÁ ĐƠN · `voucher` = Phiếu GG, để riêng vì voucher là phương thức thanh toán chứ không phải giảm giá. `net` = Tổng tiền (cùng base với daily/store_month — kỳ nền của M7.2 lấy từ đó). `rev`/`items` từ lane dòng món theo THÀNH TIỀN — base khác `net`, đừng cộng chung. `name_pos` giữ nguyên văn, chuẩn hoá ở dim_campaign.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   fact_partner               3 dòng   bắt buộc: store, partner, basis</t>
+          <t xml:space="preserve">   fact_lto_line            120 dòng   bắt buộc: date, store, bill, item_code</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Hoá đơn ĐỐI TÁC theo tháng × cửa hàng × đối tác — nền chung của M7 (thẻ Đối tác) và M9. Mỗi hoá đơn thuộc MỘT đối tác, nhận theo thứ tự `basis`: CTKM (tên CTKM khớp luật PARTNER, mã ở $promo_nature.rules[].partner) → NGUON (cột Nguồn là nền tảng) → PTTT (trả qua ví nền tảng). `camp` = tên CTKM nguyên văn (có thể rỗng). `net` = Tổng tiền (cùng base store_month) · `gross` = trước giảm giá · `disc` = Giảm giá + Chiết khấu · `voucher` = Phiếu GG · `commission` = cột Hoa hồng của POS.</t>
+          <t xml:space="preserve">                                  Dòng món thuộc nhóm LTO (Nhóm món chứa $campaign.lto_group_rx) gắn TỔNG hoá đơn chứa nó — nền doanh thu CTKM của chương trình LTO chạy theo món. `bill_net` = Tổng tiền cả hoá đơn (gồm món khác) · `line_rev` = Thành tiền riêng dòng LTO. Một hoá đơn có nhiều dòng LTO → cộng bill_net theo hoá đơn DUY NHẤT.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   daily_party               38 dòng   bắt buộc: date, store, net, tc</t>
+          <t xml:space="preserve">   fact_partner               3 dòng   bắt buộc: store, partner, basis</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Phần KHÁCH TIỆC của `daily`: chỉ các hoá đơn có Số khách ≥ $guest_segment.party_min_guests, gộp theo NGÀY × cửa hàng. ETL tự sinh từ bảng kê hoá đơn (S02). Khách lẻ = daily − daily_party.</t>
+          <t xml:space="preserve">                                  Hoá đơn ĐỐI TÁC theo tháng × cửa hàng × đối tác — nền chung của M7 (thẻ Đối tác) và M9. Mỗi hoá đơn thuộc MỘT đối tác, nhận theo thứ tự `basis`: CTKM (tên CTKM khớp luật PARTNER, mã ở $promo_nature.rules[].partner) → NGUON (cột Nguồn là nền tảng) → PTTT (trả qua ví nền tảng). `camp` = tên CTKM nguyên văn (có thể rỗng). `net` = Tổng tiền (cùng base store_month) · `gross` = trước giảm giá · `disc` = Giảm giá + Chiết khấu · `voucher` = Phiếu GG · `commission` = cột Hoa hồng của POS.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   heat                     636 dòng   bắt buộc: month, store, dow, hour_in</t>
+          <t xml:space="preserve">   daily_party               38 dòng   bắt buộc: date, store, net, tc</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Ma trận giờ vào × thứ theo tháng × cửa hàng. dow: 0 = Thứ 2 … 6 = Chủ nhật.</t>
+          <t xml:space="preserve">                                  Phần KHÁCH TIỆC của `daily`: chỉ các hoá đơn có Số khách ≥ $guest_segment.party_min_guests, gộp theo NGÀY × cửa hàng. ETL tự sinh từ bảng kê hoá đơn (S02). Khách lẻ = daily − daily_party.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   payment                  120 dòng   bắt buộc: month, store, pttt</t>
+          <t xml:space="preserve">   heat                     636 dòng   bắt buộc: month, store, dow, hour_in</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Doanh thu theo phương thức thanh toán × tháng × cửa hàng.</t>
+          <t xml:space="preserve">                                  Ma trận giờ vào × thứ theo tháng × cửa hàng. dow: 0 = Thứ 2 … 6 = Chủ nhật.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   product_month            953 dòng   bắt buộc: store, ma, qty, rev</t>
+          <t xml:space="preserve">   payment                  120 dòng   bắt buộc: month, store, pttt</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Bán món theo tháng × cửa hàng (POS báo cáo bán hàng). rev = Thành tiền (trước phí DV &amp; VAT). cogs = giá vốn BOM × số lượng — TRỐNG khi món chưa có BOM. M2 lọc brand / phạm vi / kỳ trên bảng này.</t>
+          <t xml:space="preserve">                                  Doanh thu theo phương thức thanh toán × tháng × cửa hàng.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   booking                    8 dòng   bắt buộc: month, status</t>
+          <t xml:space="preserve">   product_month            953 dòng   bắt buộc: store, ma, qty, rev</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Booking tiệc &amp; sự kiện — gộp theo tháng NHẬN LEAD (month) × tháng DIỄN RA (ev_month) × cửa hàng × phân khúc × loại × nguồn × trạng thái. month = Inquiry Date → Input Date → (thiếu cả hai) ngày sự kiện, khi đó inq_est đếm số lead bị ước. seg ∈ event|table, stage ∈ won|open|lost — luật ở $booking. exp chỉ cộng ô có số (exp_n lead); ô trống/TBA KHÔNG tính là 0. closed_n = số lead Confirmed đã nhập Closed Revenue.</t>
+          <t xml:space="preserve">                                  Bán món theo tháng × cửa hàng (POS báo cáo bán hàng). rev = Thành tiền (trước phí DV &amp; VAT). cogs = giá vốn BOM × số lượng — TRỐNG khi món chưa có BOM. M2 lọc brand / phạm vi / kỳ trên bảng này.</t>
         </is>
       </c>
     </row>
@@ -1118,6 +1108,375 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>net</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>net_item</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>net_bill</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>tc_bill</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>guest_bill</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>IFC_SIG</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>80893500</v>
+      </c>
+      <c r="D2" t="n">
+        <v>80893500</v>
+      </c>
+      <c r="E2" t="n">
+        <v>80893500</v>
+      </c>
+      <c r="F2" t="n">
+        <v>348</v>
+      </c>
+      <c r="G2" t="n">
+        <v>348</v>
+      </c>
+      <c r="H2" t="n">
+        <v>612</v>
+      </c>
+      <c r="I2" t="n">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>NCB_9ST</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>3627350</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3627350</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3627350</v>
+      </c>
+      <c r="F3" t="n">
+        <v>20</v>
+      </c>
+      <c r="G3" t="n">
+        <v>20</v>
+      </c>
+      <c r="H3" t="n">
+        <v>65</v>
+      </c>
+      <c r="I3" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>799090930</v>
+      </c>
+      <c r="D4" t="n">
+        <v>799090930</v>
+      </c>
+      <c r="E4" t="n">
+        <v>799090930</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1417</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1417</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2506</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2506</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>NCB_GW</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>13133000</v>
+      </c>
+      <c r="D5" t="n">
+        <v>13133000</v>
+      </c>
+      <c r="E5" t="n">
+        <v>13133000</v>
+      </c>
+      <c r="F5" t="n">
+        <v>73</v>
+      </c>
+      <c r="G5" t="n">
+        <v>73</v>
+      </c>
+      <c r="H5" t="n">
+        <v>109</v>
+      </c>
+      <c r="I5" t="n">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>452497650</v>
+      </c>
+      <c r="D6" t="n">
+        <v>452497650</v>
+      </c>
+      <c r="E6" t="n">
+        <v>452497650</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1933</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1933</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3147</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3147</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>NCB_NDC</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>4223000</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4223000</v>
+      </c>
+      <c r="E7" t="n">
+        <v>4223000</v>
+      </c>
+      <c r="F7" t="n">
+        <v>9</v>
+      </c>
+      <c r="G7" t="n">
+        <v>9</v>
+      </c>
+      <c r="H7" t="n">
+        <v>52</v>
+      </c>
+      <c r="I7" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>607080194</v>
+      </c>
+      <c r="D8" t="n">
+        <v>607080194</v>
+      </c>
+      <c r="E8" t="n">
+        <v>607080194</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1094</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1094</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2344</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2344</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2016252943</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2016252941</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2016252943</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2973</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2973</v>
+      </c>
+      <c r="H9" t="n">
+        <v>7521</v>
+      </c>
+      <c r="I9" t="n">
+        <v>7521</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>172245819</v>
+      </c>
+      <c r="D10" t="n">
+        <v>172245820</v>
+      </c>
+      <c r="E10" t="n">
+        <v>172245819</v>
+      </c>
+      <c r="F10" t="n">
+        <v>150</v>
+      </c>
+      <c r="G10" t="n">
+        <v>150</v>
+      </c>
+      <c r="H10" t="n">
+        <v>359</v>
+      </c>
+      <c r="I10" t="n">
+        <v>359</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -28210,7 +28569,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -36139,7 +36498,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -36389,7 +36748,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -37235,7 +37594,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -52553,7 +52912,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -55361,7 +55720,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -92709,7 +93068,3865 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>net</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>gross</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>disc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>IFC_SIG</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>80893500</v>
+      </c>
+      <c r="D2" t="n">
+        <v>612</v>
+      </c>
+      <c r="E2" t="n">
+        <v>348</v>
+      </c>
+      <c r="F2" t="n">
+        <v>82003000</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1109500</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>NCB_9ST</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>3627350</v>
+      </c>
+      <c r="D3" t="n">
+        <v>65</v>
+      </c>
+      <c r="E3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F3" t="n">
+        <v>4580000</v>
+      </c>
+      <c r="G3" t="n">
+        <v>952650</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>799090930</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2506</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1417</v>
+      </c>
+      <c r="F4" t="n">
+        <v>856626880</v>
+      </c>
+      <c r="G4" t="n">
+        <v>57535950</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>NCB_GW</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>13133000</v>
+      </c>
+      <c r="D5" t="n">
+        <v>109</v>
+      </c>
+      <c r="E5" t="n">
+        <v>73</v>
+      </c>
+      <c r="F5" t="n">
+        <v>13133000</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>452497650</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3147</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1933</v>
+      </c>
+      <c r="F6" t="n">
+        <v>474860000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>22362350</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>NCB_NDC</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>4223000</v>
+      </c>
+      <c r="D7" t="n">
+        <v>52</v>
+      </c>
+      <c r="E7" t="n">
+        <v>9</v>
+      </c>
+      <c r="F7" t="n">
+        <v>5922000</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1699000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>607080194</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2344</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1094</v>
+      </c>
+      <c r="F8" t="n">
+        <v>639881844</v>
+      </c>
+      <c r="G8" t="n">
+        <v>32801650</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2016252943</v>
+      </c>
+      <c r="D9" t="n">
+        <v>7521</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2973</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2097945393</v>
+      </c>
+      <c r="G9" t="n">
+        <v>81692450</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>172245819</v>
+      </c>
+      <c r="D10" t="n">
+        <v>359</v>
+      </c>
+      <c r="E10" t="n">
+        <v>150</v>
+      </c>
+      <c r="F10" t="n">
+        <v>192575569</v>
+      </c>
+      <c r="G10" t="n">
+        <v>20329750</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E168"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>net</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>NCB_9ST</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>446300</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>44949600</v>
+      </c>
+      <c r="D3" t="n">
+        <v>147</v>
+      </c>
+      <c r="E3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NCB_GW</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>818000</v>
+      </c>
+      <c r="D4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E4" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>21733600</v>
+      </c>
+      <c r="D5" t="n">
+        <v>126</v>
+      </c>
+      <c r="E5" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>99387758</v>
+      </c>
+      <c r="D6" t="n">
+        <v>314</v>
+      </c>
+      <c r="E6" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>10310488</v>
+      </c>
+      <c r="D7" t="n">
+        <v>17</v>
+      </c>
+      <c r="E7" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>NCB_9ST</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>69000</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>26682950</v>
+      </c>
+      <c r="D9" t="n">
+        <v>116</v>
+      </c>
+      <c r="E9" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>28472150</v>
+      </c>
+      <c r="D10" t="n">
+        <v>198</v>
+      </c>
+      <c r="E10" t="n">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2800000</v>
+      </c>
+      <c r="D11" t="n">
+        <v>11</v>
+      </c>
+      <c r="E11" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>30818138</v>
+      </c>
+      <c r="D12" t="n">
+        <v>104</v>
+      </c>
+      <c r="E12" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>9510869</v>
+      </c>
+      <c r="D13" t="n">
+        <v>18</v>
+      </c>
+      <c r="E13" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>45319500</v>
+      </c>
+      <c r="D14" t="n">
+        <v>172</v>
+      </c>
+      <c r="E14" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>NCB_GW</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>434000</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>30613000</v>
+      </c>
+      <c r="D16" t="n">
+        <v>215</v>
+      </c>
+      <c r="E16" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>NCB_NDC</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>88500</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>55749352</v>
+      </c>
+      <c r="D18" t="n">
+        <v>172</v>
+      </c>
+      <c r="E18" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>17550947</v>
+      </c>
+      <c r="D19" t="n">
+        <v>28</v>
+      </c>
+      <c r="E19" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>23863150</v>
+      </c>
+      <c r="D20" t="n">
+        <v>109</v>
+      </c>
+      <c r="E20" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>NCB_GW</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1241000</v>
+      </c>
+      <c r="D21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>30710250</v>
+      </c>
+      <c r="D22" t="n">
+        <v>243</v>
+      </c>
+      <c r="E22" t="n">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>10196350</v>
+      </c>
+      <c r="D23" t="n">
+        <v>44</v>
+      </c>
+      <c r="E23" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>26019974</v>
+      </c>
+      <c r="D24" t="n">
+        <v>120</v>
+      </c>
+      <c r="E24" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>9300608</v>
+      </c>
+      <c r="D25" t="n">
+        <v>22</v>
+      </c>
+      <c r="E25" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>NCB_9ST</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>726100</v>
+      </c>
+      <c r="D26" t="n">
+        <v>14</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>17016300</v>
+      </c>
+      <c r="D27" t="n">
+        <v>98</v>
+      </c>
+      <c r="E27" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>NCB_GW</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>118000</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>30295200</v>
+      </c>
+      <c r="D29" t="n">
+        <v>229</v>
+      </c>
+      <c r="E29" t="n">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>NCB_NDC</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>59000</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>4413700</v>
+      </c>
+      <c r="D31" t="n">
+        <v>33</v>
+      </c>
+      <c r="E31" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>79722056</v>
+      </c>
+      <c r="D32" t="n">
+        <v>214</v>
+      </c>
+      <c r="E32" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>6626286</v>
+      </c>
+      <c r="D33" t="n">
+        <v>15</v>
+      </c>
+      <c r="E33" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>NCB_9ST</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>207000</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>48523400</v>
+      </c>
+      <c r="D35" t="n">
+        <v>113</v>
+      </c>
+      <c r="E35" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>NCB_GW</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>157000</v>
+      </c>
+      <c r="D36" t="n">
+        <v>3</v>
+      </c>
+      <c r="E36" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>23532450</v>
+      </c>
+      <c r="D37" t="n">
+        <v>188</v>
+      </c>
+      <c r="E37" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>151586900</v>
+      </c>
+      <c r="D38" t="n">
+        <v>279</v>
+      </c>
+      <c r="E38" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>114603862</v>
+      </c>
+      <c r="D39" t="n">
+        <v>228</v>
+      </c>
+      <c r="E39" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>3234193</v>
+      </c>
+      <c r="D40" t="n">
+        <v>7</v>
+      </c>
+      <c r="E40" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>11888550</v>
+      </c>
+      <c r="D41" t="n">
+        <v>72</v>
+      </c>
+      <c r="E41" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>NCB_GW</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>1375000</v>
+      </c>
+      <c r="D42" t="n">
+        <v>8</v>
+      </c>
+      <c r="E42" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>15896400</v>
+      </c>
+      <c r="D43" t="n">
+        <v>93</v>
+      </c>
+      <c r="E43" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>5218850</v>
+      </c>
+      <c r="D44" t="n">
+        <v>37</v>
+      </c>
+      <c r="E44" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>67525243</v>
+      </c>
+      <c r="D45" t="n">
+        <v>230</v>
+      </c>
+      <c r="E45" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>15996935</v>
+      </c>
+      <c r="D46" t="n">
+        <v>31</v>
+      </c>
+      <c r="E46" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>21760200</v>
+      </c>
+      <c r="D47" t="n">
+        <v>104</v>
+      </c>
+      <c r="E47" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>NCB_GW</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>2358000</v>
+      </c>
+      <c r="D48" t="n">
+        <v>15</v>
+      </c>
+      <c r="E48" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>10973100</v>
+      </c>
+      <c r="D49" t="n">
+        <v>67</v>
+      </c>
+      <c r="E49" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>9908600</v>
+      </c>
+      <c r="D50" t="n">
+        <v>57</v>
+      </c>
+      <c r="E50" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>81013164</v>
+      </c>
+      <c r="D51" t="n">
+        <v>339</v>
+      </c>
+      <c r="E51" t="n">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>6473943</v>
+      </c>
+      <c r="D52" t="n">
+        <v>11</v>
+      </c>
+      <c r="E52" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>23149000</v>
+      </c>
+      <c r="D53" t="n">
+        <v>127</v>
+      </c>
+      <c r="E53" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>18762300</v>
+      </c>
+      <c r="D54" t="n">
+        <v>148</v>
+      </c>
+      <c r="E54" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>12827500</v>
+      </c>
+      <c r="D55" t="n">
+        <v>85</v>
+      </c>
+      <c r="E55" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>85365393</v>
+      </c>
+      <c r="D56" t="n">
+        <v>189</v>
+      </c>
+      <c r="E56" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>423792</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>NCB_9ST</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>108000</v>
+      </c>
+      <c r="D58" t="n">
+        <v>3</v>
+      </c>
+      <c r="E58" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>28378100</v>
+      </c>
+      <c r="D59" t="n">
+        <v>153</v>
+      </c>
+      <c r="E59" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>NCB_GW</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>589000</v>
+      </c>
+      <c r="D60" t="n">
+        <v>8</v>
+      </c>
+      <c r="E60" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>18494550</v>
+      </c>
+      <c r="D61" t="n">
+        <v>154</v>
+      </c>
+      <c r="E61" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>NCB_NDC</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>132500</v>
+      </c>
+      <c r="D62" t="n">
+        <v>3</v>
+      </c>
+      <c r="E62" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>12602650</v>
+      </c>
+      <c r="D63" t="n">
+        <v>75</v>
+      </c>
+      <c r="E63" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>77370325</v>
+      </c>
+      <c r="D64" t="n">
+        <v>198</v>
+      </c>
+      <c r="E64" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>8015998</v>
+      </c>
+      <c r="D65" t="n">
+        <v>11</v>
+      </c>
+      <c r="E65" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>37869350</v>
+      </c>
+      <c r="D66" t="n">
+        <v>117</v>
+      </c>
+      <c r="E66" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>NCB_GW</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>849000</v>
+      </c>
+      <c r="D67" t="n">
+        <v>4</v>
+      </c>
+      <c r="E67" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>17931650</v>
+      </c>
+      <c r="D68" t="n">
+        <v>120</v>
+      </c>
+      <c r="E68" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>5180450</v>
+      </c>
+      <c r="D69" t="n">
+        <v>37</v>
+      </c>
+      <c r="E69" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>46644344</v>
+      </c>
+      <c r="D70" t="n">
+        <v>201</v>
+      </c>
+      <c r="E70" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>7319643</v>
+      </c>
+      <c r="D71" t="n">
+        <v>15</v>
+      </c>
+      <c r="E71" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>NCB_9ST</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>162750</v>
+      </c>
+      <c r="D72" t="n">
+        <v>3</v>
+      </c>
+      <c r="E72" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>245398630</v>
+      </c>
+      <c r="D73" t="n">
+        <v>96</v>
+      </c>
+      <c r="E73" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>NCB_GW</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>884000</v>
+      </c>
+      <c r="D74" t="n">
+        <v>12</v>
+      </c>
+      <c r="E74" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>22861950</v>
+      </c>
+      <c r="D75" t="n">
+        <v>150</v>
+      </c>
+      <c r="E75" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>96088544</v>
+      </c>
+      <c r="D76" t="n">
+        <v>102</v>
+      </c>
+      <c r="E76" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>54555506</v>
+      </c>
+      <c r="D77" t="n">
+        <v>212</v>
+      </c>
+      <c r="E77" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>9885078</v>
+      </c>
+      <c r="D78" t="n">
+        <v>25</v>
+      </c>
+      <c r="E78" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>24040100</v>
+      </c>
+      <c r="D79" t="n">
+        <v>87</v>
+      </c>
+      <c r="E79" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>NCB_GW</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>926000</v>
+      </c>
+      <c r="D80" t="n">
+        <v>8</v>
+      </c>
+      <c r="E80" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>11861450</v>
+      </c>
+      <c r="D81" t="n">
+        <v>89</v>
+      </c>
+      <c r="E81" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>9553850</v>
+      </c>
+      <c r="D82" t="n">
+        <v>53</v>
+      </c>
+      <c r="E82" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>46291343</v>
+      </c>
+      <c r="D83" t="n">
+        <v>190</v>
+      </c>
+      <c r="E83" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>7708050</v>
+      </c>
+      <c r="D84" t="n">
+        <v>14</v>
+      </c>
+      <c r="E84" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>IFC_SIG</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>2884100</v>
+      </c>
+      <c r="D85" t="n">
+        <v>9</v>
+      </c>
+      <c r="E85" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>17504150</v>
+      </c>
+      <c r="D86" t="n">
+        <v>90</v>
+      </c>
+      <c r="E86" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>19043100</v>
+      </c>
+      <c r="D87" t="n">
+        <v>77</v>
+      </c>
+      <c r="E87" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>119778343</v>
+      </c>
+      <c r="D88" t="n">
+        <v>308</v>
+      </c>
+      <c r="E88" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>5364513</v>
+      </c>
+      <c r="D89" t="n">
+        <v>10</v>
+      </c>
+      <c r="E89" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>IFC_SIG</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>435000</v>
+      </c>
+      <c r="D90" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>11570700</v>
+      </c>
+      <c r="D91" t="n">
+        <v>73</v>
+      </c>
+      <c r="E91" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>13895850</v>
+      </c>
+      <c r="D92" t="n">
+        <v>67</v>
+      </c>
+      <c r="E92" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>63216848</v>
+      </c>
+      <c r="D93" t="n">
+        <v>258</v>
+      </c>
+      <c r="E93" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>2896689</v>
+      </c>
+      <c r="D94" t="n">
+        <v>6</v>
+      </c>
+      <c r="E94" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>IFC_SIG</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>20210400</v>
+      </c>
+      <c r="D95" t="n">
+        <v>44</v>
+      </c>
+      <c r="E95" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>30971600</v>
+      </c>
+      <c r="D96" t="n">
+        <v>85</v>
+      </c>
+      <c r="E96" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>83527290</v>
+      </c>
+      <c r="D97" t="n">
+        <v>360</v>
+      </c>
+      <c r="E97" t="n">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>IFC_SIG</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>14136500</v>
+      </c>
+      <c r="D98" t="n">
+        <v>133</v>
+      </c>
+      <c r="E98" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>27657000</v>
+      </c>
+      <c r="D99" t="n">
+        <v>146</v>
+      </c>
+      <c r="E99" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>127769849</v>
+      </c>
+      <c r="D100" t="n">
+        <v>593</v>
+      </c>
+      <c r="E100" t="n">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>IFC_SIG</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>13011000</v>
+      </c>
+      <c r="D101" t="n">
+        <v>139</v>
+      </c>
+      <c r="E101" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>25685500</v>
+      </c>
+      <c r="D102" t="n">
+        <v>147</v>
+      </c>
+      <c r="E102" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>116650290</v>
+      </c>
+      <c r="D103" t="n">
+        <v>544</v>
+      </c>
+      <c r="E103" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>IFC_SIG</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>9719000</v>
+      </c>
+      <c r="D104" t="n">
+        <v>94</v>
+      </c>
+      <c r="E104" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>20724000</v>
+      </c>
+      <c r="D105" t="n">
+        <v>117</v>
+      </c>
+      <c r="E105" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>126522372</v>
+      </c>
+      <c r="D106" t="n">
+        <v>564</v>
+      </c>
+      <c r="E106" t="n">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>IFC_SIG</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>9444000</v>
+      </c>
+      <c r="D107" t="n">
+        <v>95</v>
+      </c>
+      <c r="E107" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>18169000</v>
+      </c>
+      <c r="D108" t="n">
+        <v>122</v>
+      </c>
+      <c r="E108" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>88939862</v>
+      </c>
+      <c r="D109" t="n">
+        <v>409</v>
+      </c>
+      <c r="E109" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>IFC_SIG</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>2201000</v>
+      </c>
+      <c r="D110" t="n">
+        <v>20</v>
+      </c>
+      <c r="E110" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>20559000</v>
+      </c>
+      <c r="D111" t="n">
+        <v>127</v>
+      </c>
+      <c r="E111" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>5065000</v>
+      </c>
+      <c r="D112" t="n">
+        <v>25</v>
+      </c>
+      <c r="E112" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>25486400</v>
+      </c>
+      <c r="D113" t="n">
+        <v>138</v>
+      </c>
+      <c r="E113" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>101744461</v>
+      </c>
+      <c r="D114" t="n">
+        <v>477</v>
+      </c>
+      <c r="E114" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>7340204</v>
+      </c>
+      <c r="D115" t="n">
+        <v>19</v>
+      </c>
+      <c r="E115" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>IFC_SIG</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>1884000</v>
+      </c>
+      <c r="D116" t="n">
+        <v>17</v>
+      </c>
+      <c r="E116" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>27563800</v>
+      </c>
+      <c r="D117" t="n">
+        <v>141</v>
+      </c>
+      <c r="E117" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>11443400</v>
+      </c>
+      <c r="D118" t="n">
+        <v>63</v>
+      </c>
+      <c r="E118" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>21849650</v>
+      </c>
+      <c r="D119" t="n">
+        <v>119</v>
+      </c>
+      <c r="E119" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>72709573</v>
+      </c>
+      <c r="D120" t="n">
+        <v>331</v>
+      </c>
+      <c r="E120" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>5162648</v>
+      </c>
+      <c r="D121" t="n">
+        <v>9</v>
+      </c>
+      <c r="E121" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>IFC_SIG</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>901200</v>
+      </c>
+      <c r="D122" t="n">
+        <v>11</v>
+      </c>
+      <c r="E122" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>NCB_9ST</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>265500</v>
+      </c>
+      <c r="D123" t="n">
+        <v>6</v>
+      </c>
+      <c r="E123" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>22258100</v>
+      </c>
+      <c r="D124" t="n">
+        <v>97</v>
+      </c>
+      <c r="E124" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>22545150</v>
+      </c>
+      <c r="D125" t="n">
+        <v>180</v>
+      </c>
+      <c r="E125" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>10548300</v>
+      </c>
+      <c r="D126" t="n">
+        <v>95</v>
+      </c>
+      <c r="E126" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>40174163</v>
+      </c>
+      <c r="D127" t="n">
+        <v>198</v>
+      </c>
+      <c r="E127" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>7396993</v>
+      </c>
+      <c r="D128" t="n">
+        <v>15</v>
+      </c>
+      <c r="E128" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>IFC_SIG</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>740700</v>
+      </c>
+      <c r="D129" t="n">
+        <v>8</v>
+      </c>
+      <c r="E129" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>NCB_9ST</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>88500</v>
+      </c>
+      <c r="D130" t="n">
+        <v>3</v>
+      </c>
+      <c r="E130" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>29497550</v>
+      </c>
+      <c r="D131" t="n">
+        <v>127</v>
+      </c>
+      <c r="E131" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>NCB_GW</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>285000</v>
+      </c>
+      <c r="D132" t="n">
+        <v>3</v>
+      </c>
+      <c r="E132" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>17880450</v>
+      </c>
+      <c r="D133" t="n">
+        <v>140</v>
+      </c>
+      <c r="E133" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>14701400</v>
+      </c>
+      <c r="D134" t="n">
+        <v>114</v>
+      </c>
+      <c r="E134" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>41649428</v>
+      </c>
+      <c r="D135" t="n">
+        <v>161</v>
+      </c>
+      <c r="E135" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>14366112</v>
+      </c>
+      <c r="D136" t="n">
+        <v>32</v>
+      </c>
+      <c r="E136" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>IFC_SIG</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>2001200</v>
+      </c>
+      <c r="D137" t="n">
+        <v>8</v>
+      </c>
+      <c r="E137" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>NCB_9ST</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>59000</v>
+      </c>
+      <c r="D138" t="n">
+        <v>1</v>
+      </c>
+      <c r="E138" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>24422550</v>
+      </c>
+      <c r="D139" t="n">
+        <v>113</v>
+      </c>
+      <c r="E139" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>NCB_GW</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>205000</v>
+      </c>
+      <c r="D140" t="n">
+        <v>3</v>
+      </c>
+      <c r="E140" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>20358400</v>
+      </c>
+      <c r="D141" t="n">
+        <v>147</v>
+      </c>
+      <c r="E141" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>13035400</v>
+      </c>
+      <c r="D142" t="n">
+        <v>72</v>
+      </c>
+      <c r="E142" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>32036744</v>
+      </c>
+      <c r="D143" t="n">
+        <v>139</v>
+      </c>
+      <c r="E143" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>10478168</v>
+      </c>
+      <c r="D144" t="n">
+        <v>31</v>
+      </c>
+      <c r="E144" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>IFC_SIG</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>1341400</v>
+      </c>
+      <c r="D145" t="n">
+        <v>22</v>
+      </c>
+      <c r="E145" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>18176900</v>
+      </c>
+      <c r="D146" t="n">
+        <v>87</v>
+      </c>
+      <c r="E146" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>NCB_GW</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>654000</v>
+      </c>
+      <c r="D147" t="n">
+        <v>3</v>
+      </c>
+      <c r="E147" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>20145150</v>
+      </c>
+      <c r="D148" t="n">
+        <v>137</v>
+      </c>
+      <c r="E148" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>17245600</v>
+      </c>
+      <c r="D149" t="n">
+        <v>82</v>
+      </c>
+      <c r="E149" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>36075966</v>
+      </c>
+      <c r="D150" t="n">
+        <v>144</v>
+      </c>
+      <c r="E150" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>439992</v>
+      </c>
+      <c r="D151" t="n">
+        <v>2</v>
+      </c>
+      <c r="E151" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>IFC_SIG</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>1583100</v>
+      </c>
+      <c r="D152" t="n">
+        <v>9</v>
+      </c>
+      <c r="E152" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>NCB_9ST</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>1343250</v>
+      </c>
+      <c r="D153" t="n">
+        <v>27</v>
+      </c>
+      <c r="E153" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>28587800</v>
+      </c>
+      <c r="D154" t="n">
+        <v>150</v>
+      </c>
+      <c r="E154" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>NCB_GW</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>365000</v>
+      </c>
+      <c r="D155" t="n">
+        <v>3</v>
+      </c>
+      <c r="E155" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>27607700</v>
+      </c>
+      <c r="D156" t="n">
+        <v>175</v>
+      </c>
+      <c r="E156" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>NCB_NDC</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>3943000</v>
+      </c>
+      <c r="D157" t="n">
+        <v>46</v>
+      </c>
+      <c r="E157" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>8967100</v>
+      </c>
+      <c r="D158" t="n">
+        <v>74</v>
+      </c>
+      <c r="E158" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>46824918</v>
+      </c>
+      <c r="D159" t="n">
+        <v>140</v>
+      </c>
+      <c r="E159" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>1044767</v>
+      </c>
+      <c r="D160" t="n">
+        <v>4</v>
+      </c>
+      <c r="E160" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>IFC_SIG</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>400900</v>
+      </c>
+      <c r="D161" t="n">
+        <v>3</v>
+      </c>
+      <c r="E161" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>NCB_9ST</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>151950</v>
+      </c>
+      <c r="D162" t="n">
+        <v>3</v>
+      </c>
+      <c r="E162" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>29186400</v>
+      </c>
+      <c r="D163" t="n">
+        <v>153</v>
+      </c>
+      <c r="E163" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>NCB_GW</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>1875000</v>
+      </c>
+      <c r="D164" t="n">
+        <v>16</v>
+      </c>
+      <c r="E164" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>16239500</v>
+      </c>
+      <c r="D165" t="n">
+        <v>97</v>
+      </c>
+      <c r="E165" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>18722900</v>
+      </c>
+      <c r="D166" t="n">
+        <v>76</v>
+      </c>
+      <c r="E166" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>53566378</v>
+      </c>
+      <c r="D167" t="n">
+        <v>184</v>
+      </c>
+      <c r="E167" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>5398903</v>
+      </c>
+      <c r="D168" t="n">
+        <v>16</v>
+      </c>
+      <c r="E168" t="n">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -93429,4005 +97646,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>month</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>store</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>net</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>guest</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>tc</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>gross</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>disc</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>IFC_SIG</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>80893500</v>
-      </c>
-      <c r="D2" t="n">
-        <v>612</v>
-      </c>
-      <c r="E2" t="n">
-        <v>348</v>
-      </c>
-      <c r="F2" t="n">
-        <v>82003000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1109500</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>NCB_9ST</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>3627350</v>
-      </c>
-      <c r="D3" t="n">
-        <v>65</v>
-      </c>
-      <c r="E3" t="n">
-        <v>20</v>
-      </c>
-      <c r="F3" t="n">
-        <v>4580000</v>
-      </c>
-      <c r="G3" t="n">
-        <v>952650</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>799090930</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2506</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1417</v>
-      </c>
-      <c r="F4" t="n">
-        <v>856626880</v>
-      </c>
-      <c r="G4" t="n">
-        <v>57535950</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>NCB_GW</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>13133000</v>
-      </c>
-      <c r="D5" t="n">
-        <v>109</v>
-      </c>
-      <c r="E5" t="n">
-        <v>73</v>
-      </c>
-      <c r="F5" t="n">
-        <v>13133000</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>452497650</v>
-      </c>
-      <c r="D6" t="n">
-        <v>3147</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1933</v>
-      </c>
-      <c r="F6" t="n">
-        <v>474860000</v>
-      </c>
-      <c r="G6" t="n">
-        <v>22362350</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>NCB_NDC</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>4223000</v>
-      </c>
-      <c r="D7" t="n">
-        <v>52</v>
-      </c>
-      <c r="E7" t="n">
-        <v>9</v>
-      </c>
-      <c r="F7" t="n">
-        <v>5922000</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1699000</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>607080194</v>
-      </c>
-      <c r="D8" t="n">
-        <v>2344</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1094</v>
-      </c>
-      <c r="F8" t="n">
-        <v>639881844</v>
-      </c>
-      <c r="G8" t="n">
-        <v>32801650</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>2016252943</v>
-      </c>
-      <c r="D9" t="n">
-        <v>7521</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2973</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2097945393</v>
-      </c>
-      <c r="G9" t="n">
-        <v>81692450</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>172245819</v>
-      </c>
-      <c r="D10" t="n">
-        <v>359</v>
-      </c>
-      <c r="E10" t="n">
-        <v>150</v>
-      </c>
-      <c r="F10" t="n">
-        <v>192575569</v>
-      </c>
-      <c r="G10" t="n">
-        <v>20329750</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E168"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>store</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>net</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>guest</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>tc</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>NCB_9ST</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>446300</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>44949600</v>
-      </c>
-      <c r="D3" t="n">
-        <v>147</v>
-      </c>
-      <c r="E3" t="n">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>NCB_GW</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>818000</v>
-      </c>
-      <c r="D4" t="n">
-        <v>10</v>
-      </c>
-      <c r="E4" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>21733600</v>
-      </c>
-      <c r="D5" t="n">
-        <v>126</v>
-      </c>
-      <c r="E5" t="n">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>99387758</v>
-      </c>
-      <c r="D6" t="n">
-        <v>314</v>
-      </c>
-      <c r="E6" t="n">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>10310488</v>
-      </c>
-      <c r="D7" t="n">
-        <v>17</v>
-      </c>
-      <c r="E7" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-02-02</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>NCB_9ST</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>69000</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-02-02</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>26682950</v>
-      </c>
-      <c r="D9" t="n">
-        <v>116</v>
-      </c>
-      <c r="E9" t="n">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-02-02</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>28472150</v>
-      </c>
-      <c r="D10" t="n">
-        <v>198</v>
-      </c>
-      <c r="E10" t="n">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-02-02</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>2800000</v>
-      </c>
-      <c r="D11" t="n">
-        <v>11</v>
-      </c>
-      <c r="E11" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-02-02</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>30818138</v>
-      </c>
-      <c r="D12" t="n">
-        <v>104</v>
-      </c>
-      <c r="E12" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-02-02</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>9510869</v>
-      </c>
-      <c r="D13" t="n">
-        <v>18</v>
-      </c>
-      <c r="E13" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>45319500</v>
-      </c>
-      <c r="D14" t="n">
-        <v>172</v>
-      </c>
-      <c r="E14" t="n">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>NCB_GW</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>434000</v>
-      </c>
-      <c r="D15" t="n">
-        <v>2</v>
-      </c>
-      <c r="E15" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>30613000</v>
-      </c>
-      <c r="D16" t="n">
-        <v>215</v>
-      </c>
-      <c r="E16" t="n">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>NCB_NDC</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>88500</v>
-      </c>
-      <c r="D17" t="n">
-        <v>2</v>
-      </c>
-      <c r="E17" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>55749352</v>
-      </c>
-      <c r="D18" t="n">
-        <v>172</v>
-      </c>
-      <c r="E18" t="n">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>17550947</v>
-      </c>
-      <c r="D19" t="n">
-        <v>28</v>
-      </c>
-      <c r="E19" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>23863150</v>
-      </c>
-      <c r="D20" t="n">
-        <v>109</v>
-      </c>
-      <c r="E20" t="n">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>NCB_GW</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>1241000</v>
-      </c>
-      <c r="D21" t="n">
-        <v>10</v>
-      </c>
-      <c r="E21" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>30710250</v>
-      </c>
-      <c r="D22" t="n">
-        <v>243</v>
-      </c>
-      <c r="E22" t="n">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>10196350</v>
-      </c>
-      <c r="D23" t="n">
-        <v>44</v>
-      </c>
-      <c r="E23" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>26019974</v>
-      </c>
-      <c r="D24" t="n">
-        <v>120</v>
-      </c>
-      <c r="E24" t="n">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>9300608</v>
-      </c>
-      <c r="D25" t="n">
-        <v>22</v>
-      </c>
-      <c r="E25" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>NCB_9ST</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>726100</v>
-      </c>
-      <c r="D26" t="n">
-        <v>14</v>
-      </c>
-      <c r="E26" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>17016300</v>
-      </c>
-      <c r="D27" t="n">
-        <v>98</v>
-      </c>
-      <c r="E27" t="n">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>NCB_GW</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>118000</v>
-      </c>
-      <c r="D28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>30295200</v>
-      </c>
-      <c r="D29" t="n">
-        <v>229</v>
-      </c>
-      <c r="E29" t="n">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>NCB_NDC</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>59000</v>
-      </c>
-      <c r="D30" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>4413700</v>
-      </c>
-      <c r="D31" t="n">
-        <v>33</v>
-      </c>
-      <c r="E31" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>79722056</v>
-      </c>
-      <c r="D32" t="n">
-        <v>214</v>
-      </c>
-      <c r="E32" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>6626286</v>
-      </c>
-      <c r="D33" t="n">
-        <v>15</v>
-      </c>
-      <c r="E33" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>NCB_9ST</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>207000</v>
-      </c>
-      <c r="D34" t="n">
-        <v>2</v>
-      </c>
-      <c r="E34" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>48523400</v>
-      </c>
-      <c r="D35" t="n">
-        <v>113</v>
-      </c>
-      <c r="E35" t="n">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>NCB_GW</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>157000</v>
-      </c>
-      <c r="D36" t="n">
-        <v>3</v>
-      </c>
-      <c r="E36" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>23532450</v>
-      </c>
-      <c r="D37" t="n">
-        <v>188</v>
-      </c>
-      <c r="E37" t="n">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>151586900</v>
-      </c>
-      <c r="D38" t="n">
-        <v>279</v>
-      </c>
-      <c r="E38" t="n">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>114603862</v>
-      </c>
-      <c r="D39" t="n">
-        <v>228</v>
-      </c>
-      <c r="E39" t="n">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>3234193</v>
-      </c>
-      <c r="D40" t="n">
-        <v>7</v>
-      </c>
-      <c r="E40" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>11888550</v>
-      </c>
-      <c r="D41" t="n">
-        <v>72</v>
-      </c>
-      <c r="E41" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>NCB_GW</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>1375000</v>
-      </c>
-      <c r="D42" t="n">
-        <v>8</v>
-      </c>
-      <c r="E42" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>15896400</v>
-      </c>
-      <c r="D43" t="n">
-        <v>93</v>
-      </c>
-      <c r="E43" t="n">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>5218850</v>
-      </c>
-      <c r="D44" t="n">
-        <v>37</v>
-      </c>
-      <c r="E44" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>67525243</v>
-      </c>
-      <c r="D45" t="n">
-        <v>230</v>
-      </c>
-      <c r="E45" t="n">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>15996935</v>
-      </c>
-      <c r="D46" t="n">
-        <v>31</v>
-      </c>
-      <c r="E46" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>2026-02-08</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>21760200</v>
-      </c>
-      <c r="D47" t="n">
-        <v>104</v>
-      </c>
-      <c r="E47" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>2026-02-08</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>NCB_GW</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>2358000</v>
-      </c>
-      <c r="D48" t="n">
-        <v>15</v>
-      </c>
-      <c r="E48" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>2026-02-08</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>10973100</v>
-      </c>
-      <c r="D49" t="n">
-        <v>67</v>
-      </c>
-      <c r="E49" t="n">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>2026-02-08</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>9908600</v>
-      </c>
-      <c r="D50" t="n">
-        <v>57</v>
-      </c>
-      <c r="E50" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>2026-02-08</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>81013164</v>
-      </c>
-      <c r="D51" t="n">
-        <v>339</v>
-      </c>
-      <c r="E51" t="n">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>2026-02-08</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>6473943</v>
-      </c>
-      <c r="D52" t="n">
-        <v>11</v>
-      </c>
-      <c r="E52" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>23149000</v>
-      </c>
-      <c r="D53" t="n">
-        <v>127</v>
-      </c>
-      <c r="E53" t="n">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>18762300</v>
-      </c>
-      <c r="D54" t="n">
-        <v>148</v>
-      </c>
-      <c r="E54" t="n">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>12827500</v>
-      </c>
-      <c r="D55" t="n">
-        <v>85</v>
-      </c>
-      <c r="E55" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>85365393</v>
-      </c>
-      <c r="D56" t="n">
-        <v>189</v>
-      </c>
-      <c r="E56" t="n">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>423792</v>
-      </c>
-      <c r="D57" t="n">
-        <v>1</v>
-      </c>
-      <c r="E57" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>NCB_9ST</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>108000</v>
-      </c>
-      <c r="D58" t="n">
-        <v>3</v>
-      </c>
-      <c r="E58" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>28378100</v>
-      </c>
-      <c r="D59" t="n">
-        <v>153</v>
-      </c>
-      <c r="E59" t="n">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>NCB_GW</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>589000</v>
-      </c>
-      <c r="D60" t="n">
-        <v>8</v>
-      </c>
-      <c r="E60" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>18494550</v>
-      </c>
-      <c r="D61" t="n">
-        <v>154</v>
-      </c>
-      <c r="E61" t="n">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>NCB_NDC</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>132500</v>
-      </c>
-      <c r="D62" t="n">
-        <v>3</v>
-      </c>
-      <c r="E62" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>12602650</v>
-      </c>
-      <c r="D63" t="n">
-        <v>75</v>
-      </c>
-      <c r="E63" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>77370325</v>
-      </c>
-      <c r="D64" t="n">
-        <v>198</v>
-      </c>
-      <c r="E64" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>8015998</v>
-      </c>
-      <c r="D65" t="n">
-        <v>11</v>
-      </c>
-      <c r="E65" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>37869350</v>
-      </c>
-      <c r="D66" t="n">
-        <v>117</v>
-      </c>
-      <c r="E66" t="n">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>NCB_GW</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>849000</v>
-      </c>
-      <c r="D67" t="n">
-        <v>4</v>
-      </c>
-      <c r="E67" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
-        <v>17931650</v>
-      </c>
-      <c r="D68" t="n">
-        <v>120</v>
-      </c>
-      <c r="E68" t="n">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
-        <v>5180450</v>
-      </c>
-      <c r="D69" t="n">
-        <v>37</v>
-      </c>
-      <c r="E69" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>46644344</v>
-      </c>
-      <c r="D70" t="n">
-        <v>201</v>
-      </c>
-      <c r="E70" t="n">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C71" t="n">
-        <v>7319643</v>
-      </c>
-      <c r="D71" t="n">
-        <v>15</v>
-      </c>
-      <c r="E71" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>2026-02-12</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>NCB_9ST</t>
-        </is>
-      </c>
-      <c r="C72" t="n">
-        <v>162750</v>
-      </c>
-      <c r="D72" t="n">
-        <v>3</v>
-      </c>
-      <c r="E72" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>2026-02-12</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="C73" t="n">
-        <v>245398630</v>
-      </c>
-      <c r="D73" t="n">
-        <v>96</v>
-      </c>
-      <c r="E73" t="n">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>2026-02-12</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>NCB_GW</t>
-        </is>
-      </c>
-      <c r="C74" t="n">
-        <v>884000</v>
-      </c>
-      <c r="D74" t="n">
-        <v>12</v>
-      </c>
-      <c r="E74" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>2026-02-12</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C75" t="n">
-        <v>22861950</v>
-      </c>
-      <c r="D75" t="n">
-        <v>150</v>
-      </c>
-      <c r="E75" t="n">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>2026-02-12</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C76" t="n">
-        <v>96088544</v>
-      </c>
-      <c r="D76" t="n">
-        <v>102</v>
-      </c>
-      <c r="E76" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>2026-02-12</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C77" t="n">
-        <v>54555506</v>
-      </c>
-      <c r="D77" t="n">
-        <v>212</v>
-      </c>
-      <c r="E77" t="n">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>2026-02-12</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C78" t="n">
-        <v>9885078</v>
-      </c>
-      <c r="D78" t="n">
-        <v>25</v>
-      </c>
-      <c r="E78" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="C79" t="n">
-        <v>24040100</v>
-      </c>
-      <c r="D79" t="n">
-        <v>87</v>
-      </c>
-      <c r="E79" t="n">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>NCB_GW</t>
-        </is>
-      </c>
-      <c r="C80" t="n">
-        <v>926000</v>
-      </c>
-      <c r="D80" t="n">
-        <v>8</v>
-      </c>
-      <c r="E80" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C81" t="n">
-        <v>11861450</v>
-      </c>
-      <c r="D81" t="n">
-        <v>89</v>
-      </c>
-      <c r="E81" t="n">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C82" t="n">
-        <v>9553850</v>
-      </c>
-      <c r="D82" t="n">
-        <v>53</v>
-      </c>
-      <c r="E82" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C83" t="n">
-        <v>46291343</v>
-      </c>
-      <c r="D83" t="n">
-        <v>190</v>
-      </c>
-      <c r="E83" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C84" t="n">
-        <v>7708050</v>
-      </c>
-      <c r="D84" t="n">
-        <v>14</v>
-      </c>
-      <c r="E84" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>2026-02-14</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>IFC_SIG</t>
-        </is>
-      </c>
-      <c r="C85" t="n">
-        <v>2884100</v>
-      </c>
-      <c r="D85" t="n">
-        <v>9</v>
-      </c>
-      <c r="E85" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>2026-02-14</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C86" t="n">
-        <v>17504150</v>
-      </c>
-      <c r="D86" t="n">
-        <v>90</v>
-      </c>
-      <c r="E86" t="n">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>2026-02-14</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C87" t="n">
-        <v>19043100</v>
-      </c>
-      <c r="D87" t="n">
-        <v>77</v>
-      </c>
-      <c r="E87" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>2026-02-14</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C88" t="n">
-        <v>119778343</v>
-      </c>
-      <c r="D88" t="n">
-        <v>308</v>
-      </c>
-      <c r="E88" t="n">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>2026-02-14</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C89" t="n">
-        <v>5364513</v>
-      </c>
-      <c r="D89" t="n">
-        <v>10</v>
-      </c>
-      <c r="E89" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>2026-02-15</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>IFC_SIG</t>
-        </is>
-      </c>
-      <c r="C90" t="n">
-        <v>435000</v>
-      </c>
-      <c r="D90" t="n">
-        <v>0</v>
-      </c>
-      <c r="E90" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>2026-02-15</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C91" t="n">
-        <v>11570700</v>
-      </c>
-      <c r="D91" t="n">
-        <v>73</v>
-      </c>
-      <c r="E91" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>2026-02-15</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C92" t="n">
-        <v>13895850</v>
-      </c>
-      <c r="D92" t="n">
-        <v>67</v>
-      </c>
-      <c r="E92" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>2026-02-15</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C93" t="n">
-        <v>63216848</v>
-      </c>
-      <c r="D93" t="n">
-        <v>258</v>
-      </c>
-      <c r="E93" t="n">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>2026-02-15</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C94" t="n">
-        <v>2896689</v>
-      </c>
-      <c r="D94" t="n">
-        <v>6</v>
-      </c>
-      <c r="E94" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>2026-02-16</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>IFC_SIG</t>
-        </is>
-      </c>
-      <c r="C95" t="n">
-        <v>20210400</v>
-      </c>
-      <c r="D95" t="n">
-        <v>44</v>
-      </c>
-      <c r="E95" t="n">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>2026-02-16</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C96" t="n">
-        <v>30971600</v>
-      </c>
-      <c r="D96" t="n">
-        <v>85</v>
-      </c>
-      <c r="E96" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>2026-02-16</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C97" t="n">
-        <v>83527290</v>
-      </c>
-      <c r="D97" t="n">
-        <v>360</v>
-      </c>
-      <c r="E97" t="n">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>2026-02-17</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>IFC_SIG</t>
-        </is>
-      </c>
-      <c r="C98" t="n">
-        <v>14136500</v>
-      </c>
-      <c r="D98" t="n">
-        <v>133</v>
-      </c>
-      <c r="E98" t="n">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>2026-02-17</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C99" t="n">
-        <v>27657000</v>
-      </c>
-      <c r="D99" t="n">
-        <v>146</v>
-      </c>
-      <c r="E99" t="n">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>2026-02-17</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C100" t="n">
-        <v>127769849</v>
-      </c>
-      <c r="D100" t="n">
-        <v>593</v>
-      </c>
-      <c r="E100" t="n">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>2026-02-18</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>IFC_SIG</t>
-        </is>
-      </c>
-      <c r="C101" t="n">
-        <v>13011000</v>
-      </c>
-      <c r="D101" t="n">
-        <v>139</v>
-      </c>
-      <c r="E101" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>2026-02-18</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C102" t="n">
-        <v>25685500</v>
-      </c>
-      <c r="D102" t="n">
-        <v>147</v>
-      </c>
-      <c r="E102" t="n">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>2026-02-18</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C103" t="n">
-        <v>116650290</v>
-      </c>
-      <c r="D103" t="n">
-        <v>544</v>
-      </c>
-      <c r="E103" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>IFC_SIG</t>
-        </is>
-      </c>
-      <c r="C104" t="n">
-        <v>9719000</v>
-      </c>
-      <c r="D104" t="n">
-        <v>94</v>
-      </c>
-      <c r="E104" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C105" t="n">
-        <v>20724000</v>
-      </c>
-      <c r="D105" t="n">
-        <v>117</v>
-      </c>
-      <c r="E105" t="n">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C106" t="n">
-        <v>126522372</v>
-      </c>
-      <c r="D106" t="n">
-        <v>564</v>
-      </c>
-      <c r="E106" t="n">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>IFC_SIG</t>
-        </is>
-      </c>
-      <c r="C107" t="n">
-        <v>9444000</v>
-      </c>
-      <c r="D107" t="n">
-        <v>95</v>
-      </c>
-      <c r="E107" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C108" t="n">
-        <v>18169000</v>
-      </c>
-      <c r="D108" t="n">
-        <v>122</v>
-      </c>
-      <c r="E108" t="n">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C109" t="n">
-        <v>88939862</v>
-      </c>
-      <c r="D109" t="n">
-        <v>409</v>
-      </c>
-      <c r="E109" t="n">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>2026-02-21</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>IFC_SIG</t>
-        </is>
-      </c>
-      <c r="C110" t="n">
-        <v>2201000</v>
-      </c>
-      <c r="D110" t="n">
-        <v>20</v>
-      </c>
-      <c r="E110" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>2026-02-21</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="C111" t="n">
-        <v>20559000</v>
-      </c>
-      <c r="D111" t="n">
-        <v>127</v>
-      </c>
-      <c r="E111" t="n">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>2026-02-21</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C112" t="n">
-        <v>5065000</v>
-      </c>
-      <c r="D112" t="n">
-        <v>25</v>
-      </c>
-      <c r="E112" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>2026-02-21</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C113" t="n">
-        <v>25486400</v>
-      </c>
-      <c r="D113" t="n">
-        <v>138</v>
-      </c>
-      <c r="E113" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>2026-02-21</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C114" t="n">
-        <v>101744461</v>
-      </c>
-      <c r="D114" t="n">
-        <v>477</v>
-      </c>
-      <c r="E114" t="n">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>2026-02-21</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C115" t="n">
-        <v>7340204</v>
-      </c>
-      <c r="D115" t="n">
-        <v>19</v>
-      </c>
-      <c r="E115" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>IFC_SIG</t>
-        </is>
-      </c>
-      <c r="C116" t="n">
-        <v>1884000</v>
-      </c>
-      <c r="D116" t="n">
-        <v>17</v>
-      </c>
-      <c r="E116" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="C117" t="n">
-        <v>27563800</v>
-      </c>
-      <c r="D117" t="n">
-        <v>141</v>
-      </c>
-      <c r="E117" t="n">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C118" t="n">
-        <v>11443400</v>
-      </c>
-      <c r="D118" t="n">
-        <v>63</v>
-      </c>
-      <c r="E118" t="n">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C119" t="n">
-        <v>21849650</v>
-      </c>
-      <c r="D119" t="n">
-        <v>119</v>
-      </c>
-      <c r="E119" t="n">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C120" t="n">
-        <v>72709573</v>
-      </c>
-      <c r="D120" t="n">
-        <v>331</v>
-      </c>
-      <c r="E120" t="n">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C121" t="n">
-        <v>5162648</v>
-      </c>
-      <c r="D121" t="n">
-        <v>9</v>
-      </c>
-      <c r="E121" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>IFC_SIG</t>
-        </is>
-      </c>
-      <c r="C122" t="n">
-        <v>901200</v>
-      </c>
-      <c r="D122" t="n">
-        <v>11</v>
-      </c>
-      <c r="E122" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>NCB_9ST</t>
-        </is>
-      </c>
-      <c r="C123" t="n">
-        <v>265500</v>
-      </c>
-      <c r="D123" t="n">
-        <v>6</v>
-      </c>
-      <c r="E123" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="C124" t="n">
-        <v>22258100</v>
-      </c>
-      <c r="D124" t="n">
-        <v>97</v>
-      </c>
-      <c r="E124" t="n">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C125" t="n">
-        <v>22545150</v>
-      </c>
-      <c r="D125" t="n">
-        <v>180</v>
-      </c>
-      <c r="E125" t="n">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C126" t="n">
-        <v>10548300</v>
-      </c>
-      <c r="D126" t="n">
-        <v>95</v>
-      </c>
-      <c r="E126" t="n">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C127" t="n">
-        <v>40174163</v>
-      </c>
-      <c r="D127" t="n">
-        <v>198</v>
-      </c>
-      <c r="E127" t="n">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C128" t="n">
-        <v>7396993</v>
-      </c>
-      <c r="D128" t="n">
-        <v>15</v>
-      </c>
-      <c r="E128" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>IFC_SIG</t>
-        </is>
-      </c>
-      <c r="C129" t="n">
-        <v>740700</v>
-      </c>
-      <c r="D129" t="n">
-        <v>8</v>
-      </c>
-      <c r="E129" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>NCB_9ST</t>
-        </is>
-      </c>
-      <c r="C130" t="n">
-        <v>88500</v>
-      </c>
-      <c r="D130" t="n">
-        <v>3</v>
-      </c>
-      <c r="E130" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="C131" t="n">
-        <v>29497550</v>
-      </c>
-      <c r="D131" t="n">
-        <v>127</v>
-      </c>
-      <c r="E131" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>NCB_GW</t>
-        </is>
-      </c>
-      <c r="C132" t="n">
-        <v>285000</v>
-      </c>
-      <c r="D132" t="n">
-        <v>3</v>
-      </c>
-      <c r="E132" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C133" t="n">
-        <v>17880450</v>
-      </c>
-      <c r="D133" t="n">
-        <v>140</v>
-      </c>
-      <c r="E133" t="n">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C134" t="n">
-        <v>14701400</v>
-      </c>
-      <c r="D134" t="n">
-        <v>114</v>
-      </c>
-      <c r="E134" t="n">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C135" t="n">
-        <v>41649428</v>
-      </c>
-      <c r="D135" t="n">
-        <v>161</v>
-      </c>
-      <c r="E135" t="n">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C136" t="n">
-        <v>14366112</v>
-      </c>
-      <c r="D136" t="n">
-        <v>32</v>
-      </c>
-      <c r="E136" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>IFC_SIG</t>
-        </is>
-      </c>
-      <c r="C137" t="n">
-        <v>2001200</v>
-      </c>
-      <c r="D137" t="n">
-        <v>8</v>
-      </c>
-      <c r="E137" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>NCB_9ST</t>
-        </is>
-      </c>
-      <c r="C138" t="n">
-        <v>59000</v>
-      </c>
-      <c r="D138" t="n">
-        <v>1</v>
-      </c>
-      <c r="E138" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="C139" t="n">
-        <v>24422550</v>
-      </c>
-      <c r="D139" t="n">
-        <v>113</v>
-      </c>
-      <c r="E139" t="n">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>NCB_GW</t>
-        </is>
-      </c>
-      <c r="C140" t="n">
-        <v>205000</v>
-      </c>
-      <c r="D140" t="n">
-        <v>3</v>
-      </c>
-      <c r="E140" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C141" t="n">
-        <v>20358400</v>
-      </c>
-      <c r="D141" t="n">
-        <v>147</v>
-      </c>
-      <c r="E141" t="n">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C142" t="n">
-        <v>13035400</v>
-      </c>
-      <c r="D142" t="n">
-        <v>72</v>
-      </c>
-      <c r="E142" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C143" t="n">
-        <v>32036744</v>
-      </c>
-      <c r="D143" t="n">
-        <v>139</v>
-      </c>
-      <c r="E143" t="n">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C144" t="n">
-        <v>10478168</v>
-      </c>
-      <c r="D144" t="n">
-        <v>31</v>
-      </c>
-      <c r="E144" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>IFC_SIG</t>
-        </is>
-      </c>
-      <c r="C145" t="n">
-        <v>1341400</v>
-      </c>
-      <c r="D145" t="n">
-        <v>22</v>
-      </c>
-      <c r="E145" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="C146" t="n">
-        <v>18176900</v>
-      </c>
-      <c r="D146" t="n">
-        <v>87</v>
-      </c>
-      <c r="E146" t="n">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>NCB_GW</t>
-        </is>
-      </c>
-      <c r="C147" t="n">
-        <v>654000</v>
-      </c>
-      <c r="D147" t="n">
-        <v>3</v>
-      </c>
-      <c r="E147" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C148" t="n">
-        <v>20145150</v>
-      </c>
-      <c r="D148" t="n">
-        <v>137</v>
-      </c>
-      <c r="E148" t="n">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C149" t="n">
-        <v>17245600</v>
-      </c>
-      <c r="D149" t="n">
-        <v>82</v>
-      </c>
-      <c r="E149" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C150" t="n">
-        <v>36075966</v>
-      </c>
-      <c r="D150" t="n">
-        <v>144</v>
-      </c>
-      <c r="E150" t="n">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C151" t="n">
-        <v>439992</v>
-      </c>
-      <c r="D151" t="n">
-        <v>2</v>
-      </c>
-      <c r="E151" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>IFC_SIG</t>
-        </is>
-      </c>
-      <c r="C152" t="n">
-        <v>1583100</v>
-      </c>
-      <c r="D152" t="n">
-        <v>9</v>
-      </c>
-      <c r="E152" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>NCB_9ST</t>
-        </is>
-      </c>
-      <c r="C153" t="n">
-        <v>1343250</v>
-      </c>
-      <c r="D153" t="n">
-        <v>27</v>
-      </c>
-      <c r="E153" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="C154" t="n">
-        <v>28587800</v>
-      </c>
-      <c r="D154" t="n">
-        <v>150</v>
-      </c>
-      <c r="E154" t="n">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>NCB_GW</t>
-        </is>
-      </c>
-      <c r="C155" t="n">
-        <v>365000</v>
-      </c>
-      <c r="D155" t="n">
-        <v>3</v>
-      </c>
-      <c r="E155" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C156" t="n">
-        <v>27607700</v>
-      </c>
-      <c r="D156" t="n">
-        <v>175</v>
-      </c>
-      <c r="E156" t="n">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>NCB_NDC</t>
-        </is>
-      </c>
-      <c r="C157" t="n">
-        <v>3943000</v>
-      </c>
-      <c r="D157" t="n">
-        <v>46</v>
-      </c>
-      <c r="E157" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C158" t="n">
-        <v>8967100</v>
-      </c>
-      <c r="D158" t="n">
-        <v>74</v>
-      </c>
-      <c r="E158" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C159" t="n">
-        <v>46824918</v>
-      </c>
-      <c r="D159" t="n">
-        <v>140</v>
-      </c>
-      <c r="E159" t="n">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C160" t="n">
-        <v>1044767</v>
-      </c>
-      <c r="D160" t="n">
-        <v>4</v>
-      </c>
-      <c r="E160" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>IFC_SIG</t>
-        </is>
-      </c>
-      <c r="C161" t="n">
-        <v>400900</v>
-      </c>
-      <c r="D161" t="n">
-        <v>3</v>
-      </c>
-      <c r="E161" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>NCB_9ST</t>
-        </is>
-      </c>
-      <c r="C162" t="n">
-        <v>151950</v>
-      </c>
-      <c r="D162" t="n">
-        <v>3</v>
-      </c>
-      <c r="E162" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="C163" t="n">
-        <v>29186400</v>
-      </c>
-      <c r="D163" t="n">
-        <v>153</v>
-      </c>
-      <c r="E163" t="n">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>NCB_GW</t>
-        </is>
-      </c>
-      <c r="C164" t="n">
-        <v>1875000</v>
-      </c>
-      <c r="D164" t="n">
-        <v>16</v>
-      </c>
-      <c r="E164" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C165" t="n">
-        <v>16239500</v>
-      </c>
-      <c r="D165" t="n">
-        <v>97</v>
-      </c>
-      <c r="E165" t="n">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C166" t="n">
-        <v>18722900</v>
-      </c>
-      <c r="D166" t="n">
-        <v>76</v>
-      </c>
-      <c r="E166" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C167" t="n">
-        <v>53566378</v>
-      </c>
-      <c r="D167" t="n">
-        <v>184</v>
-      </c>
-      <c r="E167" t="n">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C168" t="n">
-        <v>5398903</v>
-      </c>
-      <c r="D168" t="n">
-        <v>16</v>
-      </c>
-      <c r="E168" t="n">
-        <v>5</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:O2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="9" customWidth="1" min="14" max="14"/>
-    <col width="9" customWidth="1" min="15" max="15"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>month</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>spend_total</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>spend_first</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>spend_second</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>spend_third</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>mem_rev</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>mem_disc</t>
-        </is>
-      </c>
-      <c r="H1" s="4" t="inlineStr">
-        <is>
-          <t>mem_inv</t>
-        </is>
-      </c>
-      <c r="I1" s="4" t="inlineStr">
-        <is>
-          <t>v_issued</t>
-        </is>
-      </c>
-      <c r="J1" s="4" t="inlineStr">
-        <is>
-          <t>v_used</t>
-        </is>
-      </c>
-      <c r="K1" s="4" t="inlineStr">
-        <is>
-          <t>v_rev_before</t>
-        </is>
-      </c>
-      <c r="L1" s="4" t="inlineStr">
-        <is>
-          <t>v_rev_after</t>
-        </is>
-      </c>
-      <c r="M1" s="4" t="inlineStr">
-        <is>
-          <t>v_disc</t>
-        </is>
-      </c>
-      <c r="N1" s="4" t="inlineStr">
-        <is>
-          <t>src</t>
-        </is>
-      </c>
-      <c r="O1" s="4" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>553</v>
-      </c>
-      <c r="C2" t="n">
-        <v>50</v>
-      </c>
-      <c r="D2" t="n">
-        <v>35</v>
-      </c>
-      <c r="E2" t="n">
-        <v>468</v>
-      </c>
-      <c r="F2" t="n">
-        <v>213385066</v>
-      </c>
-      <c r="G2" t="n">
-        <v>118222750</v>
-      </c>
-      <c r="H2" t="n">
-        <v>553</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>S28+S29</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -99294,34 +99512,42 @@
   </sheetPr>
   <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>month</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>rev</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>rev_cov</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>sku</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>sku_cov</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>pct</t>
         </is>
@@ -99362,29 +99588,36 @@
   </sheetPr>
   <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>used</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>rev</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>disc</t>
         </is>
@@ -99480,6 +99713,196 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="9" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>spend_total</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>spend_first</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>spend_second</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>spend_third</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>mem_rev</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>mem_disc</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>mem_inv</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>v_issued</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>v_used</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>v_rev_before</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>v_rev_after</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>v_disc</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>src</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>553</v>
+      </c>
+      <c r="C2" t="n">
+        <v>50</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35</v>
+      </c>
+      <c r="E2" t="n">
+        <v>468</v>
+      </c>
+      <c r="F2" t="n">
+        <v>213385066</v>
+      </c>
+      <c r="G2" t="n">
+        <v>118222750</v>
+      </c>
+      <c r="H2" t="n">
+        <v>553</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>S28+S29</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>hit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>142</v>
+      </c>
+      <c r="C2" t="n">
+        <v>141</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -99674,51 +100097,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C1" s="5" t="inlineStr">
-        <is>
-          <t>hit</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>142</v>
-      </c>
-      <c r="C2" t="n">
-        <v>141</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -99770,7 +100149,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -100760,7 +101139,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -101176,7 +101555,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -101234,7 +101613,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -101650,373 +102029,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>month</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>store</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>net</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>net_item</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>net_bill</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>tc</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>tc_bill</t>
-        </is>
-      </c>
-      <c r="H1" s="4" t="inlineStr">
-        <is>
-          <t>guest</t>
-        </is>
-      </c>
-      <c r="I1" s="4" t="inlineStr">
-        <is>
-          <t>guest_bill</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>IFC_SIG</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>80893500</v>
-      </c>
-      <c r="D2" t="n">
-        <v>80893500</v>
-      </c>
-      <c r="E2" t="n">
-        <v>80893500</v>
-      </c>
-      <c r="F2" t="n">
-        <v>348</v>
-      </c>
-      <c r="G2" t="n">
-        <v>348</v>
-      </c>
-      <c r="H2" t="n">
-        <v>612</v>
-      </c>
-      <c r="I2" t="n">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>NCB_9ST</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>3627350</v>
-      </c>
-      <c r="D3" t="n">
-        <v>3627350</v>
-      </c>
-      <c r="E3" t="n">
-        <v>3627350</v>
-      </c>
-      <c r="F3" t="n">
-        <v>20</v>
-      </c>
-      <c r="G3" t="n">
-        <v>20</v>
-      </c>
-      <c r="H3" t="n">
-        <v>65</v>
-      </c>
-      <c r="I3" t="n">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>799090930</v>
-      </c>
-      <c r="D4" t="n">
-        <v>799090930</v>
-      </c>
-      <c r="E4" t="n">
-        <v>799090930</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1417</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1417</v>
-      </c>
-      <c r="H4" t="n">
-        <v>2506</v>
-      </c>
-      <c r="I4" t="n">
-        <v>2506</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>NCB_GW</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>13133000</v>
-      </c>
-      <c r="D5" t="n">
-        <v>13133000</v>
-      </c>
-      <c r="E5" t="n">
-        <v>13133000</v>
-      </c>
-      <c r="F5" t="n">
-        <v>73</v>
-      </c>
-      <c r="G5" t="n">
-        <v>73</v>
-      </c>
-      <c r="H5" t="n">
-        <v>109</v>
-      </c>
-      <c r="I5" t="n">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>452497650</v>
-      </c>
-      <c r="D6" t="n">
-        <v>452497650</v>
-      </c>
-      <c r="E6" t="n">
-        <v>452497650</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1933</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1933</v>
-      </c>
-      <c r="H6" t="n">
-        <v>3147</v>
-      </c>
-      <c r="I6" t="n">
-        <v>3147</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>NCB_NDC</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>4223000</v>
-      </c>
-      <c r="D7" t="n">
-        <v>4223000</v>
-      </c>
-      <c r="E7" t="n">
-        <v>4223000</v>
-      </c>
-      <c r="F7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G7" t="n">
-        <v>9</v>
-      </c>
-      <c r="H7" t="n">
-        <v>52</v>
-      </c>
-      <c r="I7" t="n">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>607080194</v>
-      </c>
-      <c r="D8" t="n">
-        <v>607080194</v>
-      </c>
-      <c r="E8" t="n">
-        <v>607080194</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1094</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1094</v>
-      </c>
-      <c r="H8" t="n">
-        <v>2344</v>
-      </c>
-      <c r="I8" t="n">
-        <v>2344</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>2016252943</v>
-      </c>
-      <c r="D9" t="n">
-        <v>2016252941</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2016252943</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2973</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2973</v>
-      </c>
-      <c r="H9" t="n">
-        <v>7521</v>
-      </c>
-      <c r="I9" t="n">
-        <v>7521</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>172245819</v>
-      </c>
-      <c r="D10" t="n">
-        <v>172245820</v>
-      </c>
-      <c r="E10" t="n">
-        <v>172245819</v>
-      </c>
-      <c r="F10" t="n">
-        <v>150</v>
-      </c>
-      <c r="G10" t="n">
-        <v>150</v>
-      </c>
-      <c r="H10" t="n">
-        <v>359</v>
-      </c>
-      <c r="I10" t="n">
-        <v>359</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/data_input/monthly/2026-02.xlsx
+++ b/data_input/monthly/2026-02.xlsx
@@ -46,7 +46,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -62,8 +62,12 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00F3F2EE"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -80,6 +84,11 @@
         <fgColor rgb="FFF2EFE6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F1F26"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -93,7 +102,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -105,6 +114,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -60546,6 +60556,11 @@
           <t>COMBO VIETNAMESE CORNER &amp; COFFEE</t>
         </is>
       </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F121" t="inlineStr">
         <is>
           <t>Combo</t>
@@ -63831,6 +63846,11 @@
           <t>AFTERNOON TEA SET (359K)</t>
         </is>
       </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F203" t="inlineStr">
         <is>
           <t>Combo</t>
@@ -64461,6 +64481,11 @@
           <t>COMBO DUO PASTRY &amp; COFFEE (149K)</t>
         </is>
       </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F219" t="inlineStr">
         <is>
           <t>Combo</t>
@@ -64494,6 +64519,11 @@
           <t>COMBO DUO PASTRY &amp; COFFEE (119K)</t>
         </is>
       </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F220" t="inlineStr">
         <is>
           <t>Combo</t>
@@ -66802,6 +66832,11 @@
           <t>Bánh Sừng Bò Kẹp Dăm Bông, Phô Mai - Ham Cheese Croissant</t>
         </is>
       </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F280" t="inlineStr">
         <is>
           <t>UnCategory</t>
@@ -67943,6 +67978,11 @@
           <t>COMBO VIETNAMESE CORNER &amp; COFFEE</t>
         </is>
       </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F310" t="inlineStr">
         <is>
           <t>Combo</t>
@@ -69668,6 +69708,11 @@
           <t>COMBO DUO PASTRY &amp; COFFEE (119K)</t>
         </is>
       </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F353" t="inlineStr">
         <is>
           <t>Combo</t>
@@ -72321,6 +72366,11 @@
           <t>COMBO DUO PASTRY &amp; COFFEE (149K)</t>
         </is>
       </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F419" t="inlineStr">
         <is>
           <t>Combo</t>
@@ -72740,6 +72790,11 @@
           <t>COMBO LUNCH - 179k</t>
         </is>
       </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F430" t="inlineStr">
         <is>
           <t>Combo</t>
@@ -73703,6 +73758,11 @@
           <t>Bánh Sừng Bò Kẹp Dăm Bông, Phô Mai - Ham Cheese Croissant</t>
         </is>
       </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F455" t="inlineStr">
         <is>
           <t>UnCategory</t>
@@ -79907,6 +79967,11 @@
           <t>SET MENU A</t>
         </is>
       </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F612" t="inlineStr">
         <is>
           <t>Combo</t>
@@ -80376,6 +80441,11 @@
           <t>SET MENU C</t>
         </is>
       </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F624" t="inlineStr">
         <is>
           <t>Combo</t>
@@ -81196,6 +81266,11 @@
           <t>SET MENU D</t>
         </is>
       </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F645" t="inlineStr">
         <is>
           <t>Combo</t>
@@ -82294,6 +82369,11 @@
           <t>SET VALENTINE NOIRE DINING</t>
         </is>
       </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F673" t="inlineStr">
         <is>
           <t>Combo</t>
@@ -88488,6 +88568,11 @@
       <c r="D835" t="inlineStr">
         <is>
           <t>Combo Premium</t>
+        </is>
+      </c>
+      <c r="E835" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="F835" t="inlineStr">
@@ -98986,6 +99071,11 @@
           <t>msg</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>booking</t>
+        </is>
+      </c>
       <c r="L2" t="n">
         <v>57</v>
       </c>
@@ -99512,42 +99602,34 @@
   </sheetPr>
   <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>month</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>rev</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>rev_cov</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>sku</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>sku_cov</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>pct</t>
         </is>
@@ -99588,36 +99670,29 @@
   </sheetPr>
   <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>used</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>rev</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>disc</t>
         </is>
@@ -99861,24 +99936,19 @@
   </sheetPr>
   <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>hit</t>
         </is>

--- a/data_input/monthly/2026-02.xlsx
+++ b/data_input/monthly/2026-02.xlsx
@@ -8,26 +8,26 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_HƯỚNG DẪN" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="booking" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="crm_month" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="crm_store" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="member" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daypart" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="channel" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="identify" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="nature" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="recon" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="fact_promo_day" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="fact_lto_line" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="fact_partner" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_party" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="heat" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="payment" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="product_month" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="store_month" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="coverage" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dim_target" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="store_month" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="coverage" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dim_target" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="booking" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="crm_month" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="crm_store" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="member" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daypart" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="channel" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="identify" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="nature" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="recon" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="fact_promo_day" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="fact_lto_line" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="fact_partner" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_party" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="heat" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="payment" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="product_month" sheetId="21" state="visible" r:id="rId21"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oa" sheetId="22" state="visible" r:id="rId22"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oa_daily" sheetId="23" state="visible" r:id="rId23"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ads_month" sheetId="24" state="visible" r:id="rId24"/>
@@ -660,308 +660,308 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   booking                    8 dòng   bắt buộc: month, status</t>
+          <t xml:space="preserve">   store_month                9 dòng   bắt buộc: month, store, net, guest, tc</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Booking tiệc &amp; sự kiện — gộp theo tháng NHẬN LEAD (month) × tháng DIỄN RA (ev_month) × cửa hàng × phân khúc × loại × nguồn × trạng thái. month = Inquiry Date → Input Date → (thiếu cả hai) ngày sự kiện, khi đó inq_est đếm số lead bị ước. seg ∈ event|table, stage ∈ won|open|lost — luật ở $booking. exp chỉ cộng ô có số (exp_n lead); ô trống/TBA KHÔNG tính là 0. closed_n = số lead Confirmed đã nhập Closed Revenue.</t>
+          <t xml:space="preserve">                                  XƯƠNG SỐNG của hệ thống. net = doanh thu thuần · guest = số khách · tc = số hoá đơn.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   crm_month                  1 dòng   bắt buộc: month</t>
+          <t xml:space="preserve">                                  loader tự tính: ta, aov, brand, tier</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  CRM theo THÁNG toàn chuỗi (S27 file CRM tháng · S28 lịch sử T1–T8 · S29 CSV). spend_* = lượt chi tiêu của member theo lần (lần đầu / lần 2 / từ 3 lần); mem_rev = doanh thu thành viên SAU giảm; mem_inv = hoá đơn thành viên. Ô trống = nguồn không có (vd. T8 thiếu cơ cấu lượt) — KHÔNG phải 0. v_* = báo cáo voucher của CRM iPOS (khác nhật ký S11: bao mọi loại voucher).</t>
+          <t xml:space="preserve">   daily                    167 dòng   bắt buộc: date, store, net</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   crm_store                  7 dòng   bắt buộc: month, store</t>
+          <t xml:space="preserve">                                  Doanh thu theo NGÀY × cửa hàng. Ngày phải nằm trong tháng của file.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  CRM theo THÁNG × CỬA HÀNG (mã dim_store). mem_* từ CSV doanh thu thành viên / sheet 2·4 file CRM; spend_* chỉ có tháng có file CRM tháng; v_* chỉ T8 (lịch sử) và tháng có sheet voucher hợp lệ.</t>
+          <t xml:space="preserve">   coverage                   1 dòng   bắt buộc: month</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   member                     1 dòng   bắt buộc: month</t>
+          <t xml:space="preserve">                                  Số ngày THỰC CÓ dữ liệu — nhận diện tháng chưa trọn kỳ. Không khai thì loader suy từ daily.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Member đăng ký mới &amp; OA follow mới theo tháng (số toàn chuỗi).</t>
+          <t xml:space="preserve">                                  loader tự tính: partial</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   daypart                   36 dòng   bắt buộc: month, store, daypart</t>
+          <t xml:space="preserve">   dim_target                 4 dòng   bắt buộc: month, store, target</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Doanh thu theo khung giờ trong ngày × cửa hàng (bộ lọc brand / phạm vi ở M3 cần cột store).</t>
+          <t xml:space="preserve">                                  Target doanh thu theo cửa hàng × tháng. Được phép khai cả tháng tương lai.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   channel                   16 dòng   bắt buộc: month, store, channel</t>
+          <t xml:space="preserve">   booking                    8 dòng   bắt buộc: month, status</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Doanh thu theo kênh bán (tại chỗ, mang về, giao hàng…) × cửa hàng.</t>
+          <t xml:space="preserve">                                  Booking tiệc &amp; sự kiện — gộp theo tháng NHẬN LEAD (month) × tháng DIỄN RA (ev_month) × cửa hàng × phân khúc × loại × nguồn × trạng thái. month = Inquiry Date → Input Date → (thiếu cả hai) ngày sự kiện, khi đó inq_est đếm số lead bị ước. seg ∈ event|table, stage ∈ won|open|lost — luật ở $booking. exp chỉ cộng ô có số (exp_n lead); ô trống/TBA KHÔNG tính là 0. closed_n = số lead Confirmed đã nhập Closed Revenue.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   identify                   1 dòng   bắt buộc: month, bills, id_bills</t>
+          <t xml:space="preserve">   crm_month                  1 dòng   bắt buộc: month</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Tỷ lệ hoá đơn nhận diện được khách — trần trên của mọi phép quy doanh thu về khách. `items` = số dòng món đã xử lý trong tháng, nuôi thẻ đếm ở tab D1.</t>
+          <t xml:space="preserve">                                  CRM theo THÁNG toàn chuỗi (S27 file CRM tháng · S28 lịch sử T1–T8 · S29 CSV). spend_* = lượt chi tiêu của member theo lần (lần đầu / lần 2 / từ 3 lần); mem_rev = doanh thu thành viên SAU giảm; mem_inv = hoá đơn thành viên. Ô trống = nguồn không có (vd. T8 thiếu cơ cấu lượt) — KHÔNG phải 0. v_* = báo cáo voucher của CRM iPOS (khác nhật ký S11: bao mọi loại voucher).</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  loader tự tính: rate</t>
+          <t xml:space="preserve">   crm_store                  7 dòng   bắt buộc: month, store</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   nature                    14 dòng   bắt buộc: month, nature, brand, rev</t>
+          <t xml:space="preserve">                                  CRM theo THÁNG × CỬA HÀNG (mã dim_store). mem_* từ CSV doanh thu thành viên / sheet 2·4 file CRM; spend_* chỉ có tháng có file CRM tháng; v_* chỉ T8 (lịch sử) và tháng có sheet voucher hợp lệ.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Bản chất chương trình khuyến mãi. nature ∈ COMMERCIAL|INTERNAL|PARTNER|LOYALTY. `rev` = doanh thu chạm (cấp dòng món, THÀNH TIỀN) · `disc` = chiết khấu thật (cấp HOÁ ĐƠN) — hai base khác nhau, xem fact_promo_day.</t>
+          <t xml:space="preserve">   member                     1 dòng   bắt buộc: month</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   recon                      9 dòng   bắt buộc: month, store, net</t>
+          <t xml:space="preserve">                                  Member đăng ký mới &amp; OA follow mới theo tháng (số toàn chuỗi).</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Đối soát ba tầng: bảng tháng ↔ bảng món ↔ bảng hoá đơn.</t>
+          <t xml:space="preserve">   daypart                   36 dòng   bắt buộc: month, store, daypart</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  loader tự tính: d_bill</t>
+          <t xml:space="preserve">                                  Doanh thu theo khung giờ trong ngày × cửa hàng (bộ lọc brand / phạm vi ở M3 cần cột store).</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   fact_promo_day           559 dòng   bắt buộc: date, store, name_pos</t>
+          <t xml:space="preserve">   channel                   16 dòng   bắt buộc: month, store, channel</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  CTKM theo NGÀY × cửa hàng — nền của M7.2. `disc` = Giảm giá + Chiết khấu ở cấp HOÁ ĐƠN · `voucher` = Phiếu GG, để riêng vì voucher là phương thức thanh toán chứ không phải giảm giá. `net` = Tổng tiền (cùng base với daily/store_month — kỳ nền của M7.2 lấy từ đó). `rev`/`items` từ lane dòng món theo THÀNH TIỀN — base khác `net`, đừng cộng chung. `name_pos` giữ nguyên văn, chuẩn hoá ở dim_campaign.</t>
+          <t xml:space="preserve">                                  Doanh thu theo kênh bán (tại chỗ, mang về, giao hàng…) × cửa hàng.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   fact_lto_line            120 dòng   bắt buộc: date, store, bill, item_code</t>
+          <t xml:space="preserve">   identify                   1 dòng   bắt buộc: month, bills, id_bills</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Dòng món thuộc nhóm LTO (Nhóm món chứa $campaign.lto_group_rx) gắn TỔNG hoá đơn chứa nó — nền doanh thu CTKM của chương trình LTO chạy theo món. `bill_net` = Tổng tiền cả hoá đơn (gồm món khác) · `line_rev` = Thành tiền riêng dòng LTO. Một hoá đơn có nhiều dòng LTO → cộng bill_net theo hoá đơn DUY NHẤT.</t>
+          <t xml:space="preserve">                                  Tỷ lệ hoá đơn nhận diện được khách — trần trên của mọi phép quy doanh thu về khách. `items` = số dòng món đã xử lý trong tháng, nuôi thẻ đếm ở tab D1.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   fact_partner               3 dòng   bắt buộc: store, partner, basis</t>
+          <t xml:space="preserve">                                  loader tự tính: rate</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Hoá đơn ĐỐI TÁC theo tháng × cửa hàng × đối tác — nền chung của M7 (thẻ Đối tác) và M9. Mỗi hoá đơn thuộc MỘT đối tác, nhận theo thứ tự `basis`: CTKM (tên CTKM khớp luật PARTNER, mã ở $promo_nature.rules[].partner) → NGUON (cột Nguồn là nền tảng) → PTTT (trả qua ví nền tảng). `camp` = tên CTKM nguyên văn (có thể rỗng). `net` = Tổng tiền (cùng base store_month) · `gross` = trước giảm giá · `disc` = Giảm giá + Chiết khấu · `voucher` = Phiếu GG · `commission` = cột Hoa hồng của POS.</t>
+          <t xml:space="preserve">   nature                    14 dòng   bắt buộc: month, nature, brand, rev</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   daily_party               38 dòng   bắt buộc: date, store, net, tc</t>
+          <t xml:space="preserve">                                  Bản chất chương trình khuyến mãi. nature ∈ COMMERCIAL|INTERNAL|PARTNER|LOYALTY. `rev` = doanh thu chạm (cấp dòng món, THÀNH TIỀN) · `disc` = chiết khấu thật (cấp HOÁ ĐƠN) — hai base khác nhau, xem fact_promo_day.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Phần KHÁCH TIỆC của `daily`: chỉ các hoá đơn có Số khách ≥ $guest_segment.party_min_guests, gộp theo NGÀY × cửa hàng. ETL tự sinh từ bảng kê hoá đơn (S02). Khách lẻ = daily − daily_party.</t>
+          <t xml:space="preserve">   recon                      9 dòng   bắt buộc: month, store, net</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   heat                     636 dòng   bắt buộc: month, store, dow, hour_in</t>
+          <t xml:space="preserve">                                  Đối soát ba tầng: bảng tháng ↔ bảng món ↔ bảng hoá đơn.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Ma trận giờ vào × thứ theo tháng × cửa hàng. dow: 0 = Thứ 2 … 6 = Chủ nhật.</t>
+          <t xml:space="preserve">                                  loader tự tính: d_bill</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   payment                  120 dòng   bắt buộc: month, store, pttt</t>
+          <t xml:space="preserve">   fact_promo_day           559 dòng   bắt buộc: date, store, name_pos</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Doanh thu theo phương thức thanh toán × tháng × cửa hàng.</t>
+          <t xml:space="preserve">                                  CTKM theo NGÀY × cửa hàng — nền của M7.2. `disc` = Giảm giá + Chiết khấu ở cấp HOÁ ĐƠN · `voucher` = Phiếu GG, để riêng vì voucher là phương thức thanh toán chứ không phải giảm giá. `net` = Tổng tiền (cùng base với daily/store_month — kỳ nền của M7.2 lấy từ đó). `rev`/`items` từ lane dòng món theo THÀNH TIỀN — base khác `net`, đừng cộng chung. `name_pos` giữ nguyên văn, chuẩn hoá ở dim_campaign.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   product_month            953 dòng   bắt buộc: store, ma, qty, rev</t>
+          <t xml:space="preserve">   fact_lto_line            120 dòng   bắt buộc: date, store, bill, item_code</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Bán món theo tháng × cửa hàng (POS báo cáo bán hàng). rev = Thành tiền (trước phí DV &amp; VAT). cogs = giá vốn BOM × số lượng — TRỐNG khi món chưa có BOM. M2 lọc brand / phạm vi / kỳ trên bảng này.</t>
+          <t xml:space="preserve">                                  Dòng món thuộc nhóm LTO (Nhóm món chứa $campaign.lto_group_rx) gắn TỔNG hoá đơn chứa nó — nền doanh thu CTKM của chương trình LTO chạy theo món. `bill_net` = Tổng tiền cả hoá đơn (gồm món khác) · `line_rev` = Thành tiền riêng dòng LTO. Một hoá đơn có nhiều dòng LTO → cộng bill_net theo hoá đơn DUY NHẤT.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   store_month                9 dòng   bắt buộc: month, store, net, guest, tc</t>
+          <t xml:space="preserve">   fact_partner               3 dòng   bắt buộc: store, partner, basis</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  XƯƠNG SỐNG của hệ thống. net = doanh thu thuần · guest = số khách · tc = số hoá đơn.</t>
+          <t xml:space="preserve">                                  Hoá đơn ĐỐI TÁC theo tháng × cửa hàng × đối tác — nền chung của M7 (thẻ Đối tác) và M9. Mỗi hoá đơn thuộc MỘT đối tác, nhận theo thứ tự `basis`: CTKM (tên CTKM khớp luật PARTNER, mã ở $promo_nature.rules[].partner) → NGUON (cột Nguồn là nền tảng) → PTTT (trả qua ví nền tảng). `camp` = tên CTKM nguyên văn (có thể rỗng). `net` = Tổng tiền (cùng base store_month) · `gross` = trước giảm giá · `disc` = Giảm giá + Chiết khấu · `voucher` = Phiếu GG · `commission` = cột Hoa hồng của POS.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  loader tự tính: ta, aov, brand, tier</t>
+          <t xml:space="preserve">   daily_party               38 dòng   bắt buộc: date, store, net, tc</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   daily                    167 dòng   bắt buộc: date, store, net</t>
+          <t xml:space="preserve">                                  Phần KHÁCH TIỆC của `daily`: chỉ các hoá đơn có Số khách ≥ $guest_segment.party_min_guests, gộp theo NGÀY × cửa hàng. ETL tự sinh từ bảng kê hoá đơn (S02). Khách lẻ = daily − daily_party.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Doanh thu theo NGÀY × cửa hàng. Ngày phải nằm trong tháng của file.</t>
+          <t xml:space="preserve">   heat                     636 dòng   bắt buộc: month, store, dow, hour_in</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   coverage                   1 dòng   bắt buộc: month</t>
+          <t xml:space="preserve">                                  Ma trận giờ vào × thứ theo tháng × cửa hàng. dow: 0 = Thứ 2 … 6 = Chủ nhật.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Số ngày THỰC CÓ dữ liệu — nhận diện tháng chưa trọn kỳ. Không khai thì loader suy từ daily.</t>
+          <t xml:space="preserve">   payment                  120 dòng   bắt buộc: month, store, pttt</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  loader tự tính: partial</t>
+          <t xml:space="preserve">                                  Doanh thu theo phương thức thanh toán × tháng × cửa hàng.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   dim_target                 4 dòng   bắt buộc: month, store, target</t>
+          <t xml:space="preserve">   product_month            953 dòng   bắt buộc: store, ma, qty, rev</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Target doanh thu theo cửa hàng × tháng. Được phép khai cả tháng tương lai.</t>
+          <t xml:space="preserve">                                  Bán món theo tháng × cửa hàng (POS báo cáo bán hàng). rev = Thành tiền (trước phí DV &amp; VAT). cogs = giá vốn BOM × số lượng — TRỐNG khi món chưa có BOM. M2 lọc brand / phạm vi / kỳ trên bảng này.</t>
         </is>
       </c>
     </row>
@@ -1118,6 +1118,1888 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>daypart</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>net</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>IFC_SIG</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Sáng ≤10h</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>10460200</v>
+      </c>
+      <c r="E2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F2" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>IFC_SIG</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Trưa 11-14h</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>7556100</v>
+      </c>
+      <c r="E3" t="n">
+        <v>29</v>
+      </c>
+      <c r="F3" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>IFC_SIG</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Chiều 15-17h</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>6683800</v>
+      </c>
+      <c r="E4" t="n">
+        <v>27</v>
+      </c>
+      <c r="F4" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>IFC_SIG</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Tối 18-21h</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>43620400</v>
+      </c>
+      <c r="E5" t="n">
+        <v>188</v>
+      </c>
+      <c r="F5" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>IFC_SIG</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Khuya 22h+</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>12573000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>54</v>
+      </c>
+      <c r="F6" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>NCB_9ST</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Sáng ≤10h</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1894100</v>
+      </c>
+      <c r="E7" t="n">
+        <v>11</v>
+      </c>
+      <c r="F7" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>NCB_9ST</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Trưa 11-14h</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1031550</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>NCB_9ST</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Chiều 15-17h</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>701700</v>
+      </c>
+      <c r="E9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Sáng ≤10h</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>107134200</v>
+      </c>
+      <c r="E10" t="n">
+        <v>389</v>
+      </c>
+      <c r="F10" t="n">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Trưa 11-14h</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>183892700</v>
+      </c>
+      <c r="E11" t="n">
+        <v>491</v>
+      </c>
+      <c r="F11" t="n">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Chiều 15-17h</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>346325530</v>
+      </c>
+      <c r="E12" t="n">
+        <v>280</v>
+      </c>
+      <c r="F12" t="n">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Tối 18-21h</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>161738500</v>
+      </c>
+      <c r="E13" t="n">
+        <v>257</v>
+      </c>
+      <c r="F13" t="n">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>NCB_GW</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Trưa 11-14h</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1908000</v>
+      </c>
+      <c r="E14" t="n">
+        <v>18</v>
+      </c>
+      <c r="F14" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>NCB_GW</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Chiều 15-17h</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>8070000</v>
+      </c>
+      <c r="E15" t="n">
+        <v>38</v>
+      </c>
+      <c r="F15" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>NCB_GW</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Tối 18-21h</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>3155000</v>
+      </c>
+      <c r="E16" t="n">
+        <v>17</v>
+      </c>
+      <c r="F16" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Sáng ≤10h</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>134157650</v>
+      </c>
+      <c r="E17" t="n">
+        <v>709</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Trưa 11-14h</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>191211300</v>
+      </c>
+      <c r="E18" t="n">
+        <v>692</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1201</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Chiều 15-17h</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>70158050</v>
+      </c>
+      <c r="E19" t="n">
+        <v>344</v>
+      </c>
+      <c r="F19" t="n">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Tối 18-21h</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>56970650</v>
+      </c>
+      <c r="E20" t="n">
+        <v>188</v>
+      </c>
+      <c r="F20" t="n">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>NCB_NDC</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Sáng ≤10h</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>4002000</v>
+      </c>
+      <c r="E21" t="n">
+        <v>5</v>
+      </c>
+      <c r="F21" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>NCB_NDC</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Trưa 11-14h</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>93500</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>NCB_NDC</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Chiều 15-17h</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>127500</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Sáng ≤10h</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>106457300</v>
+      </c>
+      <c r="E24" t="n">
+        <v>338</v>
+      </c>
+      <c r="F24" t="n">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Trưa 11-14h</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>352530394</v>
+      </c>
+      <c r="E25" t="n">
+        <v>340</v>
+      </c>
+      <c r="F25" t="n">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Chiều 15-17h</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>53541500</v>
+      </c>
+      <c r="E26" t="n">
+        <v>212</v>
+      </c>
+      <c r="F26" t="n">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Tối 18-21h</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>94551000</v>
+      </c>
+      <c r="E27" t="n">
+        <v>204</v>
+      </c>
+      <c r="F27" t="n">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Sáng ≤10h</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>390565837</v>
+      </c>
+      <c r="E28" t="n">
+        <v>792</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1951</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Trưa 11-14h</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>490394343</v>
+      </c>
+      <c r="E29" t="n">
+        <v>808</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1986</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Chiều 15-17h</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>360003828</v>
+      </c>
+      <c r="E30" t="n">
+        <v>523</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1284</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Tối 18-21h</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>764137295</v>
+      </c>
+      <c r="E31" t="n">
+        <v>835</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2281</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Khuya 22h+</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>11151640</v>
+      </c>
+      <c r="E32" t="n">
+        <v>15</v>
+      </c>
+      <c r="F32" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Sáng ≤10h</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>18407025</v>
+      </c>
+      <c r="E33" t="n">
+        <v>26</v>
+      </c>
+      <c r="F33" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Trưa 11-14h</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>53365088</v>
+      </c>
+      <c r="E34" t="n">
+        <v>57</v>
+      </c>
+      <c r="F34" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Chiều 15-17h</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>23537961</v>
+      </c>
+      <c r="E35" t="n">
+        <v>16</v>
+      </c>
+      <c r="F35" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Tối 18-21h</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>76338127</v>
+      </c>
+      <c r="E36" t="n">
+        <v>50</v>
+      </c>
+      <c r="F36" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Khuya 22h+</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>597618</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>channel</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>net</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>IFC_SIG</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>TẠI CHỖ</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>78230500</v>
+      </c>
+      <c r="E2" t="n">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>IFC_SIG</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>MANG VỀ</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2663000</v>
+      </c>
+      <c r="E3" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NCB_9ST</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>TẠI CHỖ</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>3627350</v>
+      </c>
+      <c r="E4" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>TẠI CHỖ</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>693329730</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CORPORATE</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>61405000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>MANG VỀ</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>44356200</v>
+      </c>
+      <c r="E7" t="n">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>NCB_GW</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>TẠI CHỖ</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>13133000</v>
+      </c>
+      <c r="E8" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>TẠI CHỖ</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>414040500</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1685</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>MANG VỀ</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>36585150</v>
+      </c>
+      <c r="E10" t="n">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>GRAB</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1872000</v>
+      </c>
+      <c r="E11" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>NCB_NDC</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>TẠI CHỖ</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>4223000</v>
+      </c>
+      <c r="E12" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>TẠI CHỖ</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>594684444</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>MANG VỀ</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>12395750</v>
+      </c>
+      <c r="E14" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>TẠI CHỖ</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>2016252943</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2973</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>TẠI CHỖ</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>164032095</v>
+      </c>
+      <c r="E16" t="n">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>MANG VỀ</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>8213724</v>
+      </c>
+      <c r="E17" t="n">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>bills</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>id_bills</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>items</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>8017</v>
+      </c>
+      <c r="C2" t="n">
+        <v>553</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25482</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>nature</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>rev</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>disc</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>bills</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CARE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NCB</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>515000</v>
+      </c>
+      <c r="E2" t="n">
+        <v>51500</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CARE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2069000</v>
+      </c>
+      <c r="E3" t="n">
+        <v>276600</v>
+      </c>
+      <c r="F3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>COMMERCIAL</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NCB</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>190287000</v>
+      </c>
+      <c r="E4" t="n">
+        <v>100645700</v>
+      </c>
+      <c r="F4" t="n">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>COMMERCIAL</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>164722100</v>
+      </c>
+      <c r="E5" t="n">
+        <v>64043623</v>
+      </c>
+      <c r="F5" t="n">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>COMMERCIAL</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NJFB</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>33432000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>12787182</v>
+      </c>
+      <c r="F6" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>COMMERCIAL</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>6396000</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1060000</v>
+      </c>
+      <c r="F7" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>INTERNAL</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NCB</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>187306000</v>
+      </c>
+      <c r="E8" t="n">
+        <v>55636550</v>
+      </c>
+      <c r="F8" t="n">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>INTERNAL</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>109464000</v>
+      </c>
+      <c r="E9" t="n">
+        <v>29978989</v>
+      </c>
+      <c r="F9" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>INTERNAL</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NJFB</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>41508000</v>
+      </c>
+      <c r="E10" t="n">
+        <v>12749000</v>
+      </c>
+      <c r="F10" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>INTERNAL</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>198000</v>
+      </c>
+      <c r="E11" t="n">
+        <v>49500</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>LOYALTY</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NCB</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>100661000</v>
+      </c>
+      <c r="E12" t="n">
+        <v>8176000</v>
+      </c>
+      <c r="F12" t="n">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>LOYALTY</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>34126000</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2896950</v>
+      </c>
+      <c r="F13" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>LOYALTY</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NJFB</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>7085000</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>PARTNER</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NCB</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>17030000</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1703000</v>
+      </c>
+      <c r="F15" t="n">
+        <v>76</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1486,7 +3368,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -28579,7 +30461,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -36508,7 +38390,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -36758,7 +38640,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -37604,7 +39486,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -52922,7 +54804,310 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>net</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>gross</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>disc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>IFC_SIG</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>80893500</v>
+      </c>
+      <c r="D2" t="n">
+        <v>612</v>
+      </c>
+      <c r="E2" t="n">
+        <v>348</v>
+      </c>
+      <c r="F2" t="n">
+        <v>82003000</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1109500</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>NCB_9ST</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>3627350</v>
+      </c>
+      <c r="D3" t="n">
+        <v>65</v>
+      </c>
+      <c r="E3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F3" t="n">
+        <v>4580000</v>
+      </c>
+      <c r="G3" t="n">
+        <v>952650</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>799090930</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2506</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1417</v>
+      </c>
+      <c r="F4" t="n">
+        <v>856626880</v>
+      </c>
+      <c r="G4" t="n">
+        <v>57535950</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>NCB_GW</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>13133000</v>
+      </c>
+      <c r="D5" t="n">
+        <v>109</v>
+      </c>
+      <c r="E5" t="n">
+        <v>73</v>
+      </c>
+      <c r="F5" t="n">
+        <v>13133000</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>452497650</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3147</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1933</v>
+      </c>
+      <c r="F6" t="n">
+        <v>474860000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>22362350</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>NCB_NDC</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>4223000</v>
+      </c>
+      <c r="D7" t="n">
+        <v>52</v>
+      </c>
+      <c r="E7" t="n">
+        <v>9</v>
+      </c>
+      <c r="F7" t="n">
+        <v>5922000</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1699000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>607080194</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2344</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1094</v>
+      </c>
+      <c r="F8" t="n">
+        <v>639881844</v>
+      </c>
+      <c r="G8" t="n">
+        <v>32801650</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2016252943</v>
+      </c>
+      <c r="D9" t="n">
+        <v>7521</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2973</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2097945393</v>
+      </c>
+      <c r="G9" t="n">
+        <v>81692450</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>172245819</v>
+      </c>
+      <c r="D10" t="n">
+        <v>359</v>
+      </c>
+      <c r="E10" t="n">
+        <v>150</v>
+      </c>
+      <c r="F10" t="n">
+        <v>192575569</v>
+      </c>
+      <c r="G10" t="n">
+        <v>20329750</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -55730,7 +57915,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -60556,11 +62741,6 @@
           <t>COMBO VIETNAMESE CORNER &amp; COFFEE</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="F121" t="inlineStr">
         <is>
           <t>Combo</t>
@@ -63846,11 +66026,6 @@
           <t>AFTERNOON TEA SET (359K)</t>
         </is>
       </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="F203" t="inlineStr">
         <is>
           <t>Combo</t>
@@ -64481,11 +66656,6 @@
           <t>COMBO DUO PASTRY &amp; COFFEE (149K)</t>
         </is>
       </c>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="F219" t="inlineStr">
         <is>
           <t>Combo</t>
@@ -64519,11 +66689,6 @@
           <t>COMBO DUO PASTRY &amp; COFFEE (119K)</t>
         </is>
       </c>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="F220" t="inlineStr">
         <is>
           <t>Combo</t>
@@ -66832,11 +68997,6 @@
           <t>Bánh Sừng Bò Kẹp Dăm Bông, Phô Mai - Ham Cheese Croissant</t>
         </is>
       </c>
-      <c r="E280" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="F280" t="inlineStr">
         <is>
           <t>UnCategory</t>
@@ -67978,11 +70138,6 @@
           <t>COMBO VIETNAMESE CORNER &amp; COFFEE</t>
         </is>
       </c>
-      <c r="E310" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="F310" t="inlineStr">
         <is>
           <t>Combo</t>
@@ -69708,11 +71863,6 @@
           <t>COMBO DUO PASTRY &amp; COFFEE (119K)</t>
         </is>
       </c>
-      <c r="E353" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="F353" t="inlineStr">
         <is>
           <t>Combo</t>
@@ -72366,11 +74516,6 @@
           <t>COMBO DUO PASTRY &amp; COFFEE (149K)</t>
         </is>
       </c>
-      <c r="E419" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="F419" t="inlineStr">
         <is>
           <t>Combo</t>
@@ -72790,11 +74935,6 @@
           <t>COMBO LUNCH - 179k</t>
         </is>
       </c>
-      <c r="E430" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="F430" t="inlineStr">
         <is>
           <t>Combo</t>
@@ -73758,11 +75898,6 @@
           <t>Bánh Sừng Bò Kẹp Dăm Bông, Phô Mai - Ham Cheese Croissant</t>
         </is>
       </c>
-      <c r="E455" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="F455" t="inlineStr">
         <is>
           <t>UnCategory</t>
@@ -79967,11 +82102,6 @@
           <t>SET MENU A</t>
         </is>
       </c>
-      <c r="E612" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="F612" t="inlineStr">
         <is>
           <t>Combo</t>
@@ -80441,11 +82571,6 @@
           <t>SET MENU C</t>
         </is>
       </c>
-      <c r="E624" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="F624" t="inlineStr">
         <is>
           <t>Combo</t>
@@ -81266,11 +83391,6 @@
           <t>SET MENU D</t>
         </is>
       </c>
-      <c r="E645" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="F645" t="inlineStr">
         <is>
           <t>Combo</t>
@@ -82369,11 +84489,6 @@
           <t>SET VALENTINE NOIRE DINING</t>
         </is>
       </c>
-      <c r="E673" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="F673" t="inlineStr">
         <is>
           <t>Combo</t>
@@ -88568,11 +90683,6 @@
       <c r="D835" t="inlineStr">
         <is>
           <t>Combo Premium</t>
-        </is>
-      </c>
-      <c r="E835" t="inlineStr">
-        <is>
-          <t>-</t>
         </is>
       </c>
       <c r="F835" t="inlineStr">
@@ -93153,13 +95263,768 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>follows</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>msgs</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>views</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>menu</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>content</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>days</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C2" t="n">
+        <v>9</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>21</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>follows</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>msgs</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>views</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>menu</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>content</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>2</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -93167,8 +96032,6 @@
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -93179,32 +96042,22 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>store</t>
+          <t>spend</t>
         </is>
       </c>
       <c r="C1" s="4" t="inlineStr">
         <is>
-          <t>net</t>
+          <t>reach</t>
         </is>
       </c>
       <c r="D1" s="4" t="inlineStr">
         <is>
-          <t>guest</t>
+          <t>impr</t>
         </is>
       </c>
       <c r="E1" s="4" t="inlineStr">
         <is>
-          <t>tc</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>gross</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>disc</t>
+          <t>n</t>
         </is>
       </c>
     </row>
@@ -93214,241 +96067,17 @@
           <t>2026-02</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>IFC_SIG</t>
-        </is>
+      <c r="B2" t="n">
+        <v>4487025</v>
       </c>
       <c r="C2" t="n">
-        <v>80893500</v>
+        <v>80872</v>
       </c>
       <c r="D2" t="n">
-        <v>612</v>
+        <v>111502</v>
       </c>
       <c r="E2" t="n">
-        <v>348</v>
-      </c>
-      <c r="F2" t="n">
-        <v>82003000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1109500</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>NCB_9ST</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>3627350</v>
-      </c>
-      <c r="D3" t="n">
-        <v>65</v>
-      </c>
-      <c r="E3" t="n">
-        <v>20</v>
-      </c>
-      <c r="F3" t="n">
-        <v>4580000</v>
-      </c>
-      <c r="G3" t="n">
-        <v>952650</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>799090930</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2506</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1417</v>
-      </c>
-      <c r="F4" t="n">
-        <v>856626880</v>
-      </c>
-      <c r="G4" t="n">
-        <v>57535950</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>NCB_GW</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>13133000</v>
-      </c>
-      <c r="D5" t="n">
-        <v>109</v>
-      </c>
-      <c r="E5" t="n">
-        <v>73</v>
-      </c>
-      <c r="F5" t="n">
-        <v>13133000</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>452497650</v>
-      </c>
-      <c r="D6" t="n">
-        <v>3147</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1933</v>
-      </c>
-      <c r="F6" t="n">
-        <v>474860000</v>
-      </c>
-      <c r="G6" t="n">
-        <v>22362350</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>NCB_NDC</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>4223000</v>
-      </c>
-      <c r="D7" t="n">
-        <v>52</v>
-      </c>
-      <c r="E7" t="n">
-        <v>9</v>
-      </c>
-      <c r="F7" t="n">
-        <v>5922000</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1699000</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>607080194</v>
-      </c>
-      <c r="D8" t="n">
-        <v>2344</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1094</v>
-      </c>
-      <c r="F8" t="n">
-        <v>639881844</v>
-      </c>
-      <c r="G8" t="n">
-        <v>32801650</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>2016252943</v>
-      </c>
-      <c r="D9" t="n">
-        <v>7521</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2973</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2097945393</v>
-      </c>
-      <c r="G9" t="n">
-        <v>81692450</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>172245819</v>
-      </c>
-      <c r="D10" t="n">
-        <v>359</v>
-      </c>
-      <c r="E10" t="n">
-        <v>150</v>
-      </c>
-      <c r="F10" t="n">
-        <v>192575569</v>
-      </c>
-      <c r="G10" t="n">
-        <v>20329750</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -93456,7 +96085,1074 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>spend</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>reach</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>2063502</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22307</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>NCB</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1473726</v>
+      </c>
+      <c r="D3" t="n">
+        <v>32387</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NJFB</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>682581</v>
+      </c>
+      <c r="D4" t="n">
+        <v>20788</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Tuyển dụng</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>267216</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5390</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>objective</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>spend</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Tương tác</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>2663882</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1691</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Lead tiệc</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1144007</v>
+      </c>
+      <c r="D3" t="n">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Khác</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>411920</v>
+      </c>
+      <c r="D4" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Tuyển dụng</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>267216</v>
+      </c>
+      <c r="D5" t="n">
+        <v>120</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>objective</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>campaign</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>spend</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>reach</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>impr</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>result</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>rkind</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>funnel</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>clicks</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Lead tiệc</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>NOIRE Dining- YEP</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>901965</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2884</v>
+      </c>
+      <c r="G2" t="n">
+        <v>7956</v>
+      </c>
+      <c r="H2" t="n">
+        <v>27</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>msg</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>booking</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>NCB</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Tương tác</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NOIRE Bistro - Workshop</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>827497</v>
+      </c>
+      <c r="F3" t="n">
+        <v>12369</v>
+      </c>
+      <c r="G3" t="n">
+        <v>17090</v>
+      </c>
+      <c r="H3" t="n">
+        <v>333</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>engage</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NJFB</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Tương tác</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NOIRE JFB - Không gian</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>447259</v>
+      </c>
+      <c r="F4" t="n">
+        <v>8080</v>
+      </c>
+      <c r="G4" t="n">
+        <v>13594</v>
+      </c>
+      <c r="H4" t="n">
+        <v>636</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>engage</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Tương tác</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NOIRE Dining - Valentine</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>421796</v>
+      </c>
+      <c r="F5" t="n">
+        <v>6446</v>
+      </c>
+      <c r="G5" t="n">
+        <v>8465</v>
+      </c>
+      <c r="H5" t="n">
+        <v>238</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>engage</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Tương tác</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NOIRE Dining - Promotion</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>413004</v>
+      </c>
+      <c r="F6" t="n">
+        <v>6421</v>
+      </c>
+      <c r="G6" t="n">
+        <v>7857</v>
+      </c>
+      <c r="H6" t="n">
+        <v>266</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>engage</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Tuyển dụng</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Tuyển dụng</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>HR - tuyển dụng</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>267216</v>
+      </c>
+      <c r="F7" t="n">
+        <v>5390</v>
+      </c>
+      <c r="G7" t="n">
+        <v>6958</v>
+      </c>
+      <c r="H7" t="n">
+        <v>120</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>engage</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>NCB</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Lead tiệc</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NOIRE Bistro - Tiệc</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>242042</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2622</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2976</v>
+      </c>
+      <c r="H8" t="n">
+        <v>102</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>engage</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>booking</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>NJFB</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Khác</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Noire JFB- Like Fanpage</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>235322</v>
+      </c>
+      <c r="F9" t="n">
+        <v>12708</v>
+      </c>
+      <c r="G9" t="n">
+        <v>14874</v>
+      </c>
+      <c r="H9" t="n">
+        <v>91</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>like</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>NCB</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Tương tác</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NOIRE Bistro - Contest Tết</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>209699</v>
+      </c>
+      <c r="F10" t="n">
+        <v>4596</v>
+      </c>
+      <c r="G10" t="n">
+        <v>6507</v>
+      </c>
+      <c r="H10" t="n">
+        <v>62</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>engage</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Tương tác</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Thử nghiệm - NOIRE Dining - Valentine</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>207113</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2993</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3785</v>
+      </c>
+      <c r="H11" t="n">
+        <v>67</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>engage</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>NCB</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Khác</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NOIRE Bistro - Workshop</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>176598</v>
+      </c>
+      <c r="F12" t="n">
+        <v>12398</v>
+      </c>
+      <c r="G12" t="n">
+        <v>15817</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Tương tác</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NOIRE Dining - LTO Tết</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>119624</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3563</v>
+      </c>
+      <c r="G13" t="n">
+        <v>5202</v>
+      </c>
+      <c r="H13" t="n">
+        <v>77</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>engage</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>NCB</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Tương tác</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NOIRE Bistro - LTO Tết</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>17890</v>
+      </c>
+      <c r="F14" t="n">
+        <v>402</v>
+      </c>
+      <c r="G14" t="n">
+        <v>421</v>
+      </c>
+      <c r="H14" t="n">
+        <v>12</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>engage</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>rev</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>rev_cov</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>sku</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>sku_cov</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>4074479228</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2032367000</v>
+      </c>
+      <c r="D2" t="n">
+        <v>601</v>
+      </c>
+      <c r="E2" t="n">
+        <v>156</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.4988</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>used</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>rev</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>disc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>NCB</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>112</v>
+      </c>
+      <c r="D2" t="n">
+        <v>39730000</v>
+      </c>
+      <c r="E2" t="n">
+        <v>8253200</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>15</v>
+      </c>
+      <c r="D3" t="n">
+        <v>26612100</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5171000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NJFB</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4498000</v>
+      </c>
+      <c r="E4" t="n">
+        <v>899600</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Không rõ</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>8</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1184000</v>
+      </c>
+      <c r="E5" t="n">
+        <v>236800</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -97011,7 +100707,218 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>hit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>142</v>
+      </c>
+      <c r="C2" t="n">
+        <v>141</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>days_data</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>days_month</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>first</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>last</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>28</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>752400000</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>818400000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>2000000000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>340000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -97731,2063 +101638,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>month</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>days_data</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>days_month</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>first</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>last</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>28</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>month</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>store</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>target</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>752400000</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>818400000</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>2000000000</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>340000000</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>month</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>follows</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>msgs</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>views</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>menu</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>content</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>days</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>7</v>
-      </c>
-      <c r="C2" t="n">
-        <v>9</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>21</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>28</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>follows</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>msgs</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>views</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>menu</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>content</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-02-02</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-02-08</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-02-12</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>3</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-02-14</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026-02-15</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>2</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2026-02-16</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2026-02-17</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2026-02-18</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2026-02-21</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>2</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>1</v>
-      </c>
-      <c r="C27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" t="n">
-        <v>2</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>month</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>spend</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>reach</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>impr</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>4487025</v>
-      </c>
-      <c r="C2" t="n">
-        <v>80872</v>
-      </c>
-      <c r="D2" t="n">
-        <v>111502</v>
-      </c>
-      <c r="E2" t="n">
-        <v>12</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>month</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>brand</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>spend</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>reach</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>NDC</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>2063502</v>
-      </c>
-      <c r="D2" t="n">
-        <v>22307</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>NCB</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>1473726</v>
-      </c>
-      <c r="D3" t="n">
-        <v>32387</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>NJFB</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>682581</v>
-      </c>
-      <c r="D4" t="n">
-        <v>20788</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Tuyển dụng</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>267216</v>
-      </c>
-      <c r="D5" t="n">
-        <v>5390</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>month</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>objective</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>spend</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Tương tác</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>2663882</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1691</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Lead tiệc</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>1144007</v>
-      </c>
-      <c r="D3" t="n">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Khác</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>411920</v>
-      </c>
-      <c r="D4" t="n">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Tuyển dụng</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>267216</v>
-      </c>
-      <c r="D5" t="n">
-        <v>120</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>month</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>brand</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>objective</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>campaign</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>spend</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>reach</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>impr</t>
-        </is>
-      </c>
-      <c r="H1" s="4" t="inlineStr">
-        <is>
-          <t>result</t>
-        </is>
-      </c>
-      <c r="I1" s="4" t="inlineStr">
-        <is>
-          <t>page</t>
-        </is>
-      </c>
-      <c r="J1" s="4" t="inlineStr">
-        <is>
-          <t>rkind</t>
-        </is>
-      </c>
-      <c r="K1" s="4" t="inlineStr">
-        <is>
-          <t>funnel</t>
-        </is>
-      </c>
-      <c r="L1" s="4" t="inlineStr">
-        <is>
-          <t>clicks</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>NDC</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Lead tiệc</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>NOIRE Dining- YEP</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>901965</v>
-      </c>
-      <c r="F2" t="n">
-        <v>2884</v>
-      </c>
-      <c r="G2" t="n">
-        <v>7956</v>
-      </c>
-      <c r="H2" t="n">
-        <v>27</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>msg</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>booking</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>NCB</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Tương tác</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>NOIRE Bistro - Workshop</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>827497</v>
-      </c>
-      <c r="F3" t="n">
-        <v>12369</v>
-      </c>
-      <c r="G3" t="n">
-        <v>17090</v>
-      </c>
-      <c r="H3" t="n">
-        <v>333</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>engage</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>NJFB</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Tương tác</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>NOIRE JFB - Không gian</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>447259</v>
-      </c>
-      <c r="F4" t="n">
-        <v>8080</v>
-      </c>
-      <c r="G4" t="n">
-        <v>13594</v>
-      </c>
-      <c r="H4" t="n">
-        <v>636</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>engage</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>NDC</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Tương tác</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>NOIRE Dining - Valentine</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>421796</v>
-      </c>
-      <c r="F5" t="n">
-        <v>6446</v>
-      </c>
-      <c r="G5" t="n">
-        <v>8465</v>
-      </c>
-      <c r="H5" t="n">
-        <v>238</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>engage</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>NDC</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Tương tác</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>NOIRE Dining - Promotion</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>413004</v>
-      </c>
-      <c r="F6" t="n">
-        <v>6421</v>
-      </c>
-      <c r="G6" t="n">
-        <v>7857</v>
-      </c>
-      <c r="H6" t="n">
-        <v>266</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>engage</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Tuyển dụng</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Tuyển dụng</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>HR - tuyển dụng</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>267216</v>
-      </c>
-      <c r="F7" t="n">
-        <v>5390</v>
-      </c>
-      <c r="G7" t="n">
-        <v>6958</v>
-      </c>
-      <c r="H7" t="n">
-        <v>120</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>engage</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>NCB</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Lead tiệc</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NOIRE Bistro - Tiệc</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>242042</v>
-      </c>
-      <c r="F8" t="n">
-        <v>2622</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2976</v>
-      </c>
-      <c r="H8" t="n">
-        <v>102</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>engage</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>booking</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>NJFB</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Khác</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Noire JFB- Like Fanpage</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>235322</v>
-      </c>
-      <c r="F9" t="n">
-        <v>12708</v>
-      </c>
-      <c r="G9" t="n">
-        <v>14874</v>
-      </c>
-      <c r="H9" t="n">
-        <v>91</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>like</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>NCB</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Tương tác</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>NOIRE Bistro - Contest Tết</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>209699</v>
-      </c>
-      <c r="F10" t="n">
-        <v>4596</v>
-      </c>
-      <c r="G10" t="n">
-        <v>6507</v>
-      </c>
-      <c r="H10" t="n">
-        <v>62</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>engage</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>NDC</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Tương tác</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Thử nghiệm - NOIRE Dining - Valentine</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>207113</v>
-      </c>
-      <c r="F11" t="n">
-        <v>2993</v>
-      </c>
-      <c r="G11" t="n">
-        <v>3785</v>
-      </c>
-      <c r="H11" t="n">
-        <v>67</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>engage</t>
-        </is>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>NCB</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Khác</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>NOIRE Bistro - Workshop</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>176598</v>
-      </c>
-      <c r="F12" t="n">
-        <v>12398</v>
-      </c>
-      <c r="G12" t="n">
-        <v>15817</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="L12" t="n">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>NDC</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Tương tác</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>NOIRE Dining - LTO Tết</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>119624</v>
-      </c>
-      <c r="F13" t="n">
-        <v>3563</v>
-      </c>
-      <c r="G13" t="n">
-        <v>5202</v>
-      </c>
-      <c r="H13" t="n">
-        <v>77</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>engage</t>
-        </is>
-      </c>
-      <c r="L13" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>NCB</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Tương tác</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>NOIRE Bistro - LTO Tết</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>17890</v>
-      </c>
-      <c r="F14" t="n">
-        <v>402</v>
-      </c>
-      <c r="G14" t="n">
-        <v>421</v>
-      </c>
-      <c r="H14" t="n">
-        <v>12</v>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>engage</t>
-        </is>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>month</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>rev</t>
-        </is>
-      </c>
-      <c r="C1" s="5" t="inlineStr">
-        <is>
-          <t>rev_cov</t>
-        </is>
-      </c>
-      <c r="D1" s="5" t="inlineStr">
-        <is>
-          <t>sku</t>
-        </is>
-      </c>
-      <c r="E1" s="5" t="inlineStr">
-        <is>
-          <t>sku_cov</t>
-        </is>
-      </c>
-      <c r="F1" s="5" t="inlineStr">
-        <is>
-          <t>pct</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>4074479228</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2032367000</v>
-      </c>
-      <c r="D2" t="n">
-        <v>601</v>
-      </c>
-      <c r="E2" t="n">
-        <v>156</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.4988</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>brand</t>
-        </is>
-      </c>
-      <c r="C1" s="5" t="inlineStr">
-        <is>
-          <t>used</t>
-        </is>
-      </c>
-      <c r="D1" s="5" t="inlineStr">
-        <is>
-          <t>rev</t>
-        </is>
-      </c>
-      <c r="E1" s="5" t="inlineStr">
-        <is>
-          <t>disc</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>NCB</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>112</v>
-      </c>
-      <c r="D2" t="n">
-        <v>39730000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>8253200</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>NDC</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>15</v>
-      </c>
-      <c r="D3" t="n">
-        <v>26612100</v>
-      </c>
-      <c r="E3" t="n">
-        <v>5171000</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>NJFB</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>7</v>
-      </c>
-      <c r="D4" t="n">
-        <v>4498000</v>
-      </c>
-      <c r="E4" t="n">
-        <v>899600</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Không rõ</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>8</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1184000</v>
-      </c>
-      <c r="E5" t="n">
-        <v>236800</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -99928,51 +101779,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C1" s="5" t="inlineStr">
-        <is>
-          <t>hit</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>142</v>
-      </c>
-      <c r="C2" t="n">
-        <v>141</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -100167,7 +101974,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -100217,1886 +102024,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F37"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>month</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>store</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>daypart</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>net</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>tc</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>guest</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>IFC_SIG</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Sáng ≤10h</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>10460200</v>
-      </c>
-      <c r="E2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F2" t="n">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>IFC_SIG</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Trưa 11-14h</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>7556100</v>
-      </c>
-      <c r="E3" t="n">
-        <v>29</v>
-      </c>
-      <c r="F3" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>IFC_SIG</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Chiều 15-17h</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>6683800</v>
-      </c>
-      <c r="E4" t="n">
-        <v>27</v>
-      </c>
-      <c r="F4" t="n">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>IFC_SIG</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Tối 18-21h</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>43620400</v>
-      </c>
-      <c r="E5" t="n">
-        <v>188</v>
-      </c>
-      <c r="F5" t="n">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>IFC_SIG</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Khuya 22h+</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>12573000</v>
-      </c>
-      <c r="E6" t="n">
-        <v>54</v>
-      </c>
-      <c r="F6" t="n">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>NCB_9ST</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Sáng ≤10h</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>1894100</v>
-      </c>
-      <c r="E7" t="n">
-        <v>11</v>
-      </c>
-      <c r="F7" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>NCB_9ST</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Trưa 11-14h</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>1031550</v>
-      </c>
-      <c r="E8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F8" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>NCB_9ST</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Chiều 15-17h</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>701700</v>
-      </c>
-      <c r="E9" t="n">
-        <v>4</v>
-      </c>
-      <c r="F9" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Sáng ≤10h</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>107134200</v>
-      </c>
-      <c r="E10" t="n">
-        <v>389</v>
-      </c>
-      <c r="F10" t="n">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Trưa 11-14h</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>183892700</v>
-      </c>
-      <c r="E11" t="n">
-        <v>491</v>
-      </c>
-      <c r="F11" t="n">
-        <v>842</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Chiều 15-17h</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>346325530</v>
-      </c>
-      <c r="E12" t="n">
-        <v>280</v>
-      </c>
-      <c r="F12" t="n">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Tối 18-21h</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>161738500</v>
-      </c>
-      <c r="E13" t="n">
-        <v>257</v>
-      </c>
-      <c r="F13" t="n">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>NCB_GW</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Trưa 11-14h</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>1908000</v>
-      </c>
-      <c r="E14" t="n">
-        <v>18</v>
-      </c>
-      <c r="F14" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>NCB_GW</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Chiều 15-17h</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>8070000</v>
-      </c>
-      <c r="E15" t="n">
-        <v>38</v>
-      </c>
-      <c r="F15" t="n">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>NCB_GW</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Tối 18-21h</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>3155000</v>
-      </c>
-      <c r="E16" t="n">
-        <v>17</v>
-      </c>
-      <c r="F16" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Sáng ≤10h</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>134157650</v>
-      </c>
-      <c r="E17" t="n">
-        <v>709</v>
-      </c>
-      <c r="F17" t="n">
-        <v>1039</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Trưa 11-14h</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>191211300</v>
-      </c>
-      <c r="E18" t="n">
-        <v>692</v>
-      </c>
-      <c r="F18" t="n">
-        <v>1201</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Chiều 15-17h</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>70158050</v>
-      </c>
-      <c r="E19" t="n">
-        <v>344</v>
-      </c>
-      <c r="F19" t="n">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Tối 18-21h</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>56970650</v>
-      </c>
-      <c r="E20" t="n">
-        <v>188</v>
-      </c>
-      <c r="F20" t="n">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>NCB_NDC</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Sáng ≤10h</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>4002000</v>
-      </c>
-      <c r="E21" t="n">
-        <v>5</v>
-      </c>
-      <c r="F21" t="n">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>NCB_NDC</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Trưa 11-14h</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>93500</v>
-      </c>
-      <c r="E22" t="n">
-        <v>2</v>
-      </c>
-      <c r="F22" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>NCB_NDC</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Chiều 15-17h</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>127500</v>
-      </c>
-      <c r="E23" t="n">
-        <v>2</v>
-      </c>
-      <c r="F23" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Sáng ≤10h</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>106457300</v>
-      </c>
-      <c r="E24" t="n">
-        <v>338</v>
-      </c>
-      <c r="F24" t="n">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Trưa 11-14h</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>352530394</v>
-      </c>
-      <c r="E25" t="n">
-        <v>340</v>
-      </c>
-      <c r="F25" t="n">
-        <v>934</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Chiều 15-17h</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>53541500</v>
-      </c>
-      <c r="E26" t="n">
-        <v>212</v>
-      </c>
-      <c r="F26" t="n">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Tối 18-21h</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>94551000</v>
-      </c>
-      <c r="E27" t="n">
-        <v>204</v>
-      </c>
-      <c r="F27" t="n">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Sáng ≤10h</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>390565837</v>
-      </c>
-      <c r="E28" t="n">
-        <v>792</v>
-      </c>
-      <c r="F28" t="n">
-        <v>1951</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Trưa 11-14h</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>490394343</v>
-      </c>
-      <c r="E29" t="n">
-        <v>808</v>
-      </c>
-      <c r="F29" t="n">
-        <v>1986</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Chiều 15-17h</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>360003828</v>
-      </c>
-      <c r="E30" t="n">
-        <v>523</v>
-      </c>
-      <c r="F30" t="n">
-        <v>1284</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Tối 18-21h</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>764137295</v>
-      </c>
-      <c r="E31" t="n">
-        <v>835</v>
-      </c>
-      <c r="F31" t="n">
-        <v>2281</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Khuya 22h+</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>11151640</v>
-      </c>
-      <c r="E32" t="n">
-        <v>15</v>
-      </c>
-      <c r="F32" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Sáng ≤10h</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>18407025</v>
-      </c>
-      <c r="E33" t="n">
-        <v>26</v>
-      </c>
-      <c r="F33" t="n">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Trưa 11-14h</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>53365088</v>
-      </c>
-      <c r="E34" t="n">
-        <v>57</v>
-      </c>
-      <c r="F34" t="n">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Chiều 15-17h</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>23537961</v>
-      </c>
-      <c r="E35" t="n">
-        <v>16</v>
-      </c>
-      <c r="F35" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Tối 18-21h</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>76338127</v>
-      </c>
-      <c r="E36" t="n">
-        <v>50</v>
-      </c>
-      <c r="F36" t="n">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Khuya 22h+</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>597618</v>
-      </c>
-      <c r="E37" t="n">
-        <v>1</v>
-      </c>
-      <c r="F37" t="n">
-        <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>month</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>store</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>channel</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>net</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>tc</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>IFC_SIG</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>TẠI CHỖ</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>78230500</v>
-      </c>
-      <c r="E2" t="n">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>IFC_SIG</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>MANG VỀ</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>2663000</v>
-      </c>
-      <c r="E3" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>NCB_9ST</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>TẠI CHỖ</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>3627350</v>
-      </c>
-      <c r="E4" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>TẠI CHỖ</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>693329730</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1148</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>CORPORATE</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>61405000</v>
-      </c>
-      <c r="E6" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>MANG VỀ</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>44356200</v>
-      </c>
-      <c r="E7" t="n">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>NCB_GW</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>TẠI CHỖ</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>13133000</v>
-      </c>
-      <c r="E8" t="n">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>TẠI CHỖ</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>414040500</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1685</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>MANG VỀ</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>36585150</v>
-      </c>
-      <c r="E10" t="n">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>GRAB</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>1872000</v>
-      </c>
-      <c r="E11" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>NCB_NDC</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>TẠI CHỖ</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>4223000</v>
-      </c>
-      <c r="E12" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>TẠI CHỖ</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>594684444</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1024</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>MANG VỀ</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>12395750</v>
-      </c>
-      <c r="E14" t="n">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>TẠI CHỖ</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>2016252943</v>
-      </c>
-      <c r="E15" t="n">
-        <v>2973</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>TẠI CHỖ</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>164032095</v>
-      </c>
-      <c r="E16" t="n">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>MANG VỀ</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>8213724</v>
-      </c>
-      <c r="E17" t="n">
-        <v>23</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>month</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>bills</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>id_bills</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>items</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>8017</v>
-      </c>
-      <c r="C2" t="n">
-        <v>553</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25482</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>month</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>nature</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>brand</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>rev</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>disc</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>bills</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>CARE</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>NCB</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>515000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>51500</v>
-      </c>
-      <c r="F2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>CARE</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>NDC</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>2069000</v>
-      </c>
-      <c r="E3" t="n">
-        <v>276600</v>
-      </c>
-      <c r="F3" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>COMMERCIAL</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>NCB</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>190287000</v>
-      </c>
-      <c r="E4" t="n">
-        <v>100645700</v>
-      </c>
-      <c r="F4" t="n">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>COMMERCIAL</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>NDC</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>164722100</v>
-      </c>
-      <c r="E5" t="n">
-        <v>64043623</v>
-      </c>
-      <c r="F5" t="n">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>COMMERCIAL</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>NJFB</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>33432000</v>
-      </c>
-      <c r="E6" t="n">
-        <v>12787182</v>
-      </c>
-      <c r="F6" t="n">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>COMMERCIAL</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>6396000</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1060000</v>
-      </c>
-      <c r="F7" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>INTERNAL</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>NCB</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>187306000</v>
-      </c>
-      <c r="E8" t="n">
-        <v>55636550</v>
-      </c>
-      <c r="F8" t="n">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>INTERNAL</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>NDC</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>109464000</v>
-      </c>
-      <c r="E9" t="n">
-        <v>29978989</v>
-      </c>
-      <c r="F9" t="n">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>INTERNAL</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>NJFB</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>41508000</v>
-      </c>
-      <c r="E10" t="n">
-        <v>12749000</v>
-      </c>
-      <c r="F10" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>INTERNAL</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>198000</v>
-      </c>
-      <c r="E11" t="n">
-        <v>49500</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>LOYALTY</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>NCB</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>100661000</v>
-      </c>
-      <c r="E12" t="n">
-        <v>8176000</v>
-      </c>
-      <c r="F12" t="n">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>LOYALTY</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>NDC</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>34126000</v>
-      </c>
-      <c r="E13" t="n">
-        <v>2896950</v>
-      </c>
-      <c r="F13" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>LOYALTY</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>NJFB</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>7085000</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>PARTNER</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>NCB</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>17030000</v>
-      </c>
-      <c r="E15" t="n">
-        <v>1703000</v>
-      </c>
-      <c r="F15" t="n">
-        <v>76</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/data_input/monthly/2026-02.xlsx
+++ b/data_input/monthly/2026-02.xlsx
@@ -8,11 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_HƯỚNG DẪN" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="store_month" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="coverage" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dim_target" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="booking" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="booking" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="store_month" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="coverage" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dim_target" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="crm_month" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="crm_store" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="member" sheetId="9" state="visible" r:id="rId9"/>
@@ -660,84 +660,84 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   store_month                9 dòng   bắt buộc: month, store, net, guest, tc</t>
+          <t xml:space="preserve">   booking                    9 dòng   bắt buộc: month, status</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  XƯƠNG SỐNG của hệ thống. net = doanh thu thuần · guest = số khách · tc = số hoá đơn.</t>
+          <t xml:space="preserve">                                  Booking tiệc &amp; sự kiện — gộp theo tháng NHẬN LEAD (month) × tháng DIỄN RA (ev_month) × cửa hàng × phân khúc × loại × nguồn × trạng thái. month = Inquiry Date → Input Date → (thiếu cả hai) ngày sự kiện, khi đó inq_est đếm số lead bị ước. seg ∈ event|table, stage ∈ won|open|lost — luật ở $booking. exp chỉ cộng ô có số (exp_n lead); ô trống/TBA KHÔNG tính là 0. closed_n = số lead Confirmed đã nhập Closed Revenue.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  loader tự tính: ta, aov, brand, tier</t>
+          <t xml:space="preserve">   store_month                9 dòng   bắt buộc: month, store, net, guest, tc</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   daily                    167 dòng   bắt buộc: date, store, net</t>
+          <t xml:space="preserve">                                  XƯƠNG SỐNG của hệ thống. net = doanh thu thuần · guest = số khách · tc = số hoá đơn.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Doanh thu theo NGÀY × cửa hàng. Ngày phải nằm trong tháng của file.</t>
+          <t xml:space="preserve">                                  loader tự tính: ta, aov, brand, tier</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   coverage                   1 dòng   bắt buộc: month</t>
+          <t xml:space="preserve">   daily                    167 dòng   bắt buộc: date, store, net</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Số ngày THỰC CÓ dữ liệu — nhận diện tháng chưa trọn kỳ. Không khai thì loader suy từ daily.</t>
+          <t xml:space="preserve">                                  Doanh thu theo NGÀY × cửa hàng. Ngày phải nằm trong tháng của file.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  loader tự tính: partial</t>
+          <t xml:space="preserve">   coverage                   1 dòng   bắt buộc: month</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   dim_target                 4 dòng   bắt buộc: month, store, target</t>
+          <t xml:space="preserve">                                  Số ngày THỰC CÓ dữ liệu — nhận diện tháng chưa trọn kỳ. Không khai thì loader suy từ daily.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Target doanh thu theo cửa hàng × tháng. Được phép khai cả tháng tương lai.</t>
+          <t xml:space="preserve">                                  loader tự tính: partial</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   booking                    8 dòng   bắt buộc: month, status</t>
+          <t xml:space="preserve">   dim_target                 4 dòng   bắt buộc: month, store, target</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Booking tiệc &amp; sự kiện — gộp theo tháng NHẬN LEAD (month) × tháng DIỄN RA (ev_month) × cửa hàng × phân khúc × loại × nguồn × trạng thái. month = Inquiry Date → Input Date → (thiếu cả hai) ngày sự kiện, khi đó inq_est đếm số lead bị ước. seg ∈ event|table, stage ∈ won|open|lost — luật ở $booking. exp chỉ cộng ô có số (exp_n lead); ô trống/TBA KHÔNG tính là 0. closed_n = số lead Confirmed đã nhập Closed Revenue.</t>
+          <t xml:space="preserve">                                  Target doanh thu theo cửa hàng × tháng. Được phép khai cả tháng tương lai.</t>
         </is>
       </c>
     </row>
@@ -54810,16 +54810,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:R10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="9" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -54830,32 +54841,87 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
+          <t>ev_month</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
           <t>store</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>net</t>
-        </is>
-      </c>
       <c r="D1" s="4" t="inlineStr">
         <is>
-          <t>guest</t>
+          <t>brand</t>
         </is>
       </c>
       <c r="E1" s="4" t="inlineStr">
         <is>
-          <t>tc</t>
+          <t>outlet</t>
         </is>
       </c>
       <c r="F1" s="4" t="inlineStr">
         <is>
-          <t>gross</t>
+          <t>seg</t>
         </is>
       </c>
       <c r="G1" s="4" t="inlineStr">
         <is>
-          <t>disc</t>
+          <t>etype</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>stage</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>lost_reason</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>leads</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>guests</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>exp</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>exp_n</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>closed_n</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>inq_est</t>
         </is>
       </c>
     </row>
@@ -54867,23 +54933,64 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>IFC_SIG</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>80893500</v>
-      </c>
-      <c r="D2" t="n">
-        <v>612</v>
-      </c>
-      <c r="E2" t="n">
-        <v>348</v>
-      </c>
-      <c r="F2" t="n">
-        <v>82003000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1109500</v>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>NCB</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>NOIRE ET</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>MKT</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M2" t="n">
+        <v>90</v>
+      </c>
+      <c r="N2" t="n">
+        <v>75000000</v>
+      </c>
+      <c r="O2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -54894,23 +55001,69 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NCB_9ST</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>3627350</v>
-      </c>
-      <c r="D3" t="n">
-        <v>65</v>
-      </c>
-      <c r="E3" t="n">
-        <v>20</v>
-      </c>
-      <c r="F3" t="n">
-        <v>4580000</v>
-      </c>
-      <c r="G3" t="n">
-        <v>952650</v>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NCB</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>NOIRE ET</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Workshop</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>3</v>
+      </c>
+      <c r="M3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N3" t="n">
+        <v>39400000</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -54921,23 +55074,69 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>799090930</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2506</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1417</v>
-      </c>
-      <c r="F4" t="n">
-        <v>856626880</v>
-      </c>
-      <c r="G4" t="n">
-        <v>57535950</v>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>NOIRE DINING</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>YEP</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>won</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>30</v>
+      </c>
+      <c r="N4" t="n">
+        <v>36268953</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" t="n">
+        <v>36268953</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -54948,22 +55147,73 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NCB_GW</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>13133000</v>
-      </c>
-      <c r="D5" t="n">
-        <v>109</v>
-      </c>
-      <c r="E5" t="n">
-        <v>73</v>
-      </c>
-      <c r="F5" t="n">
-        <v>13133000</v>
-      </c>
-      <c r="G5" t="n">
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>NOIRE DINING</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Thuê sảnh</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>MKT</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Lost</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Không gian / sức chứa</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>40</v>
+      </c>
+      <c r="N5" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -54975,23 +55225,69 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>452497650</v>
-      </c>
-      <c r="D6" t="n">
-        <v>3147</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1933</v>
-      </c>
-      <c r="F6" t="n">
-        <v>474860000</v>
-      </c>
-      <c r="G6" t="n">
-        <v>22362350</v>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NCB</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>NOIRE ET</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Thuê sảnh</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>won</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>70</v>
+      </c>
+      <c r="N6" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -55002,23 +55298,69 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NCB_NDC</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>4223000</v>
-      </c>
-      <c r="D7" t="n">
-        <v>52</v>
-      </c>
-      <c r="E7" t="n">
-        <v>9</v>
-      </c>
-      <c r="F7" t="n">
-        <v>5922000</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1699000</v>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NCB</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>NOIRE ET</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hội nghị</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>MKT</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>20</v>
+      </c>
+      <c r="N7" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -55029,23 +55371,69 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>607080194</v>
-      </c>
-      <c r="D8" t="n">
-        <v>2344</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1094</v>
-      </c>
-      <c r="F8" t="n">
-        <v>639881844</v>
-      </c>
-      <c r="G8" t="n">
-        <v>32801650</v>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NCB</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>NOIRE ET</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hội nghị</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>won</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>40</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -55056,23 +55444,69 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>NDC_NTMK</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>2016252943</v>
-      </c>
-      <c r="D9" t="n">
-        <v>7521</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2973</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2097945393</v>
-      </c>
-      <c r="G9" t="n">
-        <v>81692450</v>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>NOIRE DINING</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Lost</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Không liên lạc được</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -55083,23 +55517,74 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>172245819</v>
-      </c>
-      <c r="D10" t="n">
-        <v>359</v>
-      </c>
-      <c r="E10" t="n">
-        <v>150</v>
-      </c>
-      <c r="F10" t="n">
-        <v>192575569</v>
-      </c>
-      <c r="G10" t="n">
-        <v>20329750</v>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>NOIRE DINING</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>YEP</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Lost</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Không liên lạc được</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>12</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -97158,7 +97643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E168"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -97166,12 +97651,14 @@
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>month</t>
         </is>
       </c>
       <c r="B1" s="4" t="inlineStr">
@@ -97192,3514 +97679,260 @@
       <c r="E1" s="4" t="inlineStr">
         <is>
           <t>tc</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>gross</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>disc</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NCB_9ST</t>
+          <t>IFC_SIG</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>446300</v>
+        <v>80893500</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>612</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>348</v>
+      </c>
+      <c r="F2" t="n">
+        <v>82003000</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1109500</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NCB_ET</t>
+          <t>NCB_9ST</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>44949600</v>
+        <v>3627350</v>
       </c>
       <c r="D3" t="n">
-        <v>147</v>
+        <v>65</v>
       </c>
       <c r="E3" t="n">
-        <v>62</v>
+        <v>20</v>
+      </c>
+      <c r="F3" t="n">
+        <v>4580000</v>
+      </c>
+      <c r="G3" t="n">
+        <v>952650</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NCB_GW</t>
+          <t>NCB_ET</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>818000</v>
+        <v>799090930</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>2506</v>
       </c>
       <c r="E4" t="n">
-        <v>8</v>
+        <v>1417</v>
+      </c>
+      <c r="F4" t="n">
+        <v>856626880</v>
+      </c>
+      <c r="G4" t="n">
+        <v>57535950</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NCB_MET</t>
+          <t>NCB_GW</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>21733600</v>
+        <v>13133000</v>
       </c>
       <c r="D5" t="n">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="E5" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="F5" t="n">
+        <v>13133000</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NDC_NTMK</t>
+          <t>NCB_MET</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>99387758</v>
+        <v>452497650</v>
       </c>
       <c r="D6" t="n">
-        <v>314</v>
+        <v>3147</v>
       </c>
       <c r="E6" t="n">
-        <v>110</v>
+        <v>1933</v>
+      </c>
+      <c r="F6" t="n">
+        <v>474860000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>22362350</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NJFB_SSV</t>
+          <t>NCB_NDC</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10310488</v>
+        <v>4223000</v>
       </c>
       <c r="D7" t="n">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="E7" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="F7" t="n">
+        <v>5922000</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1699000</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NCB_9ST</t>
+          <t>NCB_SKC</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>69000</v>
+        <v>607080194</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>2344</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>1094</v>
+      </c>
+      <c r="F8" t="n">
+        <v>639881844</v>
+      </c>
+      <c r="G8" t="n">
+        <v>32801650</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NCB_ET</t>
+          <t>NDC_NTMK</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>26682950</v>
+        <v>2016252943</v>
       </c>
       <c r="D9" t="n">
-        <v>116</v>
+        <v>7521</v>
       </c>
       <c r="E9" t="n">
-        <v>73</v>
+        <v>2973</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2097945393</v>
+      </c>
+      <c r="G9" t="n">
+        <v>81692450</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NCB_MET</t>
+          <t>NJFB_SSV</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>28472150</v>
+        <v>172245819</v>
       </c>
       <c r="D10" t="n">
-        <v>198</v>
+        <v>359</v>
       </c>
       <c r="E10" t="n">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-02-02</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>2800000</v>
-      </c>
-      <c r="D11" t="n">
-        <v>11</v>
-      </c>
-      <c r="E11" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-02-02</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>30818138</v>
-      </c>
-      <c r="D12" t="n">
-        <v>104</v>
-      </c>
-      <c r="E12" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-02-02</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>9510869</v>
-      </c>
-      <c r="D13" t="n">
-        <v>18</v>
-      </c>
-      <c r="E13" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>45319500</v>
-      </c>
-      <c r="D14" t="n">
-        <v>172</v>
-      </c>
-      <c r="E14" t="n">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>NCB_GW</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>434000</v>
-      </c>
-      <c r="D15" t="n">
-        <v>2</v>
-      </c>
-      <c r="E15" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>30613000</v>
-      </c>
-      <c r="D16" t="n">
-        <v>215</v>
-      </c>
-      <c r="E16" t="n">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>NCB_NDC</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>88500</v>
-      </c>
-      <c r="D17" t="n">
-        <v>2</v>
-      </c>
-      <c r="E17" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>55749352</v>
-      </c>
-      <c r="D18" t="n">
-        <v>172</v>
-      </c>
-      <c r="E18" t="n">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>17550947</v>
-      </c>
-      <c r="D19" t="n">
-        <v>28</v>
-      </c>
-      <c r="E19" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>23863150</v>
-      </c>
-      <c r="D20" t="n">
-        <v>109</v>
-      </c>
-      <c r="E20" t="n">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>NCB_GW</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>1241000</v>
-      </c>
-      <c r="D21" t="n">
-        <v>10</v>
-      </c>
-      <c r="E21" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>30710250</v>
-      </c>
-      <c r="D22" t="n">
-        <v>243</v>
-      </c>
-      <c r="E22" t="n">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>10196350</v>
-      </c>
-      <c r="D23" t="n">
-        <v>44</v>
-      </c>
-      <c r="E23" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>26019974</v>
-      </c>
-      <c r="D24" t="n">
-        <v>120</v>
-      </c>
-      <c r="E24" t="n">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>9300608</v>
-      </c>
-      <c r="D25" t="n">
-        <v>22</v>
-      </c>
-      <c r="E25" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>NCB_9ST</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>726100</v>
-      </c>
-      <c r="D26" t="n">
-        <v>14</v>
-      </c>
-      <c r="E26" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>17016300</v>
-      </c>
-      <c r="D27" t="n">
-        <v>98</v>
-      </c>
-      <c r="E27" t="n">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>NCB_GW</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>118000</v>
-      </c>
-      <c r="D28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>30295200</v>
-      </c>
-      <c r="D29" t="n">
-        <v>229</v>
-      </c>
-      <c r="E29" t="n">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>NCB_NDC</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>59000</v>
-      </c>
-      <c r="D30" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>4413700</v>
-      </c>
-      <c r="D31" t="n">
-        <v>33</v>
-      </c>
-      <c r="E31" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>79722056</v>
-      </c>
-      <c r="D32" t="n">
-        <v>214</v>
-      </c>
-      <c r="E32" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>6626286</v>
-      </c>
-      <c r="D33" t="n">
-        <v>15</v>
-      </c>
-      <c r="E33" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>NCB_9ST</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>207000</v>
-      </c>
-      <c r="D34" t="n">
-        <v>2</v>
-      </c>
-      <c r="E34" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>48523400</v>
-      </c>
-      <c r="D35" t="n">
-        <v>113</v>
-      </c>
-      <c r="E35" t="n">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>NCB_GW</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>157000</v>
-      </c>
-      <c r="D36" t="n">
-        <v>3</v>
-      </c>
-      <c r="E36" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>23532450</v>
-      </c>
-      <c r="D37" t="n">
-        <v>188</v>
-      </c>
-      <c r="E37" t="n">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>151586900</v>
-      </c>
-      <c r="D38" t="n">
-        <v>279</v>
-      </c>
-      <c r="E38" t="n">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>114603862</v>
-      </c>
-      <c r="D39" t="n">
-        <v>228</v>
-      </c>
-      <c r="E39" t="n">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>3234193</v>
-      </c>
-      <c r="D40" t="n">
-        <v>7</v>
-      </c>
-      <c r="E40" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>11888550</v>
-      </c>
-      <c r="D41" t="n">
-        <v>72</v>
-      </c>
-      <c r="E41" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>NCB_GW</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>1375000</v>
-      </c>
-      <c r="D42" t="n">
-        <v>8</v>
-      </c>
-      <c r="E42" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>15896400</v>
-      </c>
-      <c r="D43" t="n">
-        <v>93</v>
-      </c>
-      <c r="E43" t="n">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>5218850</v>
-      </c>
-      <c r="D44" t="n">
-        <v>37</v>
-      </c>
-      <c r="E44" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>67525243</v>
-      </c>
-      <c r="D45" t="n">
-        <v>230</v>
-      </c>
-      <c r="E45" t="n">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>15996935</v>
-      </c>
-      <c r="D46" t="n">
-        <v>31</v>
-      </c>
-      <c r="E46" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>2026-02-08</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>21760200</v>
-      </c>
-      <c r="D47" t="n">
-        <v>104</v>
-      </c>
-      <c r="E47" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>2026-02-08</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>NCB_GW</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>2358000</v>
-      </c>
-      <c r="D48" t="n">
-        <v>15</v>
-      </c>
-      <c r="E48" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>2026-02-08</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>10973100</v>
-      </c>
-      <c r="D49" t="n">
-        <v>67</v>
-      </c>
-      <c r="E49" t="n">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>2026-02-08</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>9908600</v>
-      </c>
-      <c r="D50" t="n">
-        <v>57</v>
-      </c>
-      <c r="E50" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>2026-02-08</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>81013164</v>
-      </c>
-      <c r="D51" t="n">
-        <v>339</v>
-      </c>
-      <c r="E51" t="n">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>2026-02-08</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>6473943</v>
-      </c>
-      <c r="D52" t="n">
-        <v>11</v>
-      </c>
-      <c r="E52" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>23149000</v>
-      </c>
-      <c r="D53" t="n">
-        <v>127</v>
-      </c>
-      <c r="E53" t="n">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>18762300</v>
-      </c>
-      <c r="D54" t="n">
-        <v>148</v>
-      </c>
-      <c r="E54" t="n">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>12827500</v>
-      </c>
-      <c r="D55" t="n">
-        <v>85</v>
-      </c>
-      <c r="E55" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>85365393</v>
-      </c>
-      <c r="D56" t="n">
-        <v>189</v>
-      </c>
-      <c r="E56" t="n">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>423792</v>
-      </c>
-      <c r="D57" t="n">
-        <v>1</v>
-      </c>
-      <c r="E57" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>NCB_9ST</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>108000</v>
-      </c>
-      <c r="D58" t="n">
-        <v>3</v>
-      </c>
-      <c r="E58" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>28378100</v>
-      </c>
-      <c r="D59" t="n">
-        <v>153</v>
-      </c>
-      <c r="E59" t="n">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>NCB_GW</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>589000</v>
-      </c>
-      <c r="D60" t="n">
-        <v>8</v>
-      </c>
-      <c r="E60" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>18494550</v>
-      </c>
-      <c r="D61" t="n">
-        <v>154</v>
-      </c>
-      <c r="E61" t="n">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>NCB_NDC</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>132500</v>
-      </c>
-      <c r="D62" t="n">
-        <v>3</v>
-      </c>
-      <c r="E62" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>12602650</v>
-      </c>
-      <c r="D63" t="n">
-        <v>75</v>
-      </c>
-      <c r="E63" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>77370325</v>
-      </c>
-      <c r="D64" t="n">
-        <v>198</v>
-      </c>
-      <c r="E64" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>8015998</v>
-      </c>
-      <c r="D65" t="n">
-        <v>11</v>
-      </c>
-      <c r="E65" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>37869350</v>
-      </c>
-      <c r="D66" t="n">
-        <v>117</v>
-      </c>
-      <c r="E66" t="n">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>NCB_GW</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>849000</v>
-      </c>
-      <c r="D67" t="n">
-        <v>4</v>
-      </c>
-      <c r="E67" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
-        <v>17931650</v>
-      </c>
-      <c r="D68" t="n">
-        <v>120</v>
-      </c>
-      <c r="E68" t="n">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
-        <v>5180450</v>
-      </c>
-      <c r="D69" t="n">
-        <v>37</v>
-      </c>
-      <c r="E69" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>46644344</v>
-      </c>
-      <c r="D70" t="n">
-        <v>201</v>
-      </c>
-      <c r="E70" t="n">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C71" t="n">
-        <v>7319643</v>
-      </c>
-      <c r="D71" t="n">
-        <v>15</v>
-      </c>
-      <c r="E71" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>2026-02-12</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>NCB_9ST</t>
-        </is>
-      </c>
-      <c r="C72" t="n">
-        <v>162750</v>
-      </c>
-      <c r="D72" t="n">
-        <v>3</v>
-      </c>
-      <c r="E72" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>2026-02-12</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="C73" t="n">
-        <v>245398630</v>
-      </c>
-      <c r="D73" t="n">
-        <v>96</v>
-      </c>
-      <c r="E73" t="n">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>2026-02-12</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>NCB_GW</t>
-        </is>
-      </c>
-      <c r="C74" t="n">
-        <v>884000</v>
-      </c>
-      <c r="D74" t="n">
-        <v>12</v>
-      </c>
-      <c r="E74" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>2026-02-12</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C75" t="n">
-        <v>22861950</v>
-      </c>
-      <c r="D75" t="n">
         <v>150</v>
       </c>
-      <c r="E75" t="n">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>2026-02-12</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C76" t="n">
-        <v>96088544</v>
-      </c>
-      <c r="D76" t="n">
-        <v>102</v>
-      </c>
-      <c r="E76" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>2026-02-12</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C77" t="n">
-        <v>54555506</v>
-      </c>
-      <c r="D77" t="n">
-        <v>212</v>
-      </c>
-      <c r="E77" t="n">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>2026-02-12</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C78" t="n">
-        <v>9885078</v>
-      </c>
-      <c r="D78" t="n">
-        <v>25</v>
-      </c>
-      <c r="E78" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="C79" t="n">
-        <v>24040100</v>
-      </c>
-      <c r="D79" t="n">
-        <v>87</v>
-      </c>
-      <c r="E79" t="n">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>NCB_GW</t>
-        </is>
-      </c>
-      <c r="C80" t="n">
-        <v>926000</v>
-      </c>
-      <c r="D80" t="n">
-        <v>8</v>
-      </c>
-      <c r="E80" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C81" t="n">
-        <v>11861450</v>
-      </c>
-      <c r="D81" t="n">
-        <v>89</v>
-      </c>
-      <c r="E81" t="n">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C82" t="n">
-        <v>9553850</v>
-      </c>
-      <c r="D82" t="n">
-        <v>53</v>
-      </c>
-      <c r="E82" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C83" t="n">
-        <v>46291343</v>
-      </c>
-      <c r="D83" t="n">
-        <v>190</v>
-      </c>
-      <c r="E83" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C84" t="n">
-        <v>7708050</v>
-      </c>
-      <c r="D84" t="n">
-        <v>14</v>
-      </c>
-      <c r="E84" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>2026-02-14</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>IFC_SIG</t>
-        </is>
-      </c>
-      <c r="C85" t="n">
-        <v>2884100</v>
-      </c>
-      <c r="D85" t="n">
-        <v>9</v>
-      </c>
-      <c r="E85" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>2026-02-14</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C86" t="n">
-        <v>17504150</v>
-      </c>
-      <c r="D86" t="n">
-        <v>90</v>
-      </c>
-      <c r="E86" t="n">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>2026-02-14</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C87" t="n">
-        <v>19043100</v>
-      </c>
-      <c r="D87" t="n">
-        <v>77</v>
-      </c>
-      <c r="E87" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>2026-02-14</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C88" t="n">
-        <v>119778343</v>
-      </c>
-      <c r="D88" t="n">
-        <v>308</v>
-      </c>
-      <c r="E88" t="n">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>2026-02-14</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C89" t="n">
-        <v>5364513</v>
-      </c>
-      <c r="D89" t="n">
-        <v>10</v>
-      </c>
-      <c r="E89" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>2026-02-15</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>IFC_SIG</t>
-        </is>
-      </c>
-      <c r="C90" t="n">
-        <v>435000</v>
-      </c>
-      <c r="D90" t="n">
-        <v>0</v>
-      </c>
-      <c r="E90" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>2026-02-15</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C91" t="n">
-        <v>11570700</v>
-      </c>
-      <c r="D91" t="n">
-        <v>73</v>
-      </c>
-      <c r="E91" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>2026-02-15</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C92" t="n">
-        <v>13895850</v>
-      </c>
-      <c r="D92" t="n">
-        <v>67</v>
-      </c>
-      <c r="E92" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>2026-02-15</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C93" t="n">
-        <v>63216848</v>
-      </c>
-      <c r="D93" t="n">
-        <v>258</v>
-      </c>
-      <c r="E93" t="n">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>2026-02-15</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C94" t="n">
-        <v>2896689</v>
-      </c>
-      <c r="D94" t="n">
-        <v>6</v>
-      </c>
-      <c r="E94" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>2026-02-16</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>IFC_SIG</t>
-        </is>
-      </c>
-      <c r="C95" t="n">
-        <v>20210400</v>
-      </c>
-      <c r="D95" t="n">
-        <v>44</v>
-      </c>
-      <c r="E95" t="n">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>2026-02-16</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C96" t="n">
-        <v>30971600</v>
-      </c>
-      <c r="D96" t="n">
-        <v>85</v>
-      </c>
-      <c r="E96" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>2026-02-16</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C97" t="n">
-        <v>83527290</v>
-      </c>
-      <c r="D97" t="n">
-        <v>360</v>
-      </c>
-      <c r="E97" t="n">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>2026-02-17</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>IFC_SIG</t>
-        </is>
-      </c>
-      <c r="C98" t="n">
-        <v>14136500</v>
-      </c>
-      <c r="D98" t="n">
-        <v>133</v>
-      </c>
-      <c r="E98" t="n">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>2026-02-17</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C99" t="n">
-        <v>27657000</v>
-      </c>
-      <c r="D99" t="n">
-        <v>146</v>
-      </c>
-      <c r="E99" t="n">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>2026-02-17</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C100" t="n">
-        <v>127769849</v>
-      </c>
-      <c r="D100" t="n">
-        <v>593</v>
-      </c>
-      <c r="E100" t="n">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>2026-02-18</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>IFC_SIG</t>
-        </is>
-      </c>
-      <c r="C101" t="n">
-        <v>13011000</v>
-      </c>
-      <c r="D101" t="n">
-        <v>139</v>
-      </c>
-      <c r="E101" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>2026-02-18</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C102" t="n">
-        <v>25685500</v>
-      </c>
-      <c r="D102" t="n">
-        <v>147</v>
-      </c>
-      <c r="E102" t="n">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>2026-02-18</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C103" t="n">
-        <v>116650290</v>
-      </c>
-      <c r="D103" t="n">
-        <v>544</v>
-      </c>
-      <c r="E103" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>IFC_SIG</t>
-        </is>
-      </c>
-      <c r="C104" t="n">
-        <v>9719000</v>
-      </c>
-      <c r="D104" t="n">
-        <v>94</v>
-      </c>
-      <c r="E104" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C105" t="n">
-        <v>20724000</v>
-      </c>
-      <c r="D105" t="n">
-        <v>117</v>
-      </c>
-      <c r="E105" t="n">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C106" t="n">
-        <v>126522372</v>
-      </c>
-      <c r="D106" t="n">
-        <v>564</v>
-      </c>
-      <c r="E106" t="n">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>IFC_SIG</t>
-        </is>
-      </c>
-      <c r="C107" t="n">
-        <v>9444000</v>
-      </c>
-      <c r="D107" t="n">
-        <v>95</v>
-      </c>
-      <c r="E107" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C108" t="n">
-        <v>18169000</v>
-      </c>
-      <c r="D108" t="n">
-        <v>122</v>
-      </c>
-      <c r="E108" t="n">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C109" t="n">
-        <v>88939862</v>
-      </c>
-      <c r="D109" t="n">
-        <v>409</v>
-      </c>
-      <c r="E109" t="n">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>2026-02-21</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>IFC_SIG</t>
-        </is>
-      </c>
-      <c r="C110" t="n">
-        <v>2201000</v>
-      </c>
-      <c r="D110" t="n">
-        <v>20</v>
-      </c>
-      <c r="E110" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>2026-02-21</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="C111" t="n">
-        <v>20559000</v>
-      </c>
-      <c r="D111" t="n">
-        <v>127</v>
-      </c>
-      <c r="E111" t="n">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>2026-02-21</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C112" t="n">
-        <v>5065000</v>
-      </c>
-      <c r="D112" t="n">
-        <v>25</v>
-      </c>
-      <c r="E112" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>2026-02-21</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C113" t="n">
-        <v>25486400</v>
-      </c>
-      <c r="D113" t="n">
-        <v>138</v>
-      </c>
-      <c r="E113" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>2026-02-21</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C114" t="n">
-        <v>101744461</v>
-      </c>
-      <c r="D114" t="n">
-        <v>477</v>
-      </c>
-      <c r="E114" t="n">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>2026-02-21</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C115" t="n">
-        <v>7340204</v>
-      </c>
-      <c r="D115" t="n">
-        <v>19</v>
-      </c>
-      <c r="E115" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>IFC_SIG</t>
-        </is>
-      </c>
-      <c r="C116" t="n">
-        <v>1884000</v>
-      </c>
-      <c r="D116" t="n">
-        <v>17</v>
-      </c>
-      <c r="E116" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="C117" t="n">
-        <v>27563800</v>
-      </c>
-      <c r="D117" t="n">
-        <v>141</v>
-      </c>
-      <c r="E117" t="n">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C118" t="n">
-        <v>11443400</v>
-      </c>
-      <c r="D118" t="n">
-        <v>63</v>
-      </c>
-      <c r="E118" t="n">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C119" t="n">
-        <v>21849650</v>
-      </c>
-      <c r="D119" t="n">
-        <v>119</v>
-      </c>
-      <c r="E119" t="n">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C120" t="n">
-        <v>72709573</v>
-      </c>
-      <c r="D120" t="n">
-        <v>331</v>
-      </c>
-      <c r="E120" t="n">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C121" t="n">
-        <v>5162648</v>
-      </c>
-      <c r="D121" t="n">
-        <v>9</v>
-      </c>
-      <c r="E121" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>IFC_SIG</t>
-        </is>
-      </c>
-      <c r="C122" t="n">
-        <v>901200</v>
-      </c>
-      <c r="D122" t="n">
-        <v>11</v>
-      </c>
-      <c r="E122" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>NCB_9ST</t>
-        </is>
-      </c>
-      <c r="C123" t="n">
-        <v>265500</v>
-      </c>
-      <c r="D123" t="n">
-        <v>6</v>
-      </c>
-      <c r="E123" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="C124" t="n">
-        <v>22258100</v>
-      </c>
-      <c r="D124" t="n">
-        <v>97</v>
-      </c>
-      <c r="E124" t="n">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C125" t="n">
-        <v>22545150</v>
-      </c>
-      <c r="D125" t="n">
-        <v>180</v>
-      </c>
-      <c r="E125" t="n">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C126" t="n">
-        <v>10548300</v>
-      </c>
-      <c r="D126" t="n">
-        <v>95</v>
-      </c>
-      <c r="E126" t="n">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C127" t="n">
-        <v>40174163</v>
-      </c>
-      <c r="D127" t="n">
-        <v>198</v>
-      </c>
-      <c r="E127" t="n">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C128" t="n">
-        <v>7396993</v>
-      </c>
-      <c r="D128" t="n">
-        <v>15</v>
-      </c>
-      <c r="E128" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>IFC_SIG</t>
-        </is>
-      </c>
-      <c r="C129" t="n">
-        <v>740700</v>
-      </c>
-      <c r="D129" t="n">
-        <v>8</v>
-      </c>
-      <c r="E129" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>NCB_9ST</t>
-        </is>
-      </c>
-      <c r="C130" t="n">
-        <v>88500</v>
-      </c>
-      <c r="D130" t="n">
-        <v>3</v>
-      </c>
-      <c r="E130" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="C131" t="n">
-        <v>29497550</v>
-      </c>
-      <c r="D131" t="n">
-        <v>127</v>
-      </c>
-      <c r="E131" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>NCB_GW</t>
-        </is>
-      </c>
-      <c r="C132" t="n">
-        <v>285000</v>
-      </c>
-      <c r="D132" t="n">
-        <v>3</v>
-      </c>
-      <c r="E132" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C133" t="n">
-        <v>17880450</v>
-      </c>
-      <c r="D133" t="n">
-        <v>140</v>
-      </c>
-      <c r="E133" t="n">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C134" t="n">
-        <v>14701400</v>
-      </c>
-      <c r="D134" t="n">
-        <v>114</v>
-      </c>
-      <c r="E134" t="n">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C135" t="n">
-        <v>41649428</v>
-      </c>
-      <c r="D135" t="n">
-        <v>161</v>
-      </c>
-      <c r="E135" t="n">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C136" t="n">
-        <v>14366112</v>
-      </c>
-      <c r="D136" t="n">
-        <v>32</v>
-      </c>
-      <c r="E136" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>IFC_SIG</t>
-        </is>
-      </c>
-      <c r="C137" t="n">
-        <v>2001200</v>
-      </c>
-      <c r="D137" t="n">
-        <v>8</v>
-      </c>
-      <c r="E137" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>NCB_9ST</t>
-        </is>
-      </c>
-      <c r="C138" t="n">
-        <v>59000</v>
-      </c>
-      <c r="D138" t="n">
-        <v>1</v>
-      </c>
-      <c r="E138" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="C139" t="n">
-        <v>24422550</v>
-      </c>
-      <c r="D139" t="n">
-        <v>113</v>
-      </c>
-      <c r="E139" t="n">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>NCB_GW</t>
-        </is>
-      </c>
-      <c r="C140" t="n">
-        <v>205000</v>
-      </c>
-      <c r="D140" t="n">
-        <v>3</v>
-      </c>
-      <c r="E140" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C141" t="n">
-        <v>20358400</v>
-      </c>
-      <c r="D141" t="n">
-        <v>147</v>
-      </c>
-      <c r="E141" t="n">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C142" t="n">
-        <v>13035400</v>
-      </c>
-      <c r="D142" t="n">
-        <v>72</v>
-      </c>
-      <c r="E142" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C143" t="n">
-        <v>32036744</v>
-      </c>
-      <c r="D143" t="n">
-        <v>139</v>
-      </c>
-      <c r="E143" t="n">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C144" t="n">
-        <v>10478168</v>
-      </c>
-      <c r="D144" t="n">
-        <v>31</v>
-      </c>
-      <c r="E144" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>IFC_SIG</t>
-        </is>
-      </c>
-      <c r="C145" t="n">
-        <v>1341400</v>
-      </c>
-      <c r="D145" t="n">
-        <v>22</v>
-      </c>
-      <c r="E145" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="C146" t="n">
-        <v>18176900</v>
-      </c>
-      <c r="D146" t="n">
-        <v>87</v>
-      </c>
-      <c r="E146" t="n">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>NCB_GW</t>
-        </is>
-      </c>
-      <c r="C147" t="n">
-        <v>654000</v>
-      </c>
-      <c r="D147" t="n">
-        <v>3</v>
-      </c>
-      <c r="E147" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C148" t="n">
-        <v>20145150</v>
-      </c>
-      <c r="D148" t="n">
-        <v>137</v>
-      </c>
-      <c r="E148" t="n">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C149" t="n">
-        <v>17245600</v>
-      </c>
-      <c r="D149" t="n">
-        <v>82</v>
-      </c>
-      <c r="E149" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C150" t="n">
-        <v>36075966</v>
-      </c>
-      <c r="D150" t="n">
-        <v>144</v>
-      </c>
-      <c r="E150" t="n">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C151" t="n">
-        <v>439992</v>
-      </c>
-      <c r="D151" t="n">
-        <v>2</v>
-      </c>
-      <c r="E151" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>IFC_SIG</t>
-        </is>
-      </c>
-      <c r="C152" t="n">
-        <v>1583100</v>
-      </c>
-      <c r="D152" t="n">
-        <v>9</v>
-      </c>
-      <c r="E152" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>NCB_9ST</t>
-        </is>
-      </c>
-      <c r="C153" t="n">
-        <v>1343250</v>
-      </c>
-      <c r="D153" t="n">
-        <v>27</v>
-      </c>
-      <c r="E153" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="C154" t="n">
-        <v>28587800</v>
-      </c>
-      <c r="D154" t="n">
-        <v>150</v>
-      </c>
-      <c r="E154" t="n">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>NCB_GW</t>
-        </is>
-      </c>
-      <c r="C155" t="n">
-        <v>365000</v>
-      </c>
-      <c r="D155" t="n">
-        <v>3</v>
-      </c>
-      <c r="E155" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C156" t="n">
-        <v>27607700</v>
-      </c>
-      <c r="D156" t="n">
-        <v>175</v>
-      </c>
-      <c r="E156" t="n">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>NCB_NDC</t>
-        </is>
-      </c>
-      <c r="C157" t="n">
-        <v>3943000</v>
-      </c>
-      <c r="D157" t="n">
-        <v>46</v>
-      </c>
-      <c r="E157" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C158" t="n">
-        <v>8967100</v>
-      </c>
-      <c r="D158" t="n">
-        <v>74</v>
-      </c>
-      <c r="E158" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C159" t="n">
-        <v>46824918</v>
-      </c>
-      <c r="D159" t="n">
-        <v>140</v>
-      </c>
-      <c r="E159" t="n">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C160" t="n">
-        <v>1044767</v>
-      </c>
-      <c r="D160" t="n">
-        <v>4</v>
-      </c>
-      <c r="E160" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>IFC_SIG</t>
-        </is>
-      </c>
-      <c r="C161" t="n">
-        <v>400900</v>
-      </c>
-      <c r="D161" t="n">
-        <v>3</v>
-      </c>
-      <c r="E161" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>NCB_9ST</t>
-        </is>
-      </c>
-      <c r="C162" t="n">
-        <v>151950</v>
-      </c>
-      <c r="D162" t="n">
-        <v>3</v>
-      </c>
-      <c r="E162" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="C163" t="n">
-        <v>29186400</v>
-      </c>
-      <c r="D163" t="n">
-        <v>153</v>
-      </c>
-      <c r="E163" t="n">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>NCB_GW</t>
-        </is>
-      </c>
-      <c r="C164" t="n">
-        <v>1875000</v>
-      </c>
-      <c r="D164" t="n">
-        <v>16</v>
-      </c>
-      <c r="E164" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C165" t="n">
-        <v>16239500</v>
-      </c>
-      <c r="D165" t="n">
-        <v>97</v>
-      </c>
-      <c r="E165" t="n">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C166" t="n">
-        <v>18722900</v>
-      </c>
-      <c r="D166" t="n">
-        <v>76</v>
-      </c>
-      <c r="E166" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C167" t="n">
-        <v>53566378</v>
-      </c>
-      <c r="D167" t="n">
-        <v>184</v>
-      </c>
-      <c r="E167" t="n">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C168" t="n">
-        <v>5398903</v>
-      </c>
-      <c r="D168" t="n">
-        <v>16</v>
-      </c>
-      <c r="E168" t="n">
-        <v>5</v>
+      <c r="F10" t="n">
+        <v>192575569</v>
+      </c>
+      <c r="G10" t="n">
+        <v>20329750</v>
       </c>
     </row>
   </sheetData>
@@ -100752,6 +97985,3561 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E168"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>net</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>NCB_9ST</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>446300</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>44949600</v>
+      </c>
+      <c r="D3" t="n">
+        <v>147</v>
+      </c>
+      <c r="E3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NCB_GW</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>818000</v>
+      </c>
+      <c r="D4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E4" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>21733600</v>
+      </c>
+      <c r="D5" t="n">
+        <v>126</v>
+      </c>
+      <c r="E5" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>99387758</v>
+      </c>
+      <c r="D6" t="n">
+        <v>314</v>
+      </c>
+      <c r="E6" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>10310488</v>
+      </c>
+      <c r="D7" t="n">
+        <v>17</v>
+      </c>
+      <c r="E7" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>NCB_9ST</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>69000</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>26682950</v>
+      </c>
+      <c r="D9" t="n">
+        <v>116</v>
+      </c>
+      <c r="E9" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>28472150</v>
+      </c>
+      <c r="D10" t="n">
+        <v>198</v>
+      </c>
+      <c r="E10" t="n">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2800000</v>
+      </c>
+      <c r="D11" t="n">
+        <v>11</v>
+      </c>
+      <c r="E11" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>30818138</v>
+      </c>
+      <c r="D12" t="n">
+        <v>104</v>
+      </c>
+      <c r="E12" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>9510869</v>
+      </c>
+      <c r="D13" t="n">
+        <v>18</v>
+      </c>
+      <c r="E13" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>45319500</v>
+      </c>
+      <c r="D14" t="n">
+        <v>172</v>
+      </c>
+      <c r="E14" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>NCB_GW</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>434000</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>30613000</v>
+      </c>
+      <c r="D16" t="n">
+        <v>215</v>
+      </c>
+      <c r="E16" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>NCB_NDC</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>88500</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>55749352</v>
+      </c>
+      <c r="D18" t="n">
+        <v>172</v>
+      </c>
+      <c r="E18" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>17550947</v>
+      </c>
+      <c r="D19" t="n">
+        <v>28</v>
+      </c>
+      <c r="E19" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>23863150</v>
+      </c>
+      <c r="D20" t="n">
+        <v>109</v>
+      </c>
+      <c r="E20" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>NCB_GW</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1241000</v>
+      </c>
+      <c r="D21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>30710250</v>
+      </c>
+      <c r="D22" t="n">
+        <v>243</v>
+      </c>
+      <c r="E22" t="n">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>10196350</v>
+      </c>
+      <c r="D23" t="n">
+        <v>44</v>
+      </c>
+      <c r="E23" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>26019974</v>
+      </c>
+      <c r="D24" t="n">
+        <v>120</v>
+      </c>
+      <c r="E24" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>9300608</v>
+      </c>
+      <c r="D25" t="n">
+        <v>22</v>
+      </c>
+      <c r="E25" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>NCB_9ST</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>726100</v>
+      </c>
+      <c r="D26" t="n">
+        <v>14</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>17016300</v>
+      </c>
+      <c r="D27" t="n">
+        <v>98</v>
+      </c>
+      <c r="E27" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>NCB_GW</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>118000</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>30295200</v>
+      </c>
+      <c r="D29" t="n">
+        <v>229</v>
+      </c>
+      <c r="E29" t="n">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>NCB_NDC</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>59000</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>4413700</v>
+      </c>
+      <c r="D31" t="n">
+        <v>33</v>
+      </c>
+      <c r="E31" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>79722056</v>
+      </c>
+      <c r="D32" t="n">
+        <v>214</v>
+      </c>
+      <c r="E32" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>6626286</v>
+      </c>
+      <c r="D33" t="n">
+        <v>15</v>
+      </c>
+      <c r="E33" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>NCB_9ST</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>207000</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>48523400</v>
+      </c>
+      <c r="D35" t="n">
+        <v>113</v>
+      </c>
+      <c r="E35" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>NCB_GW</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>157000</v>
+      </c>
+      <c r="D36" t="n">
+        <v>3</v>
+      </c>
+      <c r="E36" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>23532450</v>
+      </c>
+      <c r="D37" t="n">
+        <v>188</v>
+      </c>
+      <c r="E37" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>151586900</v>
+      </c>
+      <c r="D38" t="n">
+        <v>279</v>
+      </c>
+      <c r="E38" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>114603862</v>
+      </c>
+      <c r="D39" t="n">
+        <v>228</v>
+      </c>
+      <c r="E39" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>3234193</v>
+      </c>
+      <c r="D40" t="n">
+        <v>7</v>
+      </c>
+      <c r="E40" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>11888550</v>
+      </c>
+      <c r="D41" t="n">
+        <v>72</v>
+      </c>
+      <c r="E41" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>NCB_GW</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>1375000</v>
+      </c>
+      <c r="D42" t="n">
+        <v>8</v>
+      </c>
+      <c r="E42" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>15896400</v>
+      </c>
+      <c r="D43" t="n">
+        <v>93</v>
+      </c>
+      <c r="E43" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>5218850</v>
+      </c>
+      <c r="D44" t="n">
+        <v>37</v>
+      </c>
+      <c r="E44" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>67525243</v>
+      </c>
+      <c r="D45" t="n">
+        <v>230</v>
+      </c>
+      <c r="E45" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>15996935</v>
+      </c>
+      <c r="D46" t="n">
+        <v>31</v>
+      </c>
+      <c r="E46" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>21760200</v>
+      </c>
+      <c r="D47" t="n">
+        <v>104</v>
+      </c>
+      <c r="E47" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>NCB_GW</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>2358000</v>
+      </c>
+      <c r="D48" t="n">
+        <v>15</v>
+      </c>
+      <c r="E48" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>10973100</v>
+      </c>
+      <c r="D49" t="n">
+        <v>67</v>
+      </c>
+      <c r="E49" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>9908600</v>
+      </c>
+      <c r="D50" t="n">
+        <v>57</v>
+      </c>
+      <c r="E50" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>81013164</v>
+      </c>
+      <c r="D51" t="n">
+        <v>339</v>
+      </c>
+      <c r="E51" t="n">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>6473943</v>
+      </c>
+      <c r="D52" t="n">
+        <v>11</v>
+      </c>
+      <c r="E52" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>23149000</v>
+      </c>
+      <c r="D53" t="n">
+        <v>127</v>
+      </c>
+      <c r="E53" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>18762300</v>
+      </c>
+      <c r="D54" t="n">
+        <v>148</v>
+      </c>
+      <c r="E54" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>12827500</v>
+      </c>
+      <c r="D55" t="n">
+        <v>85</v>
+      </c>
+      <c r="E55" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>85365393</v>
+      </c>
+      <c r="D56" t="n">
+        <v>189</v>
+      </c>
+      <c r="E56" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>423792</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>NCB_9ST</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>108000</v>
+      </c>
+      <c r="D58" t="n">
+        <v>3</v>
+      </c>
+      <c r="E58" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>28378100</v>
+      </c>
+      <c r="D59" t="n">
+        <v>153</v>
+      </c>
+      <c r="E59" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>NCB_GW</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>589000</v>
+      </c>
+      <c r="D60" t="n">
+        <v>8</v>
+      </c>
+      <c r="E60" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>18494550</v>
+      </c>
+      <c r="D61" t="n">
+        <v>154</v>
+      </c>
+      <c r="E61" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>NCB_NDC</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>132500</v>
+      </c>
+      <c r="D62" t="n">
+        <v>3</v>
+      </c>
+      <c r="E62" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>12602650</v>
+      </c>
+      <c r="D63" t="n">
+        <v>75</v>
+      </c>
+      <c r="E63" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>77370325</v>
+      </c>
+      <c r="D64" t="n">
+        <v>198</v>
+      </c>
+      <c r="E64" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>8015998</v>
+      </c>
+      <c r="D65" t="n">
+        <v>11</v>
+      </c>
+      <c r="E65" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>37869350</v>
+      </c>
+      <c r="D66" t="n">
+        <v>117</v>
+      </c>
+      <c r="E66" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>NCB_GW</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>849000</v>
+      </c>
+      <c r="D67" t="n">
+        <v>4</v>
+      </c>
+      <c r="E67" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>17931650</v>
+      </c>
+      <c r="D68" t="n">
+        <v>120</v>
+      </c>
+      <c r="E68" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>5180450</v>
+      </c>
+      <c r="D69" t="n">
+        <v>37</v>
+      </c>
+      <c r="E69" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>46644344</v>
+      </c>
+      <c r="D70" t="n">
+        <v>201</v>
+      </c>
+      <c r="E70" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>7319643</v>
+      </c>
+      <c r="D71" t="n">
+        <v>15</v>
+      </c>
+      <c r="E71" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>NCB_9ST</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>162750</v>
+      </c>
+      <c r="D72" t="n">
+        <v>3</v>
+      </c>
+      <c r="E72" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>245398630</v>
+      </c>
+      <c r="D73" t="n">
+        <v>96</v>
+      </c>
+      <c r="E73" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>NCB_GW</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>884000</v>
+      </c>
+      <c r="D74" t="n">
+        <v>12</v>
+      </c>
+      <c r="E74" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>22861950</v>
+      </c>
+      <c r="D75" t="n">
+        <v>150</v>
+      </c>
+      <c r="E75" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>96088544</v>
+      </c>
+      <c r="D76" t="n">
+        <v>102</v>
+      </c>
+      <c r="E76" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>54555506</v>
+      </c>
+      <c r="D77" t="n">
+        <v>212</v>
+      </c>
+      <c r="E77" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>9885078</v>
+      </c>
+      <c r="D78" t="n">
+        <v>25</v>
+      </c>
+      <c r="E78" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>24040100</v>
+      </c>
+      <c r="D79" t="n">
+        <v>87</v>
+      </c>
+      <c r="E79" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>NCB_GW</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>926000</v>
+      </c>
+      <c r="D80" t="n">
+        <v>8</v>
+      </c>
+      <c r="E80" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>11861450</v>
+      </c>
+      <c r="D81" t="n">
+        <v>89</v>
+      </c>
+      <c r="E81" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>9553850</v>
+      </c>
+      <c r="D82" t="n">
+        <v>53</v>
+      </c>
+      <c r="E82" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>46291343</v>
+      </c>
+      <c r="D83" t="n">
+        <v>190</v>
+      </c>
+      <c r="E83" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>7708050</v>
+      </c>
+      <c r="D84" t="n">
+        <v>14</v>
+      </c>
+      <c r="E84" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>IFC_SIG</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>2884100</v>
+      </c>
+      <c r="D85" t="n">
+        <v>9</v>
+      </c>
+      <c r="E85" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>17504150</v>
+      </c>
+      <c r="D86" t="n">
+        <v>90</v>
+      </c>
+      <c r="E86" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>19043100</v>
+      </c>
+      <c r="D87" t="n">
+        <v>77</v>
+      </c>
+      <c r="E87" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>119778343</v>
+      </c>
+      <c r="D88" t="n">
+        <v>308</v>
+      </c>
+      <c r="E88" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>5364513</v>
+      </c>
+      <c r="D89" t="n">
+        <v>10</v>
+      </c>
+      <c r="E89" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>IFC_SIG</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>435000</v>
+      </c>
+      <c r="D90" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>11570700</v>
+      </c>
+      <c r="D91" t="n">
+        <v>73</v>
+      </c>
+      <c r="E91" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>13895850</v>
+      </c>
+      <c r="D92" t="n">
+        <v>67</v>
+      </c>
+      <c r="E92" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>63216848</v>
+      </c>
+      <c r="D93" t="n">
+        <v>258</v>
+      </c>
+      <c r="E93" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>2896689</v>
+      </c>
+      <c r="D94" t="n">
+        <v>6</v>
+      </c>
+      <c r="E94" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>IFC_SIG</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>20210400</v>
+      </c>
+      <c r="D95" t="n">
+        <v>44</v>
+      </c>
+      <c r="E95" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>30971600</v>
+      </c>
+      <c r="D96" t="n">
+        <v>85</v>
+      </c>
+      <c r="E96" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>83527290</v>
+      </c>
+      <c r="D97" t="n">
+        <v>360</v>
+      </c>
+      <c r="E97" t="n">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>IFC_SIG</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>14136500</v>
+      </c>
+      <c r="D98" t="n">
+        <v>133</v>
+      </c>
+      <c r="E98" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>27657000</v>
+      </c>
+      <c r="D99" t="n">
+        <v>146</v>
+      </c>
+      <c r="E99" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>127769849</v>
+      </c>
+      <c r="D100" t="n">
+        <v>593</v>
+      </c>
+      <c r="E100" t="n">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>IFC_SIG</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>13011000</v>
+      </c>
+      <c r="D101" t="n">
+        <v>139</v>
+      </c>
+      <c r="E101" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>25685500</v>
+      </c>
+      <c r="D102" t="n">
+        <v>147</v>
+      </c>
+      <c r="E102" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>116650290</v>
+      </c>
+      <c r="D103" t="n">
+        <v>544</v>
+      </c>
+      <c r="E103" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>IFC_SIG</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>9719000</v>
+      </c>
+      <c r="D104" t="n">
+        <v>94</v>
+      </c>
+      <c r="E104" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>20724000</v>
+      </c>
+      <c r="D105" t="n">
+        <v>117</v>
+      </c>
+      <c r="E105" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>126522372</v>
+      </c>
+      <c r="D106" t="n">
+        <v>564</v>
+      </c>
+      <c r="E106" t="n">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>IFC_SIG</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>9444000</v>
+      </c>
+      <c r="D107" t="n">
+        <v>95</v>
+      </c>
+      <c r="E107" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>18169000</v>
+      </c>
+      <c r="D108" t="n">
+        <v>122</v>
+      </c>
+      <c r="E108" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>88939862</v>
+      </c>
+      <c r="D109" t="n">
+        <v>409</v>
+      </c>
+      <c r="E109" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>IFC_SIG</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>2201000</v>
+      </c>
+      <c r="D110" t="n">
+        <v>20</v>
+      </c>
+      <c r="E110" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>20559000</v>
+      </c>
+      <c r="D111" t="n">
+        <v>127</v>
+      </c>
+      <c r="E111" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>5065000</v>
+      </c>
+      <c r="D112" t="n">
+        <v>25</v>
+      </c>
+      <c r="E112" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>25486400</v>
+      </c>
+      <c r="D113" t="n">
+        <v>138</v>
+      </c>
+      <c r="E113" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>101744461</v>
+      </c>
+      <c r="D114" t="n">
+        <v>477</v>
+      </c>
+      <c r="E114" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>7340204</v>
+      </c>
+      <c r="D115" t="n">
+        <v>19</v>
+      </c>
+      <c r="E115" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>IFC_SIG</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>1884000</v>
+      </c>
+      <c r="D116" t="n">
+        <v>17</v>
+      </c>
+      <c r="E116" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>27563800</v>
+      </c>
+      <c r="D117" t="n">
+        <v>141</v>
+      </c>
+      <c r="E117" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>11443400</v>
+      </c>
+      <c r="D118" t="n">
+        <v>63</v>
+      </c>
+      <c r="E118" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>21849650</v>
+      </c>
+      <c r="D119" t="n">
+        <v>119</v>
+      </c>
+      <c r="E119" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>72709573</v>
+      </c>
+      <c r="D120" t="n">
+        <v>331</v>
+      </c>
+      <c r="E120" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>5162648</v>
+      </c>
+      <c r="D121" t="n">
+        <v>9</v>
+      </c>
+      <c r="E121" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>IFC_SIG</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>901200</v>
+      </c>
+      <c r="D122" t="n">
+        <v>11</v>
+      </c>
+      <c r="E122" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>NCB_9ST</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>265500</v>
+      </c>
+      <c r="D123" t="n">
+        <v>6</v>
+      </c>
+      <c r="E123" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>22258100</v>
+      </c>
+      <c r="D124" t="n">
+        <v>97</v>
+      </c>
+      <c r="E124" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>22545150</v>
+      </c>
+      <c r="D125" t="n">
+        <v>180</v>
+      </c>
+      <c r="E125" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>10548300</v>
+      </c>
+      <c r="D126" t="n">
+        <v>95</v>
+      </c>
+      <c r="E126" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>40174163</v>
+      </c>
+      <c r="D127" t="n">
+        <v>198</v>
+      </c>
+      <c r="E127" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>7396993</v>
+      </c>
+      <c r="D128" t="n">
+        <v>15</v>
+      </c>
+      <c r="E128" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>IFC_SIG</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>740700</v>
+      </c>
+      <c r="D129" t="n">
+        <v>8</v>
+      </c>
+      <c r="E129" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>NCB_9ST</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>88500</v>
+      </c>
+      <c r="D130" t="n">
+        <v>3</v>
+      </c>
+      <c r="E130" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>29497550</v>
+      </c>
+      <c r="D131" t="n">
+        <v>127</v>
+      </c>
+      <c r="E131" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>NCB_GW</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>285000</v>
+      </c>
+      <c r="D132" t="n">
+        <v>3</v>
+      </c>
+      <c r="E132" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>17880450</v>
+      </c>
+      <c r="D133" t="n">
+        <v>140</v>
+      </c>
+      <c r="E133" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>14701400</v>
+      </c>
+      <c r="D134" t="n">
+        <v>114</v>
+      </c>
+      <c r="E134" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>41649428</v>
+      </c>
+      <c r="D135" t="n">
+        <v>161</v>
+      </c>
+      <c r="E135" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>14366112</v>
+      </c>
+      <c r="D136" t="n">
+        <v>32</v>
+      </c>
+      <c r="E136" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>IFC_SIG</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>2001200</v>
+      </c>
+      <c r="D137" t="n">
+        <v>8</v>
+      </c>
+      <c r="E137" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>NCB_9ST</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>59000</v>
+      </c>
+      <c r="D138" t="n">
+        <v>1</v>
+      </c>
+      <c r="E138" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>24422550</v>
+      </c>
+      <c r="D139" t="n">
+        <v>113</v>
+      </c>
+      <c r="E139" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>NCB_GW</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>205000</v>
+      </c>
+      <c r="D140" t="n">
+        <v>3</v>
+      </c>
+      <c r="E140" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>20358400</v>
+      </c>
+      <c r="D141" t="n">
+        <v>147</v>
+      </c>
+      <c r="E141" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>13035400</v>
+      </c>
+      <c r="D142" t="n">
+        <v>72</v>
+      </c>
+      <c r="E142" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>32036744</v>
+      </c>
+      <c r="D143" t="n">
+        <v>139</v>
+      </c>
+      <c r="E143" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>10478168</v>
+      </c>
+      <c r="D144" t="n">
+        <v>31</v>
+      </c>
+      <c r="E144" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>IFC_SIG</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>1341400</v>
+      </c>
+      <c r="D145" t="n">
+        <v>22</v>
+      </c>
+      <c r="E145" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>18176900</v>
+      </c>
+      <c r="D146" t="n">
+        <v>87</v>
+      </c>
+      <c r="E146" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>NCB_GW</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>654000</v>
+      </c>
+      <c r="D147" t="n">
+        <v>3</v>
+      </c>
+      <c r="E147" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>20145150</v>
+      </c>
+      <c r="D148" t="n">
+        <v>137</v>
+      </c>
+      <c r="E148" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>17245600</v>
+      </c>
+      <c r="D149" t="n">
+        <v>82</v>
+      </c>
+      <c r="E149" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>36075966</v>
+      </c>
+      <c r="D150" t="n">
+        <v>144</v>
+      </c>
+      <c r="E150" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>439992</v>
+      </c>
+      <c r="D151" t="n">
+        <v>2</v>
+      </c>
+      <c r="E151" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>IFC_SIG</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>1583100</v>
+      </c>
+      <c r="D152" t="n">
+        <v>9</v>
+      </c>
+      <c r="E152" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>NCB_9ST</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>1343250</v>
+      </c>
+      <c r="D153" t="n">
+        <v>27</v>
+      </c>
+      <c r="E153" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>28587800</v>
+      </c>
+      <c r="D154" t="n">
+        <v>150</v>
+      </c>
+      <c r="E154" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>NCB_GW</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>365000</v>
+      </c>
+      <c r="D155" t="n">
+        <v>3</v>
+      </c>
+      <c r="E155" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>27607700</v>
+      </c>
+      <c r="D156" t="n">
+        <v>175</v>
+      </c>
+      <c r="E156" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>NCB_NDC</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>3943000</v>
+      </c>
+      <c r="D157" t="n">
+        <v>46</v>
+      </c>
+      <c r="E157" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>8967100</v>
+      </c>
+      <c r="D158" t="n">
+        <v>74</v>
+      </c>
+      <c r="E158" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>46824918</v>
+      </c>
+      <c r="D159" t="n">
+        <v>140</v>
+      </c>
+      <c r="E159" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>1044767</v>
+      </c>
+      <c r="D160" t="n">
+        <v>4</v>
+      </c>
+      <c r="E160" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>IFC_SIG</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>400900</v>
+      </c>
+      <c r="D161" t="n">
+        <v>3</v>
+      </c>
+      <c r="E161" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>NCB_9ST</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>151950</v>
+      </c>
+      <c r="D162" t="n">
+        <v>3</v>
+      </c>
+      <c r="E162" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>29186400</v>
+      </c>
+      <c r="D163" t="n">
+        <v>153</v>
+      </c>
+      <c r="E163" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>NCB_GW</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>1875000</v>
+      </c>
+      <c r="D164" t="n">
+        <v>16</v>
+      </c>
+      <c r="E164" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>16239500</v>
+      </c>
+      <c r="D165" t="n">
+        <v>97</v>
+      </c>
+      <c r="E165" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>18722900</v>
+      </c>
+      <c r="D166" t="n">
+        <v>76</v>
+      </c>
+      <c r="E166" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>53566378</v>
+      </c>
+      <c r="D167" t="n">
+        <v>184</v>
+      </c>
+      <c r="E167" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>5398903</v>
+      </c>
+      <c r="D168" t="n">
+        <v>16</v>
+      </c>
+      <c r="E168" t="n">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -100822,7 +101610,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -100911,726 +101699,6 @@
       </c>
       <c r="C5" t="n">
         <v>340000000</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:R9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="9" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="9" customWidth="1" min="14" max="14"/>
-    <col width="9" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="11" customWidth="1" min="18" max="18"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>month</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>ev_month</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>store</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>brand</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>outlet</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>seg</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>etype</t>
-        </is>
-      </c>
-      <c r="H1" s="4" t="inlineStr">
-        <is>
-          <t>source</t>
-        </is>
-      </c>
-      <c r="I1" s="4" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="J1" s="4" t="inlineStr">
-        <is>
-          <t>stage</t>
-        </is>
-      </c>
-      <c r="K1" s="4" t="inlineStr">
-        <is>
-          <t>lost_reason</t>
-        </is>
-      </c>
-      <c r="L1" s="4" t="inlineStr">
-        <is>
-          <t>leads</t>
-        </is>
-      </c>
-      <c r="M1" s="4" t="inlineStr">
-        <is>
-          <t>guests</t>
-        </is>
-      </c>
-      <c r="N1" s="4" t="inlineStr">
-        <is>
-          <t>exp</t>
-        </is>
-      </c>
-      <c r="O1" s="4" t="inlineStr">
-        <is>
-          <t>exp_n</t>
-        </is>
-      </c>
-      <c r="P1" s="4" t="inlineStr">
-        <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="Q1" s="4" t="inlineStr">
-        <is>
-          <t>closed_n</t>
-        </is>
-      </c>
-      <c r="R1" s="4" t="inlineStr">
-        <is>
-          <t>inq_est</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>NCB</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>NOIRE ET</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>event</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Workshop</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>3</v>
-      </c>
-      <c r="M2" t="n">
-        <v>100</v>
-      </c>
-      <c r="N2" t="n">
-        <v>39400000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>3</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>NDC</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>NOIRE DINING</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>event</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>YEP</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>won</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M3" t="n">
-        <v>30</v>
-      </c>
-      <c r="N3" t="n">
-        <v>36268953</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1</v>
-      </c>
-      <c r="P3" t="n">
-        <v>36268953</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>NDC</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>NOIRE DINING</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>event</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Thuê sảnh</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>MKT</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Lost</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Không gian / sức chứa</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" t="n">
-        <v>40</v>
-      </c>
-      <c r="N4" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>NCB</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>NOIRE ET</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>event</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Thuê sảnh</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>won</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" t="n">
-        <v>70</v>
-      </c>
-      <c r="N5" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1</v>
-      </c>
-      <c r="P5" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>NCB</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>NOIRE ET</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>event</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Hội nghị</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>MKT</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>20</v>
-      </c>
-      <c r="N6" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>NCB</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>NOIRE ET</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>event</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Hội nghị</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>won</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>40</v>
-      </c>
-      <c r="N7" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NDC</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>NOIRE DINING</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>event</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Lost</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Không liên lạc được</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>NDC</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>NOIRE DINING</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>event</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>YEP</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Hotline</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Lost</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Không liên lạc được</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>12</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
